--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>03/05/2026 07:17:59</t>
+          <t>04/05/2026 08:16:19</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>37573.32</v>
+        <v>39666.86</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>12796283.42</v>
+        <v>12819608.79</v>
       </c>
       <c r="S10" t="n">
         <v>8397693.800000001</v>
@@ -1798,7 +1798,7 @@
         <v>8503844.35</v>
       </c>
       <c r="U10" t="n">
-        <v>11542338.2</v>
+        <v>11565663.57</v>
       </c>
       <c r="V10" t="n">
         <v>106150.55</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1929,16 +1929,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>572061</v>
+        <v>685450</v>
       </c>
       <c r="S11" t="n">
-        <v>371611</v>
+        <v>485000</v>
       </c>
       <c r="T11" t="n">
-        <v>372061</v>
+        <v>485450</v>
       </c>
       <c r="U11" t="n">
-        <v>371611</v>
+        <v>485000</v>
       </c>
       <c r="V11" t="n">
         <v>450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4037641.2</v>
+        <v>5351497.79</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1120449.02</v>
+        <v>1471182.28</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -6689,16 +6689,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>316616</v>
+        <v>435000</v>
       </c>
       <c r="S45" t="n">
-        <v>316616</v>
+        <v>435000</v>
       </c>
       <c r="T45" t="n">
-        <v>316616</v>
+        <v>435000</v>
       </c>
       <c r="U45" t="n">
-        <v>316616</v>
+        <v>435000</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -7669,16 +7669,16 @@
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>48307</v>
+        <v>55000</v>
       </c>
       <c r="S52" t="n">
-        <v>48307</v>
+        <v>55000</v>
       </c>
       <c r="T52" t="n">
-        <v>48307</v>
+        <v>55000</v>
       </c>
       <c r="U52" t="n">
-        <v>48307</v>
+        <v>55000</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -9346,7 +9346,7 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -9364,7 +9364,7 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="X64" t="n">
         <v>200000</v>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -11309,16 +11309,16 @@
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>21720</v>
+        <v>31720</v>
       </c>
       <c r="S78" t="n">
-        <v>21270</v>
+        <v>31270</v>
       </c>
       <c r="T78" t="n">
-        <v>21720</v>
+        <v>31720</v>
       </c>
       <c r="U78" t="n">
-        <v>21270</v>
+        <v>31270</v>
       </c>
       <c r="V78" t="n">
         <v>450</v>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -16629,19 +16629,19 @@
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>507656.93</v>
+        <v>634769.33</v>
       </c>
       <c r="S116" t="n">
-        <v>236304</v>
+        <v>283736.78</v>
       </c>
       <c r="T116" t="n">
-        <v>236304</v>
+        <v>363416.4</v>
       </c>
       <c r="U116" t="n">
-        <v>284390.02</v>
+        <v>411502.42</v>
       </c>
       <c r="V116" t="n">
-        <v>0</v>
+        <v>79679.62</v>
       </c>
       <c r="W116" t="n">
         <v>427085</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -16769,16 +16769,16 @@
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>47920</v>
+        <v>92250</v>
       </c>
       <c r="S117" t="n">
-        <v>45670</v>
+        <v>90000</v>
       </c>
       <c r="T117" t="n">
-        <v>47470</v>
+        <v>91800</v>
       </c>
       <c r="U117" t="n">
-        <v>45670</v>
+        <v>90000</v>
       </c>
       <c r="V117" t="n">
         <v>1800</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -17749,16 +17749,16 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>282533</v>
+        <v>440533</v>
       </c>
       <c r="S124" t="n">
-        <v>282533</v>
+        <v>440533</v>
       </c>
       <c r="T124" t="n">
-        <v>282533</v>
+        <v>440533</v>
       </c>
       <c r="U124" t="n">
-        <v>282533</v>
+        <v>440533</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -21243,13 +21243,13 @@
         <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>19140.97</v>
       </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>33669</v>
+        <v>52809.97</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -21791,7 +21791,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>14955138.28</v>
+        <v>18190190.37</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -22351,7 +22351,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>59919823.77</v>
+        <v>60017672.37</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
@@ -22369,7 +22369,7 @@
         <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>158978189.33</v>
+        <v>160562812.26</v>
       </c>
       <c r="S157" t="n">
         <v>135266690.45</v>
@@ -22378,7 +22378,7 @@
         <v>140706402.84</v>
       </c>
       <c r="U157" t="n">
-        <v>137934589.24</v>
+        <v>139519212.17</v>
       </c>
       <c r="V157" t="n">
         <v>5439712.39</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -22771,7 +22771,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29431997.31</v>
+        <v>31386458.91</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>04/05/2026 08:16:19</t>
+          <t>05/05/2026 07:59:39</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ168"/>
+  <dimension ref="A1:AJ170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>56179.21</v>
+        <v>58747.21</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1232,10 +1232,10 @@
         <v>65947.21000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>56179.21</v>
+        <v>58747.21</v>
       </c>
       <c r="T6" t="n">
-        <v>56179.21</v>
+        <v>58747.21</v>
       </c>
       <c r="U6" t="n">
         <v>58747.21</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>334134</v>
       </c>
       <c r="O7" t="n">
         <v>8220.799999999999</v>
@@ -1366,10 +1366,10 @@
         <v>96530.67999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>63262</v>
       </c>
       <c r="R7" t="n">
-        <v>355018.03</v>
+        <v>383947.05</v>
       </c>
       <c r="S7" t="n">
         <v>150254.85</v>
@@ -1378,13 +1378,13 @@
         <v>150254.85</v>
       </c>
       <c r="U7" t="n">
-        <v>258487.35</v>
+        <v>287416.37</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>264449</v>
+        <v>661845</v>
       </c>
       <c r="X7" t="n">
         <v>327711</v>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>327711</v>
+        <v>661845</v>
       </c>
       <c r="AB7" t="n">
         <v>5</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1886631.1</v>
+        <v>1891034.93</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1783,13 +1783,13 @@
         <v>1762096.42</v>
       </c>
       <c r="P10" t="n">
-        <v>1253945.22</v>
+        <v>1304276.15</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>12819608.79</v>
+        <v>12867648.63</v>
       </c>
       <c r="S10" t="n">
         <v>8397693.800000001</v>
@@ -1798,7 +1798,7 @@
         <v>8503844.35</v>
       </c>
       <c r="U10" t="n">
-        <v>11565663.57</v>
+        <v>11563372.48</v>
       </c>
       <c r="V10" t="n">
         <v>106150.55</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v>116000</v>
       </c>
       <c r="O11" t="n">
-        <v>20751.24</v>
+        <v>20963.32</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1929,16 +1929,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>685450</v>
+        <v>685900</v>
       </c>
       <c r="S11" t="n">
-        <v>485000</v>
+        <v>485450</v>
       </c>
       <c r="T11" t="n">
+        <v>485900</v>
+      </c>
+      <c r="U11" t="n">
         <v>485450</v>
-      </c>
-      <c r="U11" t="n">
-        <v>485000</v>
       </c>
       <c r="V11" t="n">
         <v>450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>944836.8199999999</v>
+        <v>948026.42</v>
       </c>
       <c r="P20" t="n">
         <v>3125692.73</v>
@@ -3192,7 +3192,7 @@
         <v>8815226.73</v>
       </c>
       <c r="S20" t="n">
-        <v>4831031.1</v>
+        <v>4831031.07</v>
       </c>
       <c r="T20" t="n">
         <v>4831031.1</v>
@@ -3201,7 +3201,7 @@
         <v>5689534</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="W20" t="n">
         <v>5690644</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>202693</v>
       </c>
       <c r="O27" t="n">
         <v>13158.64</v>
@@ -4166,10 +4166,10 @@
         <v>42067.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2308</v>
       </c>
       <c r="R27" t="n">
-        <v>382910.98</v>
+        <v>526820.98</v>
       </c>
       <c r="S27" t="n">
         <v>312903.94</v>
@@ -4178,13 +4178,13 @@
         <v>312903.94</v>
       </c>
       <c r="U27" t="n">
-        <v>340843.18</v>
+        <v>484753.18</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>460843</v>
+        <v>665844</v>
       </c>
       <c r="X27" t="n">
         <v>463151</v>
@@ -4196,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>463151</v>
+        <v>665844</v>
       </c>
       <c r="AB27" t="n">
         <v>5</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>489004.42</v>
+        <v>490620.47</v>
       </c>
       <c r="P29" t="n">
         <v>316170.82</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3193899.65</v>
+        <v>3194578.48</v>
       </c>
       <c r="P31" t="n">
         <v>800034.36</v>
@@ -4729,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>18625777.17</v>
+        <v>18626200.63</v>
       </c>
       <c r="S31" t="n">
         <v>16983877.06</v>
@@ -4738,25 +4738,25 @@
         <v>16990449.71</v>
       </c>
       <c r="U31" t="n">
-        <v>17825742.81</v>
+        <v>17826166.27</v>
       </c>
       <c r="V31" t="n">
         <v>6572.65</v>
       </c>
       <c r="W31" t="n">
-        <v>18159345</v>
+        <v>17954344</v>
       </c>
       <c r="X31" t="n">
         <v>18370086</v>
       </c>
       <c r="Y31" t="n">
-        <v>100741</v>
+        <v>103049</v>
       </c>
       <c r="Z31" t="n">
-        <v>110000</v>
+        <v>312693</v>
       </c>
       <c r="AA31" t="n">
-        <v>18260086</v>
+        <v>18057393</v>
       </c>
       <c r="AB31" t="n">
         <v>5</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -6251,22 +6251,22 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>3443.08</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>131526</v>
+      </c>
+      <c r="O42" t="n">
         <v>3115.08</v>
       </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3036.39</v>
-      </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>22671</v>
       </c>
       <c r="R42" t="n">
         <v>51525.12</v>
@@ -6284,7 +6284,7 @@
         <v>3936</v>
       </c>
       <c r="W42" t="n">
-        <v>77329</v>
+        <v>231526</v>
       </c>
       <c r="X42" t="n">
         <v>100000</v>
@@ -6296,7 +6296,7 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>100000</v>
+        <v>231526</v>
       </c>
       <c r="AB42" t="n">
         <v>5</v>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -6564,19 +6564,19 @@
         <v>422635.58</v>
       </c>
       <c r="W44" t="n">
-        <v>15006568.73</v>
+        <v>14852371.73</v>
       </c>
       <c r="X44" t="n">
         <v>21072104</v>
       </c>
       <c r="Y44" t="n">
-        <v>5330872</v>
+        <v>5353543</v>
       </c>
       <c r="Z44" t="n">
-        <v>2014895.27</v>
+        <v>2146421.27</v>
       </c>
       <c r="AA44" t="n">
-        <v>19151094.73</v>
+        <v>19019568.73</v>
       </c>
       <c r="AB44" t="n">
         <v>5</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -6689,16 +6689,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>435000</v>
+        <v>535000</v>
       </c>
       <c r="S45" t="n">
-        <v>435000</v>
+        <v>535000</v>
       </c>
       <c r="T45" t="n">
-        <v>435000</v>
+        <v>535000</v>
       </c>
       <c r="U45" t="n">
-        <v>435000</v>
+        <v>535000</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
         <v>50000</v>
       </c>
       <c r="O52" t="n">
-        <v>4583.34</v>
+        <v>6005.24</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -7669,16 +7669,16 @@
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>55000</v>
+        <v>90000</v>
       </c>
       <c r="S52" t="n">
-        <v>55000</v>
+        <v>90000</v>
       </c>
       <c r="T52" t="n">
-        <v>55000</v>
+        <v>90000</v>
       </c>
       <c r="U52" t="n">
-        <v>55000</v>
+        <v>90000</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -10886,10 +10886,10 @@
         <v>1124.65</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>30045</v>
       </c>
       <c r="R75" t="n">
-        <v>60292.66</v>
+        <v>76897.66</v>
       </c>
       <c r="S75" t="n">
         <v>58000</v>
@@ -10898,13 +10898,13 @@
         <v>58000</v>
       </c>
       <c r="U75" t="n">
-        <v>59168.01</v>
+        <v>75773.00999999999</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>74955</v>
+        <v>105000</v>
       </c>
       <c r="X75" t="n">
         <v>105000</v>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -11184,13 +11184,13 @@
         <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>848683</v>
+        <v>818638</v>
       </c>
       <c r="X77" t="n">
         <v>1314953</v>
       </c>
       <c r="Y77" t="n">
-        <v>376270</v>
+        <v>406315</v>
       </c>
       <c r="Z77" t="n">
         <v>90000</v>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -11300,7 +11300,7 @@
         <v>40000</v>
       </c>
       <c r="O78" t="n">
-        <v>953.49</v>
+        <v>1647.46</v>
       </c>
       <c r="P78" t="n">
         <v>450</v>
@@ -11309,16 +11309,16 @@
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>31720</v>
+        <v>50900</v>
       </c>
       <c r="S78" t="n">
-        <v>31270</v>
+        <v>50450</v>
       </c>
       <c r="T78" t="n">
-        <v>31720</v>
+        <v>50900</v>
       </c>
       <c r="U78" t="n">
-        <v>31270</v>
+        <v>50450</v>
       </c>
       <c r="V78" t="n">
         <v>450</v>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -13947,11 +13947,11 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -13960,7 +13960,7 @@
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -13969,25 +13969,25 @@
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>10919153.01</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>10919153.01</v>
+        <v>0</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
         <v>0</v>
@@ -13996,7 +13996,7 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
         <v>5</v>
@@ -14024,17 +14024,17 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Adrilles Jorge</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4318.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4318.33503900.00.1.500.7067</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14077,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -14091,7 +14091,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -14100,7 +14100,7 @@
         <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="P98" t="n">
         <v>0</v>
@@ -14109,25 +14109,25 @@
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>30000</v>
+        <v>10919153.01</v>
       </c>
       <c r="S98" t="n">
-        <v>30000</v>
+        <v>2861229.41</v>
       </c>
       <c r="T98" t="n">
-        <v>30000</v>
+        <v>2861229.41</v>
       </c>
       <c r="U98" t="n">
-        <v>30000</v>
+        <v>10919153.01</v>
       </c>
       <c r="V98" t="n">
         <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="X98" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="Y98" t="n">
         <v>0</v>
@@ -14136,7 +14136,7 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="AB98" t="n">
         <v>5</v>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH98" t="inlineStr">
@@ -14169,12 +14169,12 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4318.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4318.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14217,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -14249,25 +14249,25 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="X99" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="Y99" t="n">
         <v>0</v>
@@ -14276,7 +14276,7 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="AB99" t="n">
         <v>5</v>
@@ -14299,7 +14299,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH99" t="inlineStr">
@@ -14309,12 +14309,12 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4318.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4318.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -14347,17 +14347,17 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>33804100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -14404,19 +14404,19 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>8373</v>
+        <v>378632</v>
       </c>
       <c r="X100" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="Y100" t="n">
-        <v>2225</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="AB100" t="n">
         <v>5</v>
@@ -14424,12 +14424,12 @@
       <c r="AC100" t="inlineStr"/>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>CPLGBTI - Políticas</t>
+          <t>CPJ - Políticas</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>Taxa Rainbow</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH100" t="inlineStr">
@@ -14449,12 +14449,12 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4319.33804100.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4318.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -14497,17 +14497,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33804100</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -14544,19 +14544,19 @@
         <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>4000</v>
+        <v>8373</v>
       </c>
       <c r="X101" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2225</v>
       </c>
       <c r="Z101" t="n">
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="AB101" t="n">
         <v>5</v>
@@ -14574,27 +14574,27 @@
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>05 - Outras Fontes</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Taxa Rainbow</t>
         </is>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4319.33903900.05.1.703.0000</t>
+          <t>34.10.14.422.4024.4319.33804100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -14637,21 +14637,21 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3410465.43</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>3410465.43</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
         <v>0</v>
@@ -14669,34 +14669,34 @@
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>7383237.78</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>7383237.78</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>7383237.78</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>7383237.78</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>9813947</v>
+        <v>4000</v>
       </c>
       <c r="X102" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="Y102" t="n">
-        <v>2607835</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="AB102" t="n">
         <v>5</v>
@@ -14714,27 +14714,27 @@
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>05 - Outras Fontes</t>
         </is>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4319.33904800.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4319.33903900.05.1.703.0000</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -14767,17 +14767,17 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CPIPTD</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -14791,7 +14791,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>3410465.43</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -14800,7 +14800,7 @@
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>3410465.43</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
@@ -14809,34 +14809,34 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>7383237.78</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>7383237.78</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>7383237.78</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>7383237.78</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>0</v>
+        <v>9813947</v>
       </c>
       <c r="X103" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="Y103" t="n">
-        <v>56000</v>
+        <v>2607835</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="AB103" t="n">
         <v>5</v>
@@ -14844,12 +14844,12 @@
       <c r="AC103" t="inlineStr"/>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>Imigrantes</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>CPIPTD - Políticas</t>
+          <t>CPLGBTI - Políticas</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AH103" t="inlineStr">
@@ -14869,12 +14869,12 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4319.33904800.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -14927,7 +14927,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L104" t="n">
@@ -14967,16 +14967,16 @@
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>40000</v>
+        <v>56000</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="Z104" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="AB104" t="n">
         <v>5</v>
@@ -15004,17 +15004,17 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9005</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="L105" t="n">
@@ -15077,7 +15077,7 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -15104,19 +15104,19 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="Y105" t="n">
         <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AA105" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
         <v>5</v>
@@ -15144,17 +15144,17 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
+          <t>Recursos destinados ao Orçamento Cidadão</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9567</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9005</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="L106" t="n">
@@ -15284,17 +15284,17 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
         </is>
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9570</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9567</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="L107" t="n">
@@ -15357,7 +15357,7 @@
         <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -15384,7 +15384,7 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="X107" t="n">
         <v>0</v>
@@ -15396,7 +15396,7 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AB107" t="n">
         <v>5</v>
@@ -15424,17 +15424,17 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4324.33903900.00.1.500.9571</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9570</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -15467,12 +15467,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>CPIPTD</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -15487,7 +15487,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -15497,7 +15497,7 @@
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -15524,10 +15524,10 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="X108" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AB108" t="n">
         <v>5</v>
@@ -15544,12 +15544,12 @@
       <c r="AC108" t="inlineStr"/>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>Drogas</t>
+          <t>Imigrantes</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>CPD - Políticas</t>
+          <t>CPIPTD - Políticas</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -15564,17 +15564,17 @@
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
         </is>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4325.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4324.33903900.00.1.500.9571</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -15607,17 +15607,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3487177.25</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
@@ -15640,7 +15640,7 @@
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>3487177.25</v>
+        <v>0</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
@@ -15649,25 +15649,25 @@
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="U109" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="X109" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="Y109" t="n">
         <v>0</v>
@@ -15676,7 +15676,7 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="AB109" t="n">
         <v>5</v>
@@ -15684,12 +15684,12 @@
       <c r="AC109" t="inlineStr"/>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Drogas</t>
         </is>
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>CPLGBTI - Equipamentos</t>
+          <t>CPD - Políticas</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4326.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4325.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>3487177.25</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
@@ -15780,7 +15780,7 @@
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>3487177.25</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
@@ -15789,25 +15789,25 @@
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="S110" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="T110" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="U110" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="X110" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="Y110" t="n">
         <v>0</v>
@@ -15816,7 +15816,7 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="AB110" t="n">
         <v>5</v>
@@ -15839,7 +15839,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH110" t="inlineStr">
@@ -15849,12 +15849,12 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4326.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4326.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -15897,7 +15897,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -15911,7 +15911,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>254250.5</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -15920,34 +15920,34 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>204550.5</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>7843280.02</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>821264.08</v>
+        <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>821264.08</v>
+        <v>0</v>
       </c>
       <c r="U111" t="n">
-        <v>7793280.02</v>
+        <v>0</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="X111" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="Y111" t="n">
         <v>0</v>
@@ -15956,7 +15956,7 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="AB111" t="n">
         <v>5</v>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH111" t="inlineStr">
@@ -15989,12 +15989,12 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4326.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4326.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -16027,17 +16027,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -16051,7 +16051,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3046970.4</v>
+        <v>254250.5</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
@@ -16060,34 +16060,34 @@
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>3046970.4</v>
+        <v>204550.5</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>5238691</v>
+        <v>7843280.02</v>
       </c>
       <c r="S112" t="n">
-        <v>5238691</v>
+        <v>821264.08</v>
       </c>
       <c r="T112" t="n">
-        <v>8823589.4</v>
+        <v>821264.08</v>
       </c>
       <c r="U112" t="n">
-        <v>5238691</v>
+        <v>7793280.02</v>
       </c>
       <c r="V112" t="n">
-        <v>3584898.4</v>
+        <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="X112" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="Y112" t="n">
         <v>0</v>
@@ -16096,7 +16096,7 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="AB112" t="n">
         <v>5</v>
@@ -16104,12 +16104,12 @@
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Ouvidoria</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>ODH - Manutenção</t>
+          <t>CPLGBTI - Equipamentos</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4332.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4326.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>13052.54</v>
+        <v>5238691</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
@@ -16200,7 +16200,7 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>13052.54</v>
+        <v>3046970.4</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
@@ -16209,34 +16209,34 @@
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>346118.97</v>
+        <v>5238691</v>
       </c>
       <c r="S113" t="n">
-        <v>46118.97</v>
+        <v>5238691</v>
       </c>
       <c r="T113" t="n">
-        <v>46118.97</v>
+        <v>8823589.4</v>
       </c>
       <c r="U113" t="n">
-        <v>346118.97</v>
+        <v>5238691</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
+        <v>3584898.4</v>
       </c>
       <c r="W113" t="n">
-        <v>589556</v>
+        <v>5238691</v>
       </c>
       <c r="X113" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="Y113" t="n">
-        <v>278000</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="AB113" t="n">
         <v>5</v>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH113" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4332.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4332.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -16307,17 +16307,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -16331,7 +16331,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>13052.54</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
@@ -16340,7 +16340,7 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>13052.54</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
@@ -16349,34 +16349,34 @@
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>346118.97</v>
       </c>
       <c r="S114" t="n">
-        <v>0</v>
+        <v>46118.97</v>
       </c>
       <c r="T114" t="n">
-        <v>0</v>
+        <v>46118.97</v>
       </c>
       <c r="U114" t="n">
-        <v>0</v>
+        <v>346118.97</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>0</v>
+        <v>589556</v>
       </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>867556</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>278000</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>867556</v>
       </c>
       <c r="AB114" t="n">
         <v>5</v>
@@ -16384,12 +16384,12 @@
       <c r="AC114" t="inlineStr"/>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>Centro Público</t>
+          <t>Ouvidoria</t>
         </is>
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH - Manutenção</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -16399,7 +16399,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH114" t="inlineStr">
@@ -16409,12 +16409,12 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4333.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4332.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -16471,16 +16471,16 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>57410.34</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>135000</v>
       </c>
       <c r="O115" t="n">
-        <v>57410.34</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
@@ -16489,25 +16489,25 @@
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>321493</v>
+        <v>16605</v>
       </c>
       <c r="S115" t="n">
-        <v>202849.86</v>
+        <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>202849.86</v>
+        <v>0</v>
       </c>
       <c r="U115" t="n">
-        <v>321493</v>
+        <v>16605</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>321493</v>
+        <v>135000</v>
       </c>
       <c r="X115" t="n">
-        <v>321493</v>
+        <v>0</v>
       </c>
       <c r="Y115" t="n">
         <v>0</v>
@@ -16516,7 +16516,7 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>321493</v>
+        <v>135000</v>
       </c>
       <c r="AB115" t="n">
         <v>5</v>
@@ -16539,7 +16539,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH115" t="inlineStr">
@@ -16549,12 +16549,12 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4333.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4333.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -16611,43 +16611,43 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>57142.9</v>
+        <v>57410.34</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>190000</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>55924.58</v>
+        <v>57410.34</v>
       </c>
       <c r="P116" t="n">
-        <v>223266.91</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>634769.33</v>
+        <v>321493</v>
       </c>
       <c r="S116" t="n">
-        <v>283736.78</v>
+        <v>202849.86</v>
       </c>
       <c r="T116" t="n">
-        <v>363416.4</v>
+        <v>202849.86</v>
       </c>
       <c r="U116" t="n">
-        <v>411502.42</v>
+        <v>321493</v>
       </c>
       <c r="V116" t="n">
-        <v>79679.62</v>
+        <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>427085</v>
+        <v>321493</v>
       </c>
       <c r="X116" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="Y116" t="n">
         <v>0</v>
@@ -16656,7 +16656,7 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>427085</v>
+        <v>321493</v>
       </c>
       <c r="AB116" t="n">
         <v>5</v>
@@ -16679,7 +16679,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH116" t="inlineStr">
@@ -16689,12 +16689,12 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4333.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4333.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -16747,47 +16747,47 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>11293.18</v>
+        <v>57142.9</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>50000</v>
+        <v>190000</v>
       </c>
       <c r="O117" t="n">
-        <v>6998.62</v>
+        <v>55924.58</v>
       </c>
       <c r="P117" t="n">
-        <v>2250</v>
+        <v>223266.91</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>92250</v>
+        <v>634769.33</v>
       </c>
       <c r="S117" t="n">
-        <v>90000</v>
+        <v>283736.78</v>
       </c>
       <c r="T117" t="n">
-        <v>91800</v>
+        <v>363416.4</v>
       </c>
       <c r="U117" t="n">
-        <v>90000</v>
+        <v>411502.42</v>
       </c>
       <c r="V117" t="n">
-        <v>1800</v>
+        <v>79679.62</v>
       </c>
       <c r="W117" t="n">
-        <v>95670</v>
+        <v>427085</v>
       </c>
       <c r="X117" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="Y117" t="n">
         <v>0</v>
@@ -16796,7 +16796,7 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>95670</v>
+        <v>427085</v>
       </c>
       <c r="AB117" t="n">
         <v>5</v>
@@ -16824,17 +16824,17 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4333.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4024.4333.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -16867,17 +16867,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>CPEF</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -16887,47 +16887,47 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>11293.18</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>10791.68</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>92250</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>91800</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="V118" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="W118" t="n">
-        <v>50000</v>
+        <v>95670</v>
       </c>
       <c r="X118" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="Y118" t="n">
         <v>0</v>
@@ -16936,7 +16936,7 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>50000</v>
+        <v>95670</v>
       </c>
       <c r="AB118" t="n">
         <v>5</v>
@@ -16944,12 +16944,12 @@
       <c r="AC118" t="inlineStr"/>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>Egressos e Familiares</t>
+          <t>Centro Público</t>
         </is>
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>CPEF - Políticas</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -16959,22 +16959,22 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>34.10.14.422.4024.4335.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4333.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -17003,16 +17003,16 @@
         <v>422</v>
       </c>
       <c r="F119" t="n">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPEF</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -17031,52 +17031,52 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2414424.98</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2294560.33</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>2414424.98</v>
+        <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>393733.59</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>261863</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>7837448.92</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>7443715.32</v>
+        <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>7837448.91</v>
+        <v>0</v>
       </c>
       <c r="U119" t="n">
-        <v>7443715.33</v>
+        <v>0</v>
       </c>
       <c r="V119" t="n">
-        <v>393733.59</v>
+        <v>0</v>
       </c>
       <c r="W119" t="n">
-        <v>7443715.33</v>
+        <v>50000</v>
       </c>
       <c r="X119" t="n">
-        <v>5149155</v>
+        <v>50000</v>
       </c>
       <c r="Y119" t="n">
-        <v>261863</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>7443715.33</v>
+        <v>50000</v>
       </c>
       <c r="AB119" t="n">
         <v>5</v>
@@ -17084,12 +17084,12 @@
       <c r="AC119" t="inlineStr"/>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>Mulheres</t>
+          <t>Egressos e Familiares</t>
         </is>
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>CPM - Casa da Mulher Brasileira</t>
+          <t>CPEF - Políticas</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -17109,12 +17109,12 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4024.4335.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -17162,61 +17162,61 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2414424.98</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2294560.33</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>2414424.98</v>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>393733.59</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>261863</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>7837448.92</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>7443715.32</v>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>7837448.91</v>
       </c>
       <c r="U120" t="n">
-        <v>0</v>
+        <v>7443715.33</v>
       </c>
       <c r="V120" t="n">
-        <v>0</v>
+        <v>393733.59</v>
       </c>
       <c r="W120" t="n">
-        <v>0</v>
+        <v>7443715.33</v>
       </c>
       <c r="X120" t="n">
-        <v>2000</v>
+        <v>5149155</v>
       </c>
       <c r="Y120" t="n">
-        <v>2000</v>
+        <v>261863</v>
       </c>
       <c r="Z120" t="n">
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2000</v>
+        <v>7443715.33</v>
       </c>
       <c r="AB120" t="n">
         <v>5</v>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="AF120" t="inlineStr">
         <is>
-          <t>02 - Transferências Federais</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG120" t="inlineStr">
@@ -17244,17 +17244,17 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33503900.02.1.700.0000</t>
+          <t>34.10.14.422.4025.2053.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -17297,21 +17297,21 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>21384.72</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -17320,43 +17320,43 @@
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>21384.72</v>
+        <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>55391.15</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>203144.56</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>33311.56</v>
+        <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>33311.56</v>
+        <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>147753.41</v>
+        <v>0</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>150755</v>
+        <v>0</v>
       </c>
       <c r="X121" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="Y121" t="n">
-        <v>8077</v>
+        <v>2000</v>
       </c>
       <c r="Z121" t="n">
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="AB121" t="n">
         <v>5</v>
@@ -17374,27 +17374,27 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>02 - Transferências Federais</t>
         </is>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.33503900.02.1.700.0000</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -17437,7 +17437,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -17451,52 +17451,52 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>161974.24</v>
+        <v>21384.72</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>564000</v>
+        <v>166923</v>
       </c>
       <c r="O122" t="n">
-        <v>161974.24</v>
+        <v>21384.72</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>55391.15</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>8077</v>
       </c>
       <c r="R122" t="n">
-        <v>519437</v>
+        <v>203144.56</v>
       </c>
       <c r="S122" t="n">
-        <v>485922.72</v>
+        <v>33311.56</v>
       </c>
       <c r="T122" t="n">
-        <v>485922.72</v>
+        <v>33311.56</v>
       </c>
       <c r="U122" t="n">
-        <v>519437</v>
+        <v>147753.41</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>1083437</v>
+        <v>325755</v>
       </c>
       <c r="X122" t="n">
-        <v>547269</v>
+        <v>158832</v>
       </c>
       <c r="Y122" t="n">
-        <v>27832</v>
+        <v>8077</v>
       </c>
       <c r="Z122" t="n">
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1111269</v>
+        <v>325755</v>
       </c>
       <c r="AB122" t="n">
         <v>5</v>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH122" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -17591,52 +17591,52 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>808907.3100000001</v>
+        <v>161974.24</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>564000</v>
       </c>
       <c r="O123" t="n">
-        <v>642538.97</v>
+        <v>161974.24</v>
       </c>
       <c r="P123" t="n">
-        <v>2102872.47</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>5725169.27</v>
+        <v>519437</v>
       </c>
       <c r="S123" t="n">
-        <v>2711399.82</v>
+        <v>485922.72</v>
       </c>
       <c r="T123" t="n">
-        <v>2711719.82</v>
+        <v>485922.72</v>
       </c>
       <c r="U123" t="n">
-        <v>3622296.8</v>
+        <v>519437</v>
       </c>
       <c r="V123" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="W123" t="n">
-        <v>3914256.72</v>
+        <v>1083437</v>
       </c>
       <c r="X123" t="n">
-        <v>4953156</v>
+        <v>547269</v>
       </c>
       <c r="Y123" t="n">
-        <v>316899.28</v>
+        <v>27832</v>
       </c>
       <c r="Z123" t="n">
-        <v>722000</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>4231156</v>
+        <v>1111269</v>
       </c>
       <c r="AB123" t="n">
         <v>5</v>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH123" t="inlineStr">
@@ -17669,12 +17669,12 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -17727,56 +17727,56 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>22963.84</v>
+        <v>808907.3100000001</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>158000</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>22963.84</v>
+        <v>642538.97</v>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2102872.47</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>440533</v>
+        <v>5725169.27</v>
       </c>
       <c r="S124" t="n">
-        <v>440533</v>
+        <v>2711399.82</v>
       </c>
       <c r="T124" t="n">
-        <v>440533</v>
+        <v>2711719.82</v>
       </c>
       <c r="U124" t="n">
-        <v>440533</v>
+        <v>3622296.8</v>
       </c>
       <c r="V124" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="W124" t="n">
-        <v>440533</v>
+        <v>3739256.72</v>
       </c>
       <c r="X124" t="n">
-        <v>282533</v>
+        <v>4953156</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>324976.28</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>888923</v>
       </c>
       <c r="AA124" t="n">
-        <v>440533</v>
+        <v>4064233</v>
       </c>
       <c r="AB124" t="n">
         <v>5</v>
@@ -17804,17 +17804,17 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4025.2053.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -17862,25 +17862,25 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>22963.84</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>158000</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>22963.84</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
@@ -17889,25 +17889,25 @@
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>440533</v>
       </c>
       <c r="S125" t="n">
-        <v>0</v>
+        <v>440533</v>
       </c>
       <c r="T125" t="n">
-        <v>0</v>
+        <v>440533</v>
       </c>
       <c r="U125" t="n">
-        <v>0</v>
+        <v>440533</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>0</v>
+        <v>440533</v>
       </c>
       <c r="X125" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="Y125" t="n">
         <v>0</v>
@@ -17916,7 +17916,7 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>440533</v>
       </c>
       <c r="AB125" t="n">
         <v>5</v>
@@ -17934,7 +17934,7 @@
       </c>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>02 - Transferências Federais</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG125" t="inlineStr">
@@ -17944,17 +17944,17 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33903900.02.1.700.0000</t>
+          <t>34.10.14.422.4025.2053.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>33909300</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -18079,7 +18079,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>Indenizações e Restituições</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH126" t="inlineStr">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.33909300.02.1.700.0000</t>
+          <t>34.10.14.422.4025.2053.33903900.02.1.700.0000</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -18137,17 +18137,17 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>44905200</t>
+          <t>33909300</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -18187,16 +18187,16 @@
         <v>0</v>
       </c>
       <c r="X127" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
         <v>5</v>
@@ -18214,27 +18214,27 @@
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>02 - Transferências Federais</t>
         </is>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>Aquisição de Material Permanente</t>
+          <t>Indenizações e Restituições</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.44905200.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.33909300.02.1.700.0000</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44905200</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -18327,16 +18327,16 @@
         <v>0</v>
       </c>
       <c r="X128" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z128" t="n">
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB128" t="n">
         <v>5</v>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>CPM - Políticas</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -18359,22 +18359,22 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Aquisição de Material Permanente</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - André Santos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7007</t>
+          <t>34.10.14.422.4025.2053.44905200.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -18427,7 +18427,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -18437,7 +18437,7 @@
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -18464,7 +18464,7 @@
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="X129" t="n">
         <v>0</v>
@@ -18476,7 +18476,7 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
         <v>5</v>
@@ -18504,17 +18504,17 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Kenji Ito</t>
+          <t>Emendas Parlamentares - André Santos</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7007</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -18567,56 +18567,56 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>3132800</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="O130" t="n">
-        <v>3132800</v>
+        <v>0</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
-        <v>3984000</v>
+        <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>4763600</v>
+        <v>0</v>
       </c>
       <c r="U130" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>8578400</v>
+        <v>57000</v>
       </c>
       <c r="X130" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1421600</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>8705439.67</v>
+        <v>57000</v>
       </c>
       <c r="AB130" t="n">
         <v>5</v>
@@ -18639,22 +18639,22 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Kenji Ito</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -18707,11 +18707,11 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>19041664.7</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
         <v>0</v>
@@ -18720,34 +18720,34 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>16923298.94</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>1425517.51</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>23851875.51</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>21926109.23</v>
+        <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>22593123.43</v>
+        <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>22426358</v>
+        <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>667014.2</v>
+        <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>22426358</v>
+        <v>0</v>
       </c>
       <c r="X131" t="n">
-        <v>22426358</v>
+        <v>0</v>
       </c>
       <c r="Y131" t="n">
         <v>0</v>
@@ -18756,7 +18756,7 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>22426358</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
         <v>5</v>
@@ -18769,7 +18769,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -18784,17 +18784,17 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Lucas Pavanato</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7077</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -18837,7 +18837,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -18851,7 +18851,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>64653</v>
+        <v>3132800</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
@@ -18860,43 +18860,43 @@
         <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>64653</v>
+        <v>3132800</v>
       </c>
       <c r="P132" t="n">
-        <v>2075</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="R132" t="n">
-        <v>190072.94</v>
+        <v>8578400</v>
       </c>
       <c r="S132" t="n">
-        <v>141746.12</v>
+        <v>3984000</v>
       </c>
       <c r="T132" t="n">
-        <v>143540.12</v>
+        <v>4763600</v>
       </c>
       <c r="U132" t="n">
-        <v>187997.94</v>
+        <v>8578400</v>
       </c>
       <c r="V132" t="n">
-        <v>1794</v>
+        <v>779600</v>
       </c>
       <c r="W132" t="n">
-        <v>200000</v>
+        <v>8578400</v>
       </c>
       <c r="X132" t="n">
-        <v>200000</v>
+        <v>10000000</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="AA132" t="n">
-        <v>200000</v>
+        <v>8705439.67</v>
       </c>
       <c r="AB132" t="n">
         <v>5</v>
@@ -18909,7 +18909,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -18919,7 +18919,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>40338.4</v>
+        <v>19041664.7</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
@@ -19000,34 +19000,34 @@
         <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>33338.4</v>
+        <v>16923298.94</v>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1425517.51</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>95531.96000000001</v>
+        <v>23851875.51</v>
       </c>
       <c r="S133" t="n">
-        <v>95531.96000000001</v>
+        <v>21926109.23</v>
       </c>
       <c r="T133" t="n">
-        <v>95531.96000000001</v>
+        <v>22593123.43</v>
       </c>
       <c r="U133" t="n">
-        <v>95531.96000000001</v>
+        <v>22426358</v>
       </c>
       <c r="V133" t="n">
-        <v>0</v>
+        <v>667014.2</v>
       </c>
       <c r="W133" t="n">
-        <v>250000</v>
+        <v>22426358</v>
       </c>
       <c r="X133" t="n">
-        <v>250000</v>
+        <v>22426358</v>
       </c>
       <c r="Y133" t="n">
         <v>0</v>
@@ -19036,7 +19036,7 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>250000</v>
+        <v>22426358</v>
       </c>
       <c r="AB133" t="n">
         <v>5</v>
@@ -19059,7 +19059,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH133" t="inlineStr">
@@ -19069,12 +19069,12 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -19131,43 +19131,43 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>246715.46</v>
+        <v>64653</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>52998</v>
       </c>
       <c r="O134" t="n">
-        <v>246715.46</v>
+        <v>64653</v>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>7647.82</v>
       </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>2537927</v>
+        <v>206677.94</v>
       </c>
       <c r="S134" t="n">
-        <v>1074549.58</v>
+        <v>141746.12</v>
       </c>
       <c r="T134" t="n">
-        <v>1131764.02</v>
+        <v>143540.12</v>
       </c>
       <c r="U134" t="n">
-        <v>2537927</v>
+        <v>199030.12</v>
       </c>
       <c r="V134" t="n">
-        <v>57214.44</v>
+        <v>1794</v>
       </c>
       <c r="W134" t="n">
-        <v>2537927</v>
+        <v>252998</v>
       </c>
       <c r="X134" t="n">
-        <v>2537927</v>
+        <v>200000</v>
       </c>
       <c r="Y134" t="n">
         <v>0</v>
@@ -19176,7 +19176,7 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>2537927</v>
+        <v>252998</v>
       </c>
       <c r="AB134" t="n">
         <v>5</v>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH134" t="inlineStr">
@@ -19209,12 +19209,12 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -19271,7 +19271,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>929386.36</v>
+        <v>40338.4</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -19280,43 +19280,43 @@
         <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>876799.9</v>
+        <v>40338.4</v>
       </c>
       <c r="P135" t="n">
-        <v>743505.8100000001</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>3802648.2</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="S135" t="n">
-        <v>2409038.89</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="T135" t="n">
-        <v>2502957.88</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="U135" t="n">
-        <v>3059142.39</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="V135" t="n">
-        <v>93918.99000000001</v>
+        <v>0</v>
       </c>
       <c r="W135" t="n">
-        <v>4690049</v>
+        <v>250000</v>
       </c>
       <c r="X135" t="n">
-        <v>4806049</v>
+        <v>250000</v>
       </c>
       <c r="Y135" t="n">
         <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>116000</v>
+        <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>4690049</v>
+        <v>250000</v>
       </c>
       <c r="AB135" t="n">
         <v>5</v>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH135" t="inlineStr">
@@ -19349,12 +19349,12 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -19407,11 +19407,11 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>368.19</v>
+        <v>246715.46</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
@@ -19420,7 +19420,7 @@
         <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>312.26</v>
+        <v>246715.46</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -19429,25 +19429,25 @@
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>80100</v>
+        <v>2537927</v>
       </c>
       <c r="S136" t="n">
-        <v>73100</v>
+        <v>1074549.58</v>
       </c>
       <c r="T136" t="n">
-        <v>80100</v>
+        <v>1131764.02</v>
       </c>
       <c r="U136" t="n">
-        <v>80100</v>
+        <v>2537927</v>
       </c>
       <c r="V136" t="n">
-        <v>7000</v>
+        <v>57214.44</v>
       </c>
       <c r="W136" t="n">
-        <v>139282</v>
+        <v>2537927</v>
       </c>
       <c r="X136" t="n">
-        <v>139282</v>
+        <v>2537927</v>
       </c>
       <c r="Y136" t="n">
         <v>0</v>
@@ -19456,7 +19456,7 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>139282</v>
+        <v>2537927</v>
       </c>
       <c r="AB136" t="n">
         <v>5</v>
@@ -19479,22 +19479,22 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -19551,7 +19551,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>5903.55</v>
+        <v>929386.36</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -19560,43 +19560,43 @@
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>5903.55</v>
+        <v>876799.9</v>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>743505.8100000001</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>19678.5</v>
+        <v>3802648.2</v>
       </c>
       <c r="S137" t="n">
-        <v>19678.5</v>
+        <v>2409038.89</v>
       </c>
       <c r="T137" t="n">
-        <v>19678.5</v>
+        <v>2502957.88</v>
       </c>
       <c r="U137" t="n">
-        <v>19678.5</v>
+        <v>3059142.39</v>
       </c>
       <c r="V137" t="n">
-        <v>0</v>
+        <v>93918.99000000001</v>
       </c>
       <c r="W137" t="n">
-        <v>49000</v>
+        <v>4104655</v>
       </c>
       <c r="X137" t="n">
-        <v>49000</v>
+        <v>4806049</v>
       </c>
       <c r="Y137" t="n">
-        <v>0</v>
+        <v>63262</v>
       </c>
       <c r="Z137" t="n">
-        <v>0</v>
+        <v>638132</v>
       </c>
       <c r="AA137" t="n">
-        <v>49000</v>
+        <v>4167917</v>
       </c>
       <c r="AB137" t="n">
         <v>5</v>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH137" t="inlineStr">
@@ -19629,12 +19629,12 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -19667,17 +19667,17 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -19687,11 +19687,11 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>368.19</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -19700,43 +19700,43 @@
         <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>312.26</v>
       </c>
       <c r="P138" t="n">
         <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>80100</v>
       </c>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>73100</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>80100</v>
       </c>
       <c r="U138" t="n">
-        <v>0</v>
+        <v>80100</v>
       </c>
       <c r="V138" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="W138" t="n">
-        <v>0</v>
+        <v>139282</v>
       </c>
       <c r="X138" t="n">
-        <v>110000</v>
+        <v>139282</v>
       </c>
       <c r="Y138" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="Z138" t="n">
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>110000</v>
+        <v>139282</v>
       </c>
       <c r="AB138" t="n">
         <v>5</v>
@@ -19744,12 +19744,12 @@
       <c r="AC138" t="inlineStr"/>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -19759,22 +19759,22 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -19807,17 +19807,17 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -19831,7 +19831,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>5903.55</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -19840,43 +19840,43 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>5903.55</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S139" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U139" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="X139" t="n">
-        <v>100000</v>
+        <v>49000</v>
       </c>
       <c r="Y139" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="n">
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>100000</v>
+        <v>49000</v>
       </c>
       <c r="AB139" t="n">
         <v>5</v>
@@ -19884,12 +19884,12 @@
       <c r="AC139" t="inlineStr"/>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -19899,7 +19899,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AH139" t="inlineStr">
@@ -19909,12 +19909,12 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -19947,7 +19947,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -19986,7 +19986,7 @@
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>75000</v>
+        <v>220000</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
@@ -20007,16 +20007,16 @@
         <v>0</v>
       </c>
       <c r="X140" t="n">
-        <v>75000</v>
+        <v>110000</v>
       </c>
       <c r="Y140" t="n">
-        <v>75000</v>
+        <v>330000</v>
       </c>
       <c r="Z140" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="AB140" t="n">
         <v>5</v>
@@ -20029,7 +20029,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
+          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -20049,12 +20049,12 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -20083,21 +20083,21 @@
         <v>422</v>
       </c>
       <c r="F141" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -20126,7 +20126,7 @@
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
@@ -20144,19 +20144,19 @@
         <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="X141" t="n">
-        <v>11949</v>
+        <v>100000</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="Z141" t="n">
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>11949</v>
+        <v>100000</v>
       </c>
       <c r="AB141" t="n">
         <v>5</v>
@@ -20164,12 +20164,12 @@
       <c r="AC141" t="inlineStr"/>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>CPIR - Políticas</t>
+          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH141" t="inlineStr">
@@ -20189,12 +20189,12 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -20223,16 +20223,16 @@
         <v>422</v>
       </c>
       <c r="F142" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -20251,7 +20251,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>3595409.86</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -20260,43 +20260,43 @@
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>3595409.86</v>
+        <v>0</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>127000</v>
+        <v>75000</v>
       </c>
       <c r="R142" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>3596273</v>
+        <v>0</v>
       </c>
       <c r="X142" t="n">
-        <v>6455492</v>
+        <v>75000</v>
       </c>
       <c r="Y142" t="n">
-        <v>2986219</v>
+        <v>75000</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA142" t="n">
-        <v>6455492</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
         <v>5</v>
@@ -20304,12 +20304,12 @@
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -20329,12 +20329,12 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -20424,19 +20424,19 @@
         <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>5374</v>
+        <v>11949</v>
       </c>
       <c r="X143" t="n">
-        <v>10000</v>
+        <v>11949</v>
       </c>
       <c r="Y143" t="n">
-        <v>4626</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>10000</v>
+        <v>11949</v>
       </c>
       <c r="AB143" t="n">
         <v>5</v>
@@ -20449,7 +20449,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -20459,7 +20459,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH143" t="inlineStr">
@@ -20469,12 +20469,12 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -20517,7 +20517,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -20531,7 +20531,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>3595409.86</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -20540,43 +20540,43 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>3595409.86</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="S144" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="T144" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="U144" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
       </c>
       <c r="W144" t="n">
-        <v>80612</v>
+        <v>3596273</v>
       </c>
       <c r="X144" t="n">
-        <v>150000</v>
+        <v>6455492</v>
       </c>
       <c r="Y144" t="n">
-        <v>69388</v>
+        <v>2986219</v>
       </c>
       <c r="Z144" t="n">
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>150000</v>
+        <v>6455492</v>
       </c>
       <c r="AB144" t="n">
         <v>5</v>
@@ -20599,7 +20599,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH144" t="inlineStr">
@@ -20609,12 +20609,12 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -20671,7 +20671,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>112772.08</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -20680,43 +20680,43 @@
         <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>73756.84</v>
+        <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>551.08</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>5040463.02</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>570925.76</v>
+        <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>570925.76</v>
+        <v>0</v>
       </c>
       <c r="U145" t="n">
-        <v>5039911.94</v>
+        <v>0</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>5870981</v>
+        <v>5374</v>
       </c>
       <c r="X145" t="n">
-        <v>10925362</v>
+        <v>10000</v>
       </c>
       <c r="Y145" t="n">
-        <v>5054381</v>
+        <v>4626</v>
       </c>
       <c r="Z145" t="n">
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>10925362</v>
+        <v>10000</v>
       </c>
       <c r="AB145" t="n">
         <v>5</v>
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AH145" t="inlineStr">
@@ -20749,12 +20749,12 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -20807,11 +20807,11 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>76.61</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -20823,40 +20823,40 @@
         <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>925</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="U146" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>1000</v>
+        <v>80612</v>
       </c>
       <c r="X146" t="n">
-        <v>1000</v>
+        <v>150000</v>
       </c>
       <c r="Y146" t="n">
-        <v>0</v>
+        <v>69388</v>
       </c>
       <c r="Z146" t="n">
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1000</v>
+        <v>150000</v>
       </c>
       <c r="AB146" t="n">
         <v>5</v>
@@ -20879,22 +20879,22 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -20927,17 +20927,17 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -20951,7 +20951,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>112772.08</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -20960,43 +20960,43 @@
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>73756.84</v>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>551.08</v>
       </c>
       <c r="Q147" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>5040463.02</v>
       </c>
       <c r="S147" t="n">
-        <v>0</v>
+        <v>570925.76</v>
       </c>
       <c r="T147" t="n">
-        <v>0</v>
+        <v>570925.76</v>
       </c>
       <c r="U147" t="n">
-        <v>0</v>
+        <v>5039911.94</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>0</v>
+        <v>5870981</v>
       </c>
       <c r="X147" t="n">
-        <v>75000</v>
+        <v>10925362</v>
       </c>
       <c r="Y147" t="n">
-        <v>75000</v>
+        <v>5054381</v>
       </c>
       <c r="Z147" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>10925362</v>
       </c>
       <c r="AB147" t="n">
         <v>5</v>
@@ -21004,12 +21004,12 @@
       <c r="AC147" t="inlineStr"/>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -21019,7 +21019,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH147" t="inlineStr">
@@ -21029,12 +21029,12 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -21060,24 +21060,24 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F148" t="n">
         <v>4026</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -21087,11 +21087,11 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>76.61</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -21103,40 +21103,40 @@
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>11400</v>
+        <v>925</v>
       </c>
       <c r="Q148" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>21600</v>
+        <v>1900</v>
       </c>
       <c r="S148" t="n">
-        <v>9600</v>
+        <v>975</v>
       </c>
       <c r="T148" t="n">
-        <v>9600</v>
+        <v>975</v>
       </c>
       <c r="U148" t="n">
-        <v>10200</v>
+        <v>975</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>22143</v>
+        <v>1000</v>
       </c>
       <c r="X148" t="n">
-        <v>46881</v>
+        <v>1000</v>
       </c>
       <c r="Y148" t="n">
-        <v>39738</v>
+        <v>0</v>
       </c>
       <c r="Z148" t="n">
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>46881</v>
+        <v>1000</v>
       </c>
       <c r="AB148" t="n">
         <v>5</v>
@@ -21144,12 +21144,12 @@
       <c r="AC148" t="inlineStr"/>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>COPIND - Políticas</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -21159,22 +21159,22 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -21200,24 +21200,24 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F149" t="n">
         <v>4026</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -21243,13 +21243,13 @@
         <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>19140.97</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="R149" t="n">
-        <v>52809.97</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -21258,25 +21258,25 @@
         <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="X149" t="n">
-        <v>220966</v>
+        <v>75000</v>
       </c>
       <c r="Y149" t="n">
-        <v>187297</v>
+        <v>75000</v>
       </c>
       <c r="Z149" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA149" t="n">
-        <v>220966</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
         <v>5</v>
@@ -21284,12 +21284,12 @@
       <c r="AC149" t="inlineStr"/>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>COPIND - Políticas</t>
+          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH149" t="inlineStr">
@@ -21309,12 +21309,12 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -21347,17 +21347,17 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -21383,40 +21383,40 @@
         <v>0</v>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="Q150" t="n">
-        <v>127873.65</v>
+        <v>15000</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="S150" t="n">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="T150" t="n">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="U150" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>0</v>
+        <v>22143</v>
       </c>
       <c r="X150" t="n">
-        <v>100000</v>
+        <v>46881</v>
       </c>
       <c r="Y150" t="n">
-        <v>155747.3</v>
+        <v>39738</v>
       </c>
       <c r="Z150" t="n">
-        <v>72126.35000000001</v>
+        <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>27873.65</v>
+        <v>46881</v>
       </c>
       <c r="AB150" t="n">
         <v>5</v>
@@ -21424,12 +21424,12 @@
       <c r="AC150" t="inlineStr"/>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH150" t="inlineStr">
@@ -21449,12 +21449,12 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -21466,12 +21466,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21480,24 +21480,24 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F151" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -21507,56 +21507,56 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>19140.97</v>
       </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>150000</v>
+        <v>52809.97</v>
       </c>
       <c r="S151" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U151" t="n">
-        <v>150000</v>
+        <v>33669</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>150000</v>
+        <v>33669</v>
       </c>
       <c r="X151" t="n">
-        <v>0</v>
+        <v>220966</v>
       </c>
       <c r="Y151" t="n">
-        <v>0</v>
+        <v>187297</v>
       </c>
       <c r="Z151" t="n">
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>150000</v>
+        <v>220966</v>
       </c>
       <c r="AB151" t="n">
         <v>5</v>
@@ -21564,12 +21564,12 @@
       <c r="AC151" t="inlineStr"/>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -21579,22 +21579,22 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
+          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -21606,12 +21606,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -21620,24 +21620,24 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F152" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -21666,7 +21666,7 @@
         <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>127873.65</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
@@ -21687,16 +21687,16 @@
         <v>0</v>
       </c>
       <c r="X152" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="Y152" t="n">
-        <v>589773</v>
+        <v>155747.3</v>
       </c>
       <c r="Z152" t="n">
-        <v>0</v>
+        <v>72126.35000000001</v>
       </c>
       <c r="AA152" t="n">
-        <v>589773</v>
+        <v>27873.65</v>
       </c>
       <c r="AB152" t="n">
         <v>5</v>
@@ -21704,12 +21704,12 @@
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
@@ -21729,50 +21729,50 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F153" t="n">
         <v>4010</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -21787,20 +21787,20 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>18190190.37</v>
+        <v>150000</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O153" t="n">
-        <v>12940208.36</v>
+        <v>150000</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
@@ -21809,25 +21809,25 @@
         <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>40835555</v>
+        <v>150000</v>
       </c>
       <c r="S153" t="n">
-        <v>40835555</v>
+        <v>150000</v>
       </c>
       <c r="T153" t="n">
-        <v>40835555</v>
+        <v>150000</v>
       </c>
       <c r="U153" t="n">
-        <v>40835555</v>
+        <v>150000</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>40835555</v>
+        <v>150000</v>
       </c>
       <c r="X153" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="Y153" t="n">
         <v>0</v>
@@ -21836,7 +21836,7 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>40835555</v>
+        <v>150000</v>
       </c>
       <c r="AB153" t="n">
         <v>5</v>
@@ -21849,7 +21849,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -21864,60 +21864,60 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F154" t="n">
         <v>4010</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -21964,19 +21964,19 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>600437</v>
+        <v>0</v>
       </c>
       <c r="X154" t="n">
-        <v>16896102</v>
+        <v>589773</v>
       </c>
       <c r="Y154" t="n">
-        <v>16295665</v>
+        <v>589773</v>
       </c>
       <c r="Z154" t="n">
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>16896102</v>
+        <v>589773</v>
       </c>
       <c r="AB154" t="n">
         <v>5</v>
@@ -21989,7 +21989,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -21999,7 +21999,7 @@
       </c>
       <c r="AG154" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH154" t="inlineStr">
@@ -22009,12 +22009,12 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -22036,28 +22036,28 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F155" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -22071,7 +22071,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>18190190.37</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
@@ -22080,7 +22080,7 @@
         <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>0</v>
+        <v>12940208.36</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
@@ -22089,25 +22089,25 @@
         <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>40835555</v>
       </c>
       <c r="S155" t="n">
-        <v>0</v>
+        <v>40835555</v>
       </c>
       <c r="T155" t="n">
-        <v>0</v>
+        <v>40835555</v>
       </c>
       <c r="U155" t="n">
-        <v>0</v>
+        <v>40835555</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>1000</v>
+        <v>40835555</v>
       </c>
       <c r="X155" t="n">
-        <v>1000</v>
+        <v>40835555</v>
       </c>
       <c r="Y155" t="n">
         <v>0</v>
@@ -22116,7 +22116,7 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1000</v>
+        <v>40835555</v>
       </c>
       <c r="AB155" t="n">
         <v>5</v>
@@ -22129,7 +22129,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -22139,7 +22139,7 @@
       </c>
       <c r="AG155" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH155" t="inlineStr">
@@ -22149,12 +22149,12 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -22176,28 +22176,28 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F156" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>44906100</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -22217,7 +22217,7 @@
         <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -22229,7 +22229,7 @@
         <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -22238,25 +22238,25 @@
         <v>0</v>
       </c>
       <c r="U156" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>361510</v>
+        <v>600437</v>
       </c>
       <c r="X156" t="n">
-        <v>0</v>
+        <v>16896102</v>
       </c>
       <c r="Y156" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Z156" t="n">
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>361510</v>
+        <v>16896102</v>
       </c>
       <c r="AB156" t="n">
         <v>5</v>
@@ -22269,7 +22269,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -22279,7 +22279,7 @@
       </c>
       <c r="AG156" t="inlineStr">
         <is>
-          <t>Aquisição de Imóveis</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AH156" t="inlineStr">
@@ -22289,12 +22289,12 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -22320,14 +22320,14 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F157" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -22337,7 +22337,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -22351,7 +22351,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>60017672.37</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
@@ -22360,43 +22360,43 @@
         <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>59869982.53</v>
+        <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>21043600.09</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
         <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>160562812.26</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>135266690.45</v>
+        <v>0</v>
       </c>
       <c r="T157" t="n">
-        <v>140706402.84</v>
+        <v>0</v>
       </c>
       <c r="U157" t="n">
-        <v>139519212.17</v>
+        <v>0</v>
       </c>
       <c r="V157" t="n">
-        <v>5439712.39</v>
+        <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>165715582</v>
+        <v>1000</v>
       </c>
       <c r="X157" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="Y157" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Z157" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>171451529</v>
+        <v>1000</v>
       </c>
       <c r="AB157" t="n">
         <v>5</v>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -22419,7 +22419,7 @@
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr">
@@ -22429,12 +22429,12 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
+          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -22460,14 +22460,14 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F158" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -22477,17 +22477,17 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>44906100</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -22497,7 +22497,7 @@
         <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -22509,7 +22509,7 @@
         <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -22518,16 +22518,16 @@
         <v>0</v>
       </c>
       <c r="U158" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>2000</v>
+        <v>361510</v>
       </c>
       <c r="X158" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y158" t="n">
         <v>0</v>
@@ -22536,7 +22536,7 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>2000</v>
+        <v>361510</v>
       </c>
       <c r="AB158" t="n">
         <v>5</v>
@@ -22549,32 +22549,32 @@
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
         <is>
-          <t>05 - Outras Fontes</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG158" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Aquisição de Imóveis</t>
         </is>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
+          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -22617,21 +22617,21 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>60048172.37</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -22640,43 +22640,43 @@
         <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>0</v>
+        <v>59869982.53</v>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>21043600.09</v>
       </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>160562812.27</v>
       </c>
       <c r="S159" t="n">
-        <v>0</v>
+        <v>135266690.46</v>
       </c>
       <c r="T159" t="n">
-        <v>0</v>
+        <v>140706402.85</v>
       </c>
       <c r="U159" t="n">
-        <v>0</v>
+        <v>139519212.18</v>
       </c>
       <c r="V159" t="n">
-        <v>0</v>
+        <v>5439712.39</v>
       </c>
       <c r="W159" t="n">
-        <v>11298</v>
+        <v>165715582</v>
       </c>
       <c r="X159" t="n">
-        <v>11298</v>
+        <v>171813039</v>
       </c>
       <c r="Y159" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Z159" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="AA159" t="n">
-        <v>11298</v>
+        <v>171451529</v>
       </c>
       <c r="AB159" t="n">
         <v>5</v>
@@ -22694,27 +22694,27 @@
       </c>
       <c r="AF159" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG159" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
+          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -22757,21 +22757,21 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>31386458.91</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
@@ -22780,43 +22780,43 @@
         <v>0</v>
       </c>
       <c r="O160" t="n">
-        <v>29380182.6</v>
+        <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>60670522</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>197559544</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>107626518.4</v>
+        <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>107626518.4</v>
+        <v>0</v>
       </c>
       <c r="U160" t="n">
-        <v>136889022</v>
+        <v>0</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>136889022</v>
+        <v>2000</v>
       </c>
       <c r="X160" t="n">
-        <v>141616875</v>
+        <v>2000</v>
       </c>
       <c r="Y160" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Z160" t="n">
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>141616875</v>
+        <v>2000</v>
       </c>
       <c r="AB160" t="n">
         <v>5</v>
@@ -22834,27 +22834,27 @@
       </c>
       <c r="AF160" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>05 - Outras Fontes</t>
         </is>
       </c>
       <c r="AG160" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
         </is>
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -22897,21 +22897,21 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>24794007.34</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
         <v>0</v>
@@ -22920,43 +22920,43 @@
         <v>0</v>
       </c>
       <c r="O161" t="n">
-        <v>24014598.76</v>
+        <v>0</v>
       </c>
       <c r="P161" t="n">
-        <v>49898263.91</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>129341289.91</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>79232487.98999999</v>
+        <v>0</v>
       </c>
       <c r="T161" t="n">
-        <v>79676487.98999999</v>
+        <v>0</v>
       </c>
       <c r="U161" t="n">
-        <v>79443026</v>
+        <v>0</v>
       </c>
       <c r="V161" t="n">
-        <v>444000</v>
+        <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>79443026</v>
+        <v>11298</v>
       </c>
       <c r="X161" t="n">
-        <v>83642123</v>
+        <v>11298</v>
       </c>
       <c r="Y161" t="n">
-        <v>2792377</v>
+        <v>0</v>
       </c>
       <c r="Z161" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>82235403</v>
+        <v>11298</v>
       </c>
       <c r="AB161" t="n">
         <v>5</v>
@@ -22974,27 +22974,27 @@
       </c>
       <c r="AF161" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
         </is>
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -23037,21 +23037,21 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>31386458.91</v>
       </c>
       <c r="M162" t="n">
         <v>0</v>
@@ -23060,43 +23060,43 @@
         <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>0</v>
+        <v>29380182.6</v>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>60670522</v>
       </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>197559544</v>
       </c>
       <c r="S162" t="n">
-        <v>0</v>
+        <v>107626518.4</v>
       </c>
       <c r="T162" t="n">
-        <v>0</v>
+        <v>107626518.4</v>
       </c>
       <c r="U162" t="n">
-        <v>0</v>
+        <v>136889022</v>
       </c>
       <c r="V162" t="n">
         <v>0</v>
       </c>
       <c r="W162" t="n">
-        <v>2000</v>
+        <v>136889022</v>
       </c>
       <c r="X162" t="n">
-        <v>2000</v>
+        <v>141616875</v>
       </c>
       <c r="Y162" t="n">
-        <v>0</v>
+        <v>4727853</v>
       </c>
       <c r="Z162" t="n">
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>2000</v>
+        <v>141616875</v>
       </c>
       <c r="AB162" t="n">
         <v>5</v>
@@ -23114,27 +23114,27 @@
       </c>
       <c r="AF162" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
+          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -23177,7 +23177,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>33913900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -23191,52 +23191,52 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>336000</v>
+        <v>24794007.34</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
       </c>
       <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>24104598.76</v>
+      </c>
+      <c r="P163" t="n">
+        <v>49898263.91</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>129341289.91</v>
+      </c>
+      <c r="S163" t="n">
+        <v>79232487.98999999</v>
+      </c>
+      <c r="T163" t="n">
+        <v>79676487.98999999</v>
+      </c>
+      <c r="U163" t="n">
+        <v>79443026</v>
+      </c>
+      <c r="V163" t="n">
+        <v>444000</v>
+      </c>
+      <c r="W163" t="n">
+        <v>79443026</v>
+      </c>
+      <c r="X163" t="n">
+        <v>83642123</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>2792377</v>
+      </c>
+      <c r="Z163" t="n">
         <v>1406720</v>
       </c>
-      <c r="O163" t="n">
-        <v>336000</v>
-      </c>
-      <c r="P163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
-      <c r="R163" t="n">
-        <v>1406720</v>
-      </c>
-      <c r="S163" t="n">
-        <v>1406720</v>
-      </c>
-      <c r="T163" t="n">
-        <v>1406720</v>
-      </c>
-      <c r="U163" t="n">
-        <v>1406720</v>
-      </c>
-      <c r="V163" t="n">
-        <v>0</v>
-      </c>
-      <c r="W163" t="n">
-        <v>1406720</v>
-      </c>
-      <c r="X163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z163" t="n">
-        <v>0</v>
-      </c>
       <c r="AA163" t="n">
-        <v>1406720</v>
+        <v>82235403</v>
       </c>
       <c r="AB163" t="n">
         <v>5</v>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Transferência entre Órgãos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH163" t="inlineStr">
@@ -23269,24 +23269,24 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -23300,34 +23300,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F164" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="L164" t="n">
@@ -23364,10 +23364,10 @@
         <v>0</v>
       </c>
       <c r="W164" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="X164" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="Y164" t="n">
         <v>0</v>
@@ -23376,7 +23376,7 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="AB164" t="n">
         <v>5</v>
@@ -23384,49 +23384,49 @@
       <c r="AC164" t="inlineStr"/>
       <c r="AD164" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
         </is>
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -23440,24 +23440,24 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F165" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33913900</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -23471,16 +23471,16 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>336000</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="O165" t="n">
-        <v>0</v>
+        <v>336000</v>
       </c>
       <c r="P165" t="n">
         <v>0</v>
@@ -23489,25 +23489,25 @@
         <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="S165" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="T165" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="U165" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
       </c>
       <c r="W165" t="n">
-        <v>6245</v>
+        <v>1406720</v>
       </c>
       <c r="X165" t="n">
-        <v>6245</v>
+        <v>0</v>
       </c>
       <c r="Y165" t="n">
         <v>0</v>
@@ -23516,7 +23516,7 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>6245</v>
+        <v>1406720</v>
       </c>
       <c r="AB165" t="n">
         <v>5</v>
@@ -23524,12 +23524,12 @@
       <c r="AC165" t="inlineStr"/>
       <c r="AD165" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Transferência entre Órgãos</t>
         </is>
       </c>
       <c r="AH165" t="inlineStr">
@@ -23549,12 +23549,12 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -23580,24 +23580,24 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F166" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>DTIC</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -23644,10 +23644,10 @@
         <v>0</v>
       </c>
       <c r="W166" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="X166" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="Y166" t="n">
         <v>0</v>
@@ -23656,7 +23656,7 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="AB166" t="n">
         <v>5</v>
@@ -23664,12 +23664,12 @@
       <c r="AC166" t="inlineStr"/>
       <c r="AD166" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>DTIC - Desenvolvimento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -23679,7 +23679,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH166" t="inlineStr">
@@ -23689,12 +23689,12 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
+          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -23720,24 +23720,24 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F167" t="n">
-        <v>4019</v>
+        <v>4004</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -23747,7 +23747,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L167" t="n">
@@ -23784,10 +23784,10 @@
         <v>0</v>
       </c>
       <c r="W167" t="n">
-        <v>0</v>
+        <v>6245</v>
       </c>
       <c r="X167" t="n">
-        <v>0</v>
+        <v>6245</v>
       </c>
       <c r="Y167" t="n">
         <v>0</v>
@@ -23796,7 +23796,7 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>6245</v>
       </c>
       <c r="AB167" t="n">
         <v>5</v>
@@ -23804,12 +23804,12 @@
       <c r="AC167" t="inlineStr"/>
       <c r="AD167" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -23819,22 +23819,22 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>05/05/2026 07:59:39</t>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>
@@ -23860,38 +23860,38 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F168" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>26316455.82</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
@@ -23900,34 +23900,34 @@
         <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>24479179.14</v>
+        <v>0</v>
       </c>
       <c r="P168" t="n">
-        <v>3158618.88</v>
+        <v>0</v>
       </c>
       <c r="Q168" t="n">
         <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>41074441.37</v>
+        <v>0</v>
       </c>
       <c r="S168" t="n">
-        <v>32622739.07</v>
+        <v>0</v>
       </c>
       <c r="T168" t="n">
-        <v>34235503.17</v>
+        <v>0</v>
       </c>
       <c r="U168" t="n">
-        <v>37915822.49</v>
+        <v>0</v>
       </c>
       <c r="V168" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="W168" t="n">
-        <v>61292510</v>
+        <v>1000</v>
       </c>
       <c r="X168" t="n">
-        <v>61292510</v>
+        <v>1000</v>
       </c>
       <c r="Y168" t="n">
         <v>0</v>
@@ -23936,7 +23936,7 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>61292510</v>
+        <v>1000</v>
       </c>
       <c r="AB168" t="n">
         <v>5</v>
@@ -23944,37 +23944,317 @@
       <c r="AC168" t="inlineStr"/>
       <c r="AD168" t="inlineStr">
         <is>
+          <t>Tecnologia</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>DTIC - Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>06/05/2026 08:16:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>422</v>
+      </c>
+      <c r="F169" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>0004</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" t="n">
+        <v>0</v>
+      </c>
+      <c r="X169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr">
+        <is>
           <t>Criança e Adolescente</t>
         </is>
       </c>
-      <c r="AE168" t="inlineStr">
+      <c r="AE169" t="inlineStr">
         <is>
           <t>FUMCAD</t>
         </is>
       </c>
-      <c r="AF168" t="inlineStr">
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>06/05/2026 08:16:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>422</v>
+      </c>
+      <c r="F170" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>26512660.49</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>24479179.14</v>
+      </c>
+      <c r="P170" t="n">
+        <v>3399155.21</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
+        <v>41074441.37</v>
+      </c>
+      <c r="S170" t="n">
+        <v>33060265.85</v>
+      </c>
+      <c r="T170" t="n">
+        <v>34673029.95</v>
+      </c>
+      <c r="U170" t="n">
+        <v>37675286.16</v>
+      </c>
+      <c r="V170" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="W170" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X170" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC170" t="inlineStr"/>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
         <is>
           <t>08 - Recusos Vinculados</t>
         </is>
       </c>
-      <c r="AG168" t="inlineStr">
+      <c r="AG170" t="inlineStr">
         <is>
           <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
-      <c r="AH168" t="inlineStr">
+      <c r="AH170" t="inlineStr">
         <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AI168" t="inlineStr">
+      <c r="AI170" t="inlineStr">
         <is>
           <t>90.10.14.422.4019.6160.33503900.08.1.759.0958</t>
         </is>
       </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>05/05/2026 07:59:39</t>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>06/05/2026 08:16:35</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>334134</v>
       </c>
       <c r="O7" t="n">
-        <v>8220.799999999999</v>
+        <v>11982.8</v>
       </c>
       <c r="P7" t="n">
         <v>96530.67999999999</v>
@@ -1369,7 +1369,7 @@
         <v>63262</v>
       </c>
       <c r="R7" t="n">
-        <v>383947.05</v>
+        <v>595544.36</v>
       </c>
       <c r="S7" t="n">
         <v>150254.85</v>
@@ -1378,7 +1378,7 @@
         <v>150254.85</v>
       </c>
       <c r="U7" t="n">
-        <v>287416.37</v>
+        <v>499013.68</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         <v>115966</v>
       </c>
       <c r="O8" t="n">
-        <v>31684.04</v>
+        <v>37573.32</v>
       </c>
       <c r="P8" t="n">
         <v>181083.4</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1762096.42</v>
+        <v>1772550.72</v>
       </c>
       <c r="P10" t="n">
         <v>1304276.15</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>178219.94</v>
+        <v>180019.94</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>948026.42</v>
+        <v>1408379.49</v>
       </c>
       <c r="P20" t="n">
         <v>3125692.73</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
         <v>2308</v>
       </c>
       <c r="R27" t="n">
-        <v>526820.98</v>
+        <v>610820.98</v>
       </c>
       <c r="S27" t="n">
         <v>312903.94</v>
@@ -4178,7 +4178,7 @@
         <v>312903.94</v>
       </c>
       <c r="U27" t="n">
-        <v>484753.18</v>
+        <v>568753.1800000001</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>490620.47</v>
+        <v>500588.52</v>
       </c>
       <c r="P29" t="n">
         <v>316170.82</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3194578.48</v>
+        <v>3286386.22</v>
       </c>
       <c r="P31" t="n">
         <v>800034.36</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
         <v>110000</v>
       </c>
       <c r="O32" t="n">
-        <v>106383.99</v>
+        <v>124304.29</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
         <v>22671</v>
       </c>
       <c r="R42" t="n">
-        <v>51525.12</v>
+        <v>118525.12</v>
       </c>
       <c r="S42" t="n">
         <v>50187</v>
@@ -6278,7 +6278,7 @@
         <v>54123</v>
       </c>
       <c r="U42" t="n">
-        <v>51525.12</v>
+        <v>118525.12</v>
       </c>
       <c r="V42" t="n">
         <v>3936</v>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>912895.4300000001</v>
+        <v>923810.98</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -6540,7 +6540,7 @@
         <v>93886</v>
       </c>
       <c r="O44" t="n">
-        <v>867201.2</v>
+        <v>886604.63</v>
       </c>
       <c r="P44" t="n">
         <v>615163.5600000001</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
         <v>219000</v>
       </c>
       <c r="O45" t="n">
-        <v>30872.53</v>
+        <v>41714.54</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3336703.28</v>
+        <v>3699664.86</v>
       </c>
       <c r="P49" t="n">
         <v>4140329.7</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12271,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>15166.7</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -12712,10 +12712,10 @@
         <v>78000</v>
       </c>
       <c r="S88" t="n">
-        <v>52500</v>
+        <v>78000</v>
       </c>
       <c r="T88" t="n">
-        <v>52500</v>
+        <v>78000</v>
       </c>
       <c r="U88" t="n">
         <v>78000</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -16051,7 +16051,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>254250.5</v>
+        <v>283796.08</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
@@ -16060,7 +16060,7 @@
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>204550.5</v>
+        <v>247150.5</v>
       </c>
       <c r="P112" t="n">
         <v>50000</v>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>16605</v>
+        <v>83605</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -16498,7 +16498,7 @@
         <v>0</v>
       </c>
       <c r="U115" t="n">
-        <v>16605</v>
+        <v>83605</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -17469,7 +17469,7 @@
         <v>8077</v>
       </c>
       <c r="R122" t="n">
-        <v>203144.56</v>
+        <v>307882.16</v>
       </c>
       <c r="S122" t="n">
         <v>33311.56</v>
@@ -17478,7 +17478,7 @@
         <v>33311.56</v>
       </c>
       <c r="U122" t="n">
-        <v>147753.41</v>
+        <v>252491.01</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -17609,16 +17609,16 @@
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>519437</v>
+        <v>1083437</v>
       </c>
       <c r="S123" t="n">
-        <v>485922.72</v>
+        <v>971845.4399999999</v>
       </c>
       <c r="T123" t="n">
-        <v>485922.72</v>
+        <v>971845.4399999999</v>
       </c>
       <c r="U123" t="n">
-        <v>519437</v>
+        <v>1083437</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>642538.97</v>
+        <v>780008.0600000001</v>
       </c>
       <c r="P124" t="n">
         <v>2102872.47</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -19149,7 +19149,7 @@
         <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>206677.94</v>
+        <v>226677.94</v>
       </c>
       <c r="S134" t="n">
         <v>141746.12</v>
@@ -19158,7 +19158,7 @@
         <v>143540.12</v>
       </c>
       <c r="U134" t="n">
-        <v>199030.12</v>
+        <v>219030.12</v>
       </c>
       <c r="V134" t="n">
         <v>1794</v>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -19551,7 +19551,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>929386.36</v>
+        <v>930485.55</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -19560,7 +19560,7 @@
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>876799.9</v>
+        <v>904661.4399999999</v>
       </c>
       <c r="P137" t="n">
         <v>743505.8100000001</v>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -20951,7 +20951,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>112772.08</v>
+        <v>132386.98</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -20960,7 +20960,7 @@
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>73756.84</v>
+        <v>110600.71</v>
       </c>
       <c r="P147" t="n">
         <v>551.08</v>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -22631,7 +22631,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>60048172.37</v>
+        <v>86350213.91</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -22640,7 +22640,7 @@
         <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>59869982.53</v>
+        <v>59919823.77</v>
       </c>
       <c r="P159" t="n">
         <v>21043600.09</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23060,7 @@
         <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>29380182.6</v>
+        <v>29431997.31</v>
       </c>
       <c r="P162" t="n">
         <v>60670522</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23191,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24794007.34</v>
+        <v>24839100.08</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -23200,7 +23200,7 @@
         <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>24104598.76</v>
+        <v>24164007.34</v>
       </c>
       <c r="P163" t="n">
         <v>49898263.91</v>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>
@@ -24183,7 +24183,7 @@
         <v>24479179.14</v>
       </c>
       <c r="P170" t="n">
-        <v>3399155.21</v>
+        <v>3563076.37</v>
       </c>
       <c r="Q170" t="n">
         <v>0</v>
@@ -24192,13 +24192,13 @@
         <v>41074441.37</v>
       </c>
       <c r="S170" t="n">
-        <v>33060265.85</v>
+        <v>33672380.41</v>
       </c>
       <c r="T170" t="n">
-        <v>34673029.95</v>
+        <v>35285144.51</v>
       </c>
       <c r="U170" t="n">
-        <v>37675286.16</v>
+        <v>37511365</v>
       </c>
       <c r="V170" t="n">
         <v>1612764.1</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>06/05/2026 08:16:35</t>
+          <t>07/05/2026 08:19:38</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3081610.16</v>
+        <v>3838685.61</v>
       </c>
       <c r="P3" t="n">
         <v>220570.58</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1372,10 +1372,10 @@
         <v>595544.36</v>
       </c>
       <c r="S7" t="n">
-        <v>150254.85</v>
+        <v>153487.35</v>
       </c>
       <c r="T7" t="n">
-        <v>150254.85</v>
+        <v>153487.35</v>
       </c>
       <c r="U7" t="n">
         <v>499013.68</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>39666.86</v>
+        <v>40895.11</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1891034.93</v>
+        <v>2214574.36</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1418100.68</v>
+        <v>1418495.21</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -4172,10 +4172,10 @@
         <v>610820.98</v>
       </c>
       <c r="S27" t="n">
-        <v>312903.94</v>
+        <v>329040.58</v>
       </c>
       <c r="T27" t="n">
-        <v>312903.94</v>
+        <v>329040.58</v>
       </c>
       <c r="U27" t="n">
         <v>568753.1800000001</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>501019.15</v>
+        <v>587064.48</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>897502.4</v>
+        <v>907411.4399999999</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3286386.22</v>
+        <v>3579277.19</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
         <v>110000</v>
       </c>
       <c r="O32" t="n">
-        <v>124304.29</v>
+        <v>124605.95</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>832228.22</v>
+        <v>834960.12</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3443.08</v>
+        <v>4434.28</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>923810.98</v>
+        <v>1207764.31</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
         <v>20096</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>20096</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>486700</v>
+        <v>612250</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -10052,10 +10052,10 @@
         <v>921519</v>
       </c>
       <c r="S69" t="n">
-        <v>492900</v>
+        <v>618450</v>
       </c>
       <c r="T69" t="n">
-        <v>492900</v>
+        <v>618450</v>
       </c>
       <c r="U69" t="n">
         <v>921519</v>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -10746,7 +10746,7 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>238608</v>
       </c>
       <c r="R74" t="n">
         <v>1193451</v>
@@ -10764,7 +10764,7 @@
         <v>354819.03</v>
       </c>
       <c r="W74" t="n">
-        <v>1193451</v>
+        <v>1432059</v>
       </c>
       <c r="X74" t="n">
         <v>1671844</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -10892,10 +10892,10 @@
         <v>76897.66</v>
       </c>
       <c r="S75" t="n">
-        <v>58000</v>
+        <v>59168.01</v>
       </c>
       <c r="T75" t="n">
-        <v>58000</v>
+        <v>59168.01</v>
       </c>
       <c r="U75" t="n">
         <v>75773.00999999999</v>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>81922.86</v>
+        <v>122884.29</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -11151,7 +11151,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>30850.58</v>
+        <v>46172.22</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -11184,13 +11184,13 @@
         <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>818638</v>
+        <v>580030</v>
       </c>
       <c r="X77" t="n">
         <v>1314953</v>
       </c>
       <c r="Y77" t="n">
-        <v>406315</v>
+        <v>644923</v>
       </c>
       <c r="Z77" t="n">
         <v>90000</v>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -12551,7 +12551,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>345.28</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -13531,7 +13531,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -14791,7 +14791,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3410465.43</v>
+        <v>3416080.98</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -16051,7 +16051,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>283796.08</v>
+        <v>386071.33</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
@@ -16060,7 +16060,7 @@
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>247150.5</v>
+        <v>254250.5</v>
       </c>
       <c r="P112" t="n">
         <v>50000</v>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>57142.9</v>
+        <v>96278.44</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2414424.98</v>
+        <v>6086256.83</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -17591,7 +17591,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>161974.24</v>
+        <v>242961.36</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -17871,7 +17871,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>22963.84</v>
+        <v>70236.35000000001</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>3132800</v>
+        <v>3947200</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -19000,7 +19000,7 @@
         <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>16923298.94</v>
+        <v>19041664.7</v>
       </c>
       <c r="P133" t="n">
         <v>1425517.51</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -19152,10 +19152,10 @@
         <v>226677.94</v>
       </c>
       <c r="S134" t="n">
-        <v>141746.12</v>
+        <v>143901.12</v>
       </c>
       <c r="T134" t="n">
-        <v>143540.12</v>
+        <v>145695.12</v>
       </c>
       <c r="U134" t="n">
         <v>219030.12</v>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -19271,7 +19271,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>40338.4</v>
+        <v>51451.2</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>246715.46</v>
+        <v>256624.5</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -19551,7 +19551,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>930485.55</v>
+        <v>982655.9300000001</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>5903.55</v>
+        <v>7871.4</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -22080,7 +22080,7 @@
         <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>12940208.36</v>
+        <v>14955138.28</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -22631,7 +22631,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>86350213.91</v>
+        <v>89675298.11</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -22646,7 +22646,7 @@
         <v>21043600.09</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>5086650.13</v>
       </c>
       <c r="R159" t="n">
         <v>160562812.27</v>
@@ -22664,7 +22664,7 @@
         <v>5439712.39</v>
       </c>
       <c r="W159" t="n">
-        <v>165715582</v>
+        <v>170802232.13</v>
       </c>
       <c r="X159" t="n">
         <v>171813039</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>31386458.91</v>
+        <v>32341444.51</v>
       </c>
       <c r="M162" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23191,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24839100.08</v>
+        <v>25038623.04</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -23200,7 +23200,7 @@
         <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>24164007.34</v>
+        <v>24434007.34</v>
       </c>
       <c r="P163" t="n">
         <v>49898263.91</v>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>
@@ -24180,7 +24180,7 @@
         <v>0</v>
       </c>
       <c r="O170" t="n">
-        <v>24479179.14</v>
+        <v>26316455.82</v>
       </c>
       <c r="P170" t="n">
         <v>3563076.37</v>
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>41074441.37</v>
+        <v>41134719.61</v>
       </c>
       <c r="S170" t="n">
         <v>33672380.41</v>
@@ -24198,7 +24198,7 @@
         <v>35285144.51</v>
       </c>
       <c r="U170" t="n">
-        <v>37511365</v>
+        <v>37571643.24</v>
       </c>
       <c r="V170" t="n">
         <v>1612764.1</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>07/05/2026 08:19:38</t>
+          <t>08/05/2026 07:50:57</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>09/05/2026 07:23:36</t>
+          <t>10/05/2026 07:29:45</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>10/05/2026 07:29:45</t>
+          <t>11/05/2026 09:28:42</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>65947.21000000001</v>
+        <v>67391.71000000001</v>
       </c>
       <c r="S6" t="n">
         <v>58747.21</v>
@@ -1238,7 +1238,7 @@
         <v>58747.21</v>
       </c>
       <c r="U6" t="n">
-        <v>58747.21</v>
+        <v>60191.71</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
         <v>597048.9</v>
       </c>
       <c r="S8" t="n">
-        <v>191768.25</v>
+        <v>174956.22</v>
       </c>
       <c r="T8" t="n">
         <v>211768.25</v>
@@ -1521,7 +1521,7 @@
         <v>415965.5</v>
       </c>
       <c r="V8" t="n">
-        <v>20000</v>
+        <v>36812.03</v>
       </c>
       <c r="W8" t="n">
         <v>415966</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
         <v>1866731.38</v>
       </c>
       <c r="S44" t="n">
-        <v>1460688.16</v>
+        <v>1421712.98</v>
       </c>
       <c r="T44" t="n">
         <v>1460688.16</v>
@@ -6561,7 +6561,7 @@
         <v>1460688.16</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>38975.18</v>
       </c>
       <c r="W44" t="n">
         <v>1471969</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1207764.31</v>
+        <v>1208215.71</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
         <v>200000</v>
@@ -9513,10 +9513,10 @@
         <v>600000</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="AA65" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
         <v>5</v>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>2300000</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
         <v>2300000</v>
@@ -9653,10 +9653,10 @@
         <v>6900000</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2300000</v>
       </c>
       <c r="AA66" t="n">
-        <v>2300000</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
         <v>5</v>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -10883,22 +10883,22 @@
         <v>1193382.32</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>238607.79</v>
       </c>
       <c r="Q75" t="n">
         <v>238608</v>
       </c>
       <c r="R75" t="n">
-        <v>1193451</v>
+        <v>1670666.79</v>
       </c>
       <c r="S75" t="n">
-        <v>1193451</v>
+        <v>1432058.79</v>
       </c>
       <c r="T75" t="n">
-        <v>1548270.03</v>
+        <v>1786877.82</v>
       </c>
       <c r="U75" t="n">
-        <v>1193451</v>
+        <v>1432059</v>
       </c>
       <c r="V75" t="n">
         <v>354819.03</v>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -16349,16 +16349,16 @@
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>5238691</v>
+        <v>5442598.8</v>
       </c>
       <c r="S114" t="n">
-        <v>5238691</v>
+        <v>5442598.8</v>
       </c>
       <c r="T114" t="n">
-        <v>8823589.4</v>
+        <v>9027497.199999999</v>
       </c>
       <c r="U114" t="n">
-        <v>5238691</v>
+        <v>5442598.8</v>
       </c>
       <c r="V114" t="n">
         <v>3584898.4</v>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -19572,7 +19572,7 @@
         <v>2537927</v>
       </c>
       <c r="S137" t="n">
-        <v>1074549.58</v>
+        <v>1064838.18</v>
       </c>
       <c r="T137" t="n">
         <v>1131764.02</v>
@@ -19581,7 +19581,7 @@
         <v>2537927</v>
       </c>
       <c r="V137" t="n">
-        <v>57214.44</v>
+        <v>66925.84</v>
       </c>
       <c r="W137" t="n">
         <v>2537927</v>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -22771,7 +22771,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>89675298.11</v>
+        <v>90332993.66</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23191,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>32341444.51</v>
+        <v>34703144.51</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>336000</v>
+        <v>448000</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>11/05/2026 09:28:42</t>
+          <t>12/05/2026 08:32:06</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42:57</t>
+          <t>14/05/2026 08:28:39</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>14/05/2026 08:28:39</t>
+          <t>15/05/2026 08:36:27</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>15/05/2026 08:36:27</t>
+          <t>16/05/2026 07:31:02</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ172"/>
+  <dimension ref="A1:AJ173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>193.66</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -952,13 +952,13 @@
         <v>178086</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>93692.34</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>93692.34</v>
       </c>
       <c r="U4" t="n">
-        <v>178086</v>
+        <v>177892.34</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>60191.71</v>
+        <v>44477.62</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1220,28 +1220,28 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>56179.21</v>
+        <v>43033.12</v>
       </c>
       <c r="P6" t="n">
-        <v>7200</v>
+        <v>22914.09</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>67391.71000000001</v>
+        <v>77359.71000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>60191.71</v>
+        <v>44477.62</v>
       </c>
       <c r="T6" t="n">
         <v>60191.71</v>
       </c>
       <c r="U6" t="n">
-        <v>60191.71</v>
+        <v>54445.62</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>15714.09</v>
       </c>
       <c r="W6" t="n">
         <v>203353</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>14217.8</v>
+        <v>60379.3</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         <v>115966</v>
       </c>
       <c r="O8" t="n">
-        <v>37573.32</v>
+        <v>39666.86</v>
       </c>
       <c r="P8" t="n">
         <v>181083.4</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2214697.36</v>
+        <v>2275961.54</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1822468.7</v>
+        <v>1973590.98</v>
       </c>
       <c r="P10" t="n">
         <v>1305626.15</v>
@@ -1792,16 +1792,16 @@
         <v>12905283.63</v>
       </c>
       <c r="S10" t="n">
-        <v>8396343.800000001</v>
+        <v>8409678.279999999</v>
       </c>
       <c r="T10" t="n">
-        <v>8503844.35</v>
+        <v>8533781.869999999</v>
       </c>
       <c r="U10" t="n">
         <v>11599657.48</v>
       </c>
       <c r="V10" t="n">
-        <v>107500.55</v>
+        <v>124103.59</v>
       </c>
       <c r="W10" t="n">
         <v>12250650</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>393876.57</v>
+        <v>539416.15</v>
       </c>
       <c r="P18" t="n">
         <v>14849.99</v>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1429645.87</v>
+        <v>1869188.08</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1418100.68</v>
+        <v>1418495.21</v>
       </c>
       <c r="P20" t="n">
         <v>3125692.73</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>500768.52</v>
+        <v>503279.78</v>
       </c>
       <c r="P30" t="n">
         <v>316170.82</v>
@@ -4592,16 +4592,16 @@
         <v>2157842.86</v>
       </c>
       <c r="S30" t="n">
-        <v>1634951.64</v>
+        <v>1635347.1</v>
       </c>
       <c r="T30" t="n">
-        <v>1748452.01</v>
+        <v>1749242.93</v>
       </c>
       <c r="U30" t="n">
         <v>1841672.04</v>
       </c>
       <c r="V30" t="n">
-        <v>113500.37</v>
+        <v>113895.83</v>
       </c>
       <c r="W30" t="n">
         <v>1841736</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>897502.4</v>
+        <v>907411.4399999999</v>
       </c>
       <c r="P31" t="n">
         <v>2164954.67</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3940398.7</v>
+        <v>4042025.11</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3286386.22</v>
+        <v>3543371.61</v>
       </c>
       <c r="P32" t="n">
         <v>800034.36</v>
@@ -4872,10 +4872,10 @@
         <v>18626200.63</v>
       </c>
       <c r="S32" t="n">
-        <v>16983877.06</v>
+        <v>16984300.52</v>
       </c>
       <c r="T32" t="n">
-        <v>16990449.71</v>
+        <v>16990873.17</v>
       </c>
       <c r="U32" t="n">
         <v>17826166.27</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>130879.01</v>
+        <v>146687.82</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>26138.53</v>
+        <v>42156.29</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>834960.12</v>
+        <v>837355.79</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
         <v>131526</v>
       </c>
       <c r="O43" t="n">
-        <v>3115.08</v>
+        <v>4106.28</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1208215.71</v>
+        <v>1275719.01</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6680,7 +6680,7 @@
         <v>93886</v>
       </c>
       <c r="O45" t="n">
-        <v>900771.09</v>
+        <v>1156730.37</v>
       </c>
       <c r="P45" t="n">
         <v>615163.5600000001</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>55921.64</v>
+        <v>65193.76</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4476108.99</v>
+        <v>6028997.25</v>
       </c>
       <c r="P50" t="n">
         <v>4140329.7</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>612250</v>
+        <v>609150</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -10320,7 +10320,7 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>612250</v>
+        <v>609150</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -11300,7 +11300,7 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>81922.86</v>
+        <v>122884.29</v>
       </c>
       <c r="P78" t="n">
         <v>12692.75</v>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>30850.58</v>
+        <v>46172.22</v>
       </c>
       <c r="P79" t="n">
         <v>3571.59</v>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2830.87</v>
+        <v>3589.39</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -12149,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>679177.12</v>
+        <v>1838981</v>
       </c>
       <c r="S84" t="n">
         <v>679177.12</v>
@@ -12158,7 +12158,7 @@
         <v>679177.12</v>
       </c>
       <c r="U84" t="n">
-        <v>679177.12</v>
+        <v>1838981</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -12840,7 +12840,7 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>345.28</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>61500</v>
+        <v>66000</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
         <v>400000</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3416080.98</v>
+        <v>4418871.33</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -16331,16 +16331,16 @@
         </is>
       </c>
       <c r="L114" t="n">
+        <v>399585.19</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
         <v>386071.33</v>
-      </c>
-      <c r="M114" t="n">
-        <v>0</v>
-      </c>
-      <c r="N114" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" t="n">
-        <v>283796.08</v>
       </c>
       <c r="P114" t="n">
         <v>560000</v>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -16480,7 +16480,7 @@
         <v>203908</v>
       </c>
       <c r="O115" t="n">
-        <v>3046970.4</v>
+        <v>5238691</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -17040,7 +17040,7 @@
         <v>190000</v>
       </c>
       <c r="O119" t="n">
-        <v>57142.9</v>
+        <v>96278.44</v>
       </c>
       <c r="P119" t="n">
         <v>227316.91</v>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>11422.18</v>
+        <v>15685.63</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -17460,7 +17460,7 @@
         <v>2294560.33</v>
       </c>
       <c r="O122" t="n">
-        <v>2414424.98</v>
+        <v>6141769.7</v>
       </c>
       <c r="P122" t="n">
         <v>393733.59</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -17880,7 +17880,7 @@
         <v>564000</v>
       </c>
       <c r="O125" t="n">
-        <v>161974.24</v>
+        <v>242961.36</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -18011,16 +18011,16 @@
         </is>
       </c>
       <c r="L126" t="n">
+        <v>854277.5699999999</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
         <v>808907.3100000001</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" t="n">
-        <v>780215.36</v>
       </c>
       <c r="P126" t="n">
         <v>2102872.47</v>
@@ -18029,7 +18029,7 @@
         <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>5725169.27</v>
+        <v>5741562.6</v>
       </c>
       <c r="S126" t="n">
         <v>2711399.82</v>
@@ -18038,7 +18038,7 @@
         <v>2711719.82</v>
       </c>
       <c r="U126" t="n">
-        <v>3622296.8</v>
+        <v>3638690.13</v>
       </c>
       <c r="V126" t="n">
         <v>320</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -18160,7 +18160,7 @@
         <v>158000</v>
       </c>
       <c r="O127" t="n">
-        <v>22963.84</v>
+        <v>38891.38</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -18857,7 +18857,7 @@
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -18884,7 +18884,7 @@
         <v>0</v>
       </c>
       <c r="W132" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="X132" t="n">
         <v>0</v>
@@ -18896,7 +18896,7 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
         <v>5</v>
@@ -18924,17 +18924,17 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Kenji Ito</t>
+          <t>Emendas Parlamentares - Senival Moura</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7048</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -18997,7 +18997,7 @@
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -19024,7 +19024,7 @@
         <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="X133" t="n">
         <v>0</v>
@@ -19036,7 +19036,7 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="AB133" t="n">
         <v>5</v>
@@ -19064,17 +19064,17 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Lucas Pavanato</t>
+          <t>Emendas Parlamentares - Kenji Ito</t>
         </is>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7077</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -19127,11 +19127,11 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>3947200</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
@@ -19140,43 +19140,43 @@
         <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>3947200</v>
+        <v>0</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>3984000</v>
+        <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>4763600</v>
+        <v>0</v>
       </c>
       <c r="U134" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="V134" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="W134" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="X134" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1421600</v>
+        <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>8705439.67</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
         <v>5</v>
@@ -19199,22 +19199,22 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Lucas Pavanato</t>
         </is>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7077</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -19247,7 +19247,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -19257,7 +19257,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -19271,7 +19271,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>19041664.7</v>
+        <v>3919200</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -19280,43 +19280,43 @@
         <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>19041664.7</v>
+        <v>3919200</v>
       </c>
       <c r="P135" t="n">
-        <v>1425517.51</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="R135" t="n">
-        <v>23851875.51</v>
+        <v>8578400</v>
       </c>
       <c r="S135" t="n">
-        <v>21926109.23</v>
+        <v>3984000</v>
       </c>
       <c r="T135" t="n">
-        <v>22593123.43</v>
+        <v>4763600</v>
       </c>
       <c r="U135" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="V135" t="n">
-        <v>667014.2</v>
+        <v>779600</v>
       </c>
       <c r="W135" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="X135" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="AA135" t="n">
-        <v>22426358</v>
+        <v>8705439.67</v>
       </c>
       <c r="AB135" t="n">
         <v>5</v>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AH135" t="inlineStr">
@@ -19349,12 +19349,12 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -19411,43 +19411,43 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>64653</v>
+        <v>19041664.7</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>52998</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>64653</v>
+        <v>19041664.7</v>
       </c>
       <c r="P136" t="n">
-        <v>7647.82</v>
+        <v>1425517.51</v>
       </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>226677.94</v>
+        <v>23851875.51</v>
       </c>
       <c r="S136" t="n">
-        <v>143901.12</v>
+        <v>21926109.23</v>
       </c>
       <c r="T136" t="n">
-        <v>145695.12</v>
+        <v>22593123.43</v>
       </c>
       <c r="U136" t="n">
-        <v>219030.12</v>
+        <v>22426358</v>
       </c>
       <c r="V136" t="n">
-        <v>1794</v>
+        <v>667014.2</v>
       </c>
       <c r="W136" t="n">
-        <v>252998</v>
+        <v>22426358</v>
       </c>
       <c r="X136" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="Y136" t="n">
         <v>0</v>
@@ -19456,7 +19456,7 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>252998</v>
+        <v>22426358</v>
       </c>
       <c r="AB136" t="n">
         <v>5</v>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH136" t="inlineStr">
@@ -19489,12 +19489,12 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -19551,43 +19551,43 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>51451.2</v>
+        <v>64653</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>52998</v>
       </c>
       <c r="O137" t="n">
-        <v>40338.4</v>
+        <v>64653</v>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>7647.82</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>95531.96000000001</v>
+        <v>226677.94</v>
       </c>
       <c r="S137" t="n">
-        <v>95531.96000000001</v>
+        <v>143901.12</v>
       </c>
       <c r="T137" t="n">
-        <v>95531.96000000001</v>
+        <v>145695.12</v>
       </c>
       <c r="U137" t="n">
-        <v>95531.96000000001</v>
+        <v>219030.12</v>
       </c>
       <c r="V137" t="n">
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="W137" t="n">
-        <v>250000</v>
+        <v>252998</v>
       </c>
       <c r="X137" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="Y137" t="n">
         <v>0</v>
@@ -19596,7 +19596,7 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>250000</v>
+        <v>252998</v>
       </c>
       <c r="AB137" t="n">
         <v>5</v>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH137" t="inlineStr">
@@ -19629,12 +19629,12 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -19677,7 +19677,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -19691,7 +19691,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>370073.19</v>
+        <v>51451.2</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -19700,7 +19700,7 @@
         <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>246715.46</v>
+        <v>40338.4</v>
       </c>
       <c r="P138" t="n">
         <v>0</v>
@@ -19709,25 +19709,25 @@
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>2537927</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="S138" t="n">
-        <v>1064838.18</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="T138" t="n">
-        <v>1131764.02</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="U138" t="n">
-        <v>2537927</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="V138" t="n">
-        <v>66925.84</v>
+        <v>0</v>
       </c>
       <c r="W138" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="X138" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="Y138" t="n">
         <v>0</v>
@@ -19736,7 +19736,7 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="AB138" t="n">
         <v>5</v>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH138" t="inlineStr">
@@ -19769,12 +19769,12 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -19831,7 +19831,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>982655.9300000001</v>
+        <v>370073.19</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -19840,43 +19840,43 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>929386.36</v>
+        <v>256624.5</v>
       </c>
       <c r="P139" t="n">
-        <v>743505.8100000001</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>3802648.2</v>
+        <v>2537927</v>
       </c>
       <c r="S139" t="n">
-        <v>2409038.89</v>
+        <v>1064838.18</v>
       </c>
       <c r="T139" t="n">
-        <v>2502957.88</v>
+        <v>1131764.02</v>
       </c>
       <c r="U139" t="n">
-        <v>3059142.39</v>
+        <v>2537927</v>
       </c>
       <c r="V139" t="n">
-        <v>93918.99000000001</v>
+        <v>66925.84</v>
       </c>
       <c r="W139" t="n">
-        <v>4104655</v>
+        <v>2537927</v>
       </c>
       <c r="X139" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="Y139" t="n">
-        <v>63262</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="n">
-        <v>638132</v>
+        <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>4167917</v>
+        <v>2537927</v>
       </c>
       <c r="AB139" t="n">
         <v>5</v>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH139" t="inlineStr">
@@ -19909,12 +19909,12 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -19967,11 +19967,11 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>368.19</v>
+        <v>1011239.26</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -19980,43 +19980,43 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>312.26</v>
+        <v>982655.9300000001</v>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>743505.8100000001</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>80100</v>
+        <v>3802648.2</v>
       </c>
       <c r="S140" t="n">
-        <v>73100</v>
+        <v>2409038.89</v>
       </c>
       <c r="T140" t="n">
-        <v>80100</v>
+        <v>2502957.88</v>
       </c>
       <c r="U140" t="n">
-        <v>80100</v>
+        <v>3059142.39</v>
       </c>
       <c r="V140" t="n">
-        <v>7000</v>
+        <v>93918.99000000001</v>
       </c>
       <c r="W140" t="n">
-        <v>139282</v>
+        <v>4104655</v>
       </c>
       <c r="X140" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="Y140" t="n">
-        <v>0</v>
+        <v>63262</v>
       </c>
       <c r="Z140" t="n">
-        <v>0</v>
+        <v>638132</v>
       </c>
       <c r="AA140" t="n">
-        <v>139282</v>
+        <v>4167917</v>
       </c>
       <c r="AB140" t="n">
         <v>5</v>
@@ -20044,17 +20044,17 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -20097,7 +20097,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -20107,11 +20107,11 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>7871.4</v>
+        <v>368.19</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -20120,7 +20120,7 @@
         <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>7871.4</v>
+        <v>312.26</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
@@ -20129,25 +20129,25 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="S141" t="n">
-        <v>19678.5</v>
+        <v>73100</v>
       </c>
       <c r="T141" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="U141" t="n">
-        <v>19678.5</v>
+        <v>80100</v>
       </c>
       <c r="V141" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="W141" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="X141" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="Y141" t="n">
         <v>0</v>
@@ -20156,7 +20156,7 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="AB141" t="n">
         <v>5</v>
@@ -20179,22 +20179,22 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -20227,17 +20227,17 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -20251,7 +20251,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>7871.4</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -20260,43 +20260,43 @@
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>7871.4</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S142" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T142" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U142" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="X142" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="Y142" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="AB142" t="n">
         <v>5</v>
@@ -20304,12 +20304,12 @@
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -20319,7 +20319,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
@@ -20329,12 +20329,12 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -20406,7 +20406,7 @@
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>200000</v>
+        <v>220000</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
@@ -20427,16 +20427,16 @@
         <v>0</v>
       </c>
       <c r="X143" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="Y143" t="n">
-        <v>300000</v>
+        <v>330000</v>
       </c>
       <c r="Z143" t="n">
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="AB143" t="n">
         <v>5</v>
@@ -20449,7 +20449,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
+          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -20469,12 +20469,12 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -20507,7 +20507,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -20546,7 +20546,7 @@
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>75000</v>
+        <v>200000</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
@@ -20567,16 +20567,16 @@
         <v>0</v>
       </c>
       <c r="X144" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y144" t="n">
-        <v>75000</v>
+        <v>300000</v>
       </c>
       <c r="Z144" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AB144" t="n">
         <v>5</v>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
+          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -20609,12 +20609,12 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -20643,21 +20643,21 @@
         <v>422</v>
       </c>
       <c r="F145" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -20686,7 +20686,7 @@
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
@@ -20704,19 +20704,19 @@
         <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="X145" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="Y145" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Z145" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA145" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
         <v>5</v>
@@ -20724,12 +20724,12 @@
       <c r="AC145" t="inlineStr"/>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>CPIR - Políticas</t>
+          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH145" t="inlineStr">
@@ -20749,12 +20749,12 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -20787,7 +20787,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -20797,7 +20797,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -20811,7 +20811,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>3595409.86</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -20820,43 +20820,43 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>3595409.86</v>
+        <v>0</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>127000</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="U146" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>3596273</v>
+        <v>11949</v>
       </c>
       <c r="X146" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="Y146" t="n">
-        <v>2986219</v>
+        <v>0</v>
       </c>
       <c r="Z146" t="n">
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="AB146" t="n">
         <v>5</v>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH146" t="inlineStr">
@@ -20889,12 +20889,12 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -20951,7 +20951,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>3595409.86</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -20960,43 +20960,43 @@
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>3595409.86</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="S147" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="T147" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="U147" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>5374</v>
+        <v>3596273</v>
       </c>
       <c r="X147" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="Y147" t="n">
-        <v>4626</v>
+        <v>2986219</v>
       </c>
       <c r="Z147" t="n">
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="AB147" t="n">
         <v>5</v>
@@ -21019,7 +21019,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH147" t="inlineStr">
@@ -21029,12 +21029,12 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -21124,19 +21124,19 @@
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>80612</v>
+        <v>5374</v>
       </c>
       <c r="X148" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="Y148" t="n">
-        <v>69388</v>
+        <v>4626</v>
       </c>
       <c r="Z148" t="n">
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="AB148" t="n">
         <v>5</v>
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
@@ -21169,12 +21169,12 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -21231,7 +21231,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>132386.98</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
@@ -21240,43 +21240,43 @@
         <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>132386.98</v>
+        <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>551.08</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>5040463.02</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>570925.76</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>570925.76</v>
+        <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>5039911.94</v>
+        <v>0</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>5870981</v>
+        <v>80612</v>
       </c>
       <c r="X149" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="Y149" t="n">
-        <v>5054381</v>
+        <v>69388</v>
       </c>
       <c r="Z149" t="n">
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="AB149" t="n">
         <v>5</v>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH149" t="inlineStr">
@@ -21309,12 +21309,12 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -21367,11 +21367,11 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>76.61</v>
+        <v>132386.98</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -21380,43 +21380,43 @@
         <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>76.61</v>
+        <v>132386.98</v>
       </c>
       <c r="P150" t="n">
-        <v>925</v>
+        <v>551.08</v>
       </c>
       <c r="Q150" t="n">
         <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>1900</v>
+        <v>5040463.02</v>
       </c>
       <c r="S150" t="n">
-        <v>975</v>
+        <v>570925.76</v>
       </c>
       <c r="T150" t="n">
-        <v>975</v>
+        <v>570925.76</v>
       </c>
       <c r="U150" t="n">
-        <v>975</v>
+        <v>5039911.94</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>1000</v>
+        <v>5870981</v>
       </c>
       <c r="X150" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="Y150" t="n">
-        <v>0</v>
+        <v>5054381</v>
       </c>
       <c r="Z150" t="n">
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="AB150" t="n">
         <v>5</v>
@@ -21444,17 +21444,17 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -21487,17 +21487,17 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -21507,11 +21507,11 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>76.61</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -21520,43 +21520,43 @@
         <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>0</v>
+        <v>76.61</v>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="Q151" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="S151" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="T151" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="U151" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X151" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="Y151" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB151" t="n">
         <v>5</v>
@@ -21564,12 +21564,12 @@
       <c r="AC151" t="inlineStr"/>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -21579,22 +21579,22 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -21620,24 +21620,24 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F152" t="n">
         <v>4026</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21663,40 +21663,40 @@
         <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>11400</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>15000</v>
+        <v>75000</v>
       </c>
       <c r="R152" t="n">
-        <v>21600</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="U152" t="n">
-        <v>10200</v>
+        <v>0</v>
       </c>
       <c r="V152" t="n">
         <v>0</v>
       </c>
       <c r="W152" t="n">
-        <v>22143</v>
+        <v>0</v>
       </c>
       <c r="X152" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="Y152" t="n">
-        <v>39738</v>
+        <v>75000</v>
       </c>
       <c r="Z152" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA152" t="n">
-        <v>46881</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
         <v>5</v>
@@ -21704,12 +21704,12 @@
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>COPIND - Políticas</t>
+          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
@@ -21729,12 +21729,12 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -21777,7 +21777,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -21791,7 +21791,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -21803,40 +21803,40 @@
         <v>0</v>
       </c>
       <c r="P153" t="n">
-        <v>19140.97</v>
+        <v>11400</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="R153" t="n">
-        <v>52809.97</v>
+        <v>21600</v>
       </c>
       <c r="S153" t="n">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="T153" t="n">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="U153" t="n">
-        <v>33669</v>
+        <v>10200</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>33669</v>
+        <v>22143</v>
       </c>
       <c r="X153" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="Y153" t="n">
-        <v>187297</v>
+        <v>39738</v>
       </c>
       <c r="Z153" t="n">
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="AB153" t="n">
         <v>5</v>
@@ -21859,7 +21859,7 @@
       </c>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH153" t="inlineStr">
@@ -21869,12 +21869,12 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -21907,17 +21907,17 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -21943,13 +21943,13 @@
         <v>0</v>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>19140.97</v>
       </c>
       <c r="Q154" t="n">
-        <v>127873.65</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>52809.97</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -21958,25 +21958,25 @@
         <v>0</v>
       </c>
       <c r="U154" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="X154" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="Y154" t="n">
-        <v>155747.3</v>
+        <v>187297</v>
       </c>
       <c r="Z154" t="n">
-        <v>72126.35000000001</v>
+        <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>27873.65</v>
+        <v>220966</v>
       </c>
       <c r="AB154" t="n">
         <v>5</v>
@@ -21984,12 +21984,12 @@
       <c r="AC154" t="inlineStr"/>
       <c r="AD154" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -21999,7 +21999,7 @@
       </c>
       <c r="AG154" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH154" t="inlineStr">
@@ -22009,12 +22009,12 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -22026,12 +22026,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -22040,19 +22040,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F155" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -22067,56 +22067,56 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>127873.65</v>
       </c>
       <c r="R155" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="T155" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U155" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="X155" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="Y155" t="n">
-        <v>0</v>
+        <v>155747.3</v>
       </c>
       <c r="Z155" t="n">
-        <v>0</v>
+        <v>72126.35000000001</v>
       </c>
       <c r="AA155" t="n">
-        <v>150000</v>
+        <v>27873.65</v>
       </c>
       <c r="AB155" t="n">
         <v>5</v>
@@ -22124,12 +22124,12 @@
       <c r="AC155" t="inlineStr"/>
       <c r="AD155" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -22144,17 +22144,17 @@
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
+          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -22197,7 +22197,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -22207,20 +22207,20 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M156" t="n">
         <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O156" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
@@ -22229,34 +22229,34 @@
         <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="T156" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U156" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="X156" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="Z156" t="n">
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>589773</v>
+        <v>150000</v>
       </c>
       <c r="AB156" t="n">
         <v>5</v>
@@ -22279,65 +22279,65 @@
       </c>
       <c r="AG156" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
         </is>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F157" t="n">
         <v>4010</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -22351,7 +22351,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>18190190.37</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
@@ -22360,7 +22360,7 @@
         <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>18190190.37</v>
+        <v>0</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -22369,34 +22369,34 @@
         <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="T157" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="U157" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="X157" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="Y157" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="Z157" t="n">
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="AB157" t="n">
         <v>5</v>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -22419,7 +22419,7 @@
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr">
@@ -22429,12 +22429,12 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -22477,7 +22477,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -22491,16 +22491,16 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>18190190.37</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>5086650.13</v>
       </c>
       <c r="O158" t="n">
-        <v>0</v>
+        <v>18190190.37</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -22509,34 +22509,34 @@
         <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>45922205.13</v>
       </c>
       <c r="S158" t="n">
-        <v>0</v>
+        <v>45922205.12</v>
       </c>
       <c r="T158" t="n">
-        <v>0</v>
+        <v>45922205.12</v>
       </c>
       <c r="U158" t="n">
-        <v>0</v>
+        <v>45922205.13</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>600437</v>
+        <v>45922205.13</v>
       </c>
       <c r="X158" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="Y158" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="n">
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>16896102</v>
+        <v>45922205.13</v>
       </c>
       <c r="AB158" t="n">
         <v>5</v>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="AG158" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH158" t="inlineStr">
@@ -22569,12 +22569,12 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -22596,23 +22596,23 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F159" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -22664,19 +22664,19 @@
         <v>0</v>
       </c>
       <c r="W159" t="n">
-        <v>1000</v>
+        <v>600437</v>
       </c>
       <c r="X159" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="Y159" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Z159" t="n">
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="AB159" t="n">
         <v>5</v>
@@ -22689,7 +22689,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -22709,12 +22709,12 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>44906100</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -22777,7 +22777,7 @@
         <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -22789,7 +22789,7 @@
         <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -22798,16 +22798,16 @@
         <v>0</v>
       </c>
       <c r="U160" t="n">
-        <v>361510</v>
+        <v>0</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>361510</v>
+        <v>1000</v>
       </c>
       <c r="X160" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y160" t="n">
         <v>0</v>
@@ -22816,7 +22816,7 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>361510</v>
+        <v>1000</v>
       </c>
       <c r="AB160" t="n">
         <v>5</v>
@@ -22839,7 +22839,7 @@
       </c>
       <c r="AG160" t="inlineStr">
         <is>
-          <t>Aquisição de Imóveis</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AH160" t="inlineStr">
@@ -22849,12 +22849,12 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
+          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -22880,14 +22880,14 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F161" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44906100</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -22911,52 +22911,52 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>90332993.66</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
         <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="O161" t="n">
-        <v>60017672.37</v>
+        <v>0</v>
       </c>
       <c r="P161" t="n">
-        <v>21043600.09</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>5086650.13</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>160562812.27</v>
+        <v>361510</v>
       </c>
       <c r="S161" t="n">
-        <v>135266690.46</v>
+        <v>0</v>
       </c>
       <c r="T161" t="n">
-        <v>140706402.85</v>
+        <v>0</v>
       </c>
       <c r="U161" t="n">
-        <v>139519212.18</v>
+        <v>361510</v>
       </c>
       <c r="V161" t="n">
-        <v>5439712.39</v>
+        <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>170802232.13</v>
+        <v>361510</v>
       </c>
       <c r="X161" t="n">
-        <v>171813039</v>
+        <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Z161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA161" t="n">
         <v>361510</v>
-      </c>
-      <c r="AA161" t="n">
-        <v>171451529</v>
       </c>
       <c r="AB161" t="n">
         <v>5</v>
@@ -22969,7 +22969,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -22979,7 +22979,7 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Aquisição de Imóveis</t>
         </is>
       </c>
       <c r="AH161" t="inlineStr">
@@ -22989,12 +22989,12 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
+          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -23037,21 +23037,21 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>90456591.02</v>
       </c>
       <c r="M162" t="n">
         <v>0</v>
@@ -23060,43 +23060,43 @@
         <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>0</v>
+        <v>89675298.11</v>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>21043600.09</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>5086650.13</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>160562812.27</v>
       </c>
       <c r="S162" t="n">
-        <v>0</v>
+        <v>135266690.46</v>
       </c>
       <c r="T162" t="n">
-        <v>0</v>
+        <v>140706402.85</v>
       </c>
       <c r="U162" t="n">
-        <v>0</v>
+        <v>139519212.18</v>
       </c>
       <c r="V162" t="n">
-        <v>0</v>
+        <v>5439712.39</v>
       </c>
       <c r="W162" t="n">
-        <v>2000</v>
+        <v>165715582</v>
       </c>
       <c r="X162" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="Y162" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Z162" t="n">
-        <v>0</v>
+        <v>5448160.13</v>
       </c>
       <c r="AA162" t="n">
-        <v>2000</v>
+        <v>166364878.87</v>
       </c>
       <c r="AB162" t="n">
         <v>5</v>
@@ -23114,27 +23114,27 @@
       </c>
       <c r="AF162" t="inlineStr">
         <is>
-          <t>05 - Outras Fontes</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
+          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -23182,12 +23182,12 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -23224,10 +23224,10 @@
         <v>0</v>
       </c>
       <c r="W163" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="X163" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="Y163" t="n">
         <v>0</v>
@@ -23236,7 +23236,7 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="AB163" t="n">
         <v>5</v>
@@ -23254,7 +23254,7 @@
       </c>
       <c r="AF163" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>05 - Outras Fontes</t>
         </is>
       </c>
       <c r="AG163" t="inlineStr">
@@ -23264,17 +23264,17 @@
       </c>
       <c r="AH163" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
+          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -23317,21 +23317,21 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>36595939.71</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
         <v>0</v>
@@ -23340,43 +23340,43 @@
         <v>0</v>
       </c>
       <c r="O164" t="n">
-        <v>29431997.31</v>
+        <v>0</v>
       </c>
       <c r="P164" t="n">
-        <v>60670522</v>
+        <v>0</v>
       </c>
       <c r="Q164" t="n">
         <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>197559544</v>
+        <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>107626518.4</v>
+        <v>0</v>
       </c>
       <c r="T164" t="n">
-        <v>107626518.4</v>
+        <v>0</v>
       </c>
       <c r="U164" t="n">
-        <v>136889022</v>
+        <v>0</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
       </c>
       <c r="W164" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="X164" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="Y164" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Z164" t="n">
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="AB164" t="n">
         <v>5</v>
@@ -23394,27 +23394,27 @@
       </c>
       <c r="AF164" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
         </is>
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -23471,7 +23471,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>25155138.67</v>
+        <v>38488734.91</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
@@ -23480,43 +23480,43 @@
         <v>0</v>
       </c>
       <c r="O165" t="n">
-        <v>24794007.34</v>
+        <v>32341444.51</v>
       </c>
       <c r="P165" t="n">
-        <v>49898263.91</v>
+        <v>60670522</v>
       </c>
       <c r="Q165" t="n">
         <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>129341289.91</v>
+        <v>197559544</v>
       </c>
       <c r="S165" t="n">
-        <v>78692487.98999999</v>
+        <v>107626518.4</v>
       </c>
       <c r="T165" t="n">
-        <v>95336487.98999999</v>
+        <v>107626518.4</v>
       </c>
       <c r="U165" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="V165" t="n">
-        <v>16644000</v>
+        <v>0</v>
       </c>
       <c r="W165" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="X165" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="Y165" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="Z165" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>82235403</v>
+        <v>141616875</v>
       </c>
       <c r="AB165" t="n">
         <v>5</v>
@@ -23539,7 +23539,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AH165" t="inlineStr">
@@ -23549,12 +23549,12 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -23602,16 +23602,16 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>25547681.59</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -23620,43 +23620,43 @@
         <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>0</v>
+        <v>25155138.67</v>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>49898263.91</v>
       </c>
       <c r="Q166" t="n">
         <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>129341289.91</v>
       </c>
       <c r="S166" t="n">
-        <v>0</v>
+        <v>79232487.98999999</v>
       </c>
       <c r="T166" t="n">
-        <v>0</v>
+        <v>99116487.98999999</v>
       </c>
       <c r="U166" t="n">
-        <v>0</v>
+        <v>79443026</v>
       </c>
       <c r="V166" t="n">
-        <v>0</v>
+        <v>19884000</v>
       </c>
       <c r="W166" t="n">
-        <v>2000</v>
+        <v>79443026</v>
       </c>
       <c r="X166" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="Y166" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Z166" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="AA166" t="n">
-        <v>2000</v>
+        <v>82235403</v>
       </c>
       <c r="AB166" t="n">
         <v>5</v>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="AF166" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG166" t="inlineStr">
@@ -23684,17 +23684,17 @@
       </c>
       <c r="AH166" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
+          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -23737,30 +23737,30 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>33913900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>448000</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>336000</v>
+        <v>0</v>
       </c>
       <c r="P167" t="n">
         <v>0</v>
@@ -23769,25 +23769,25 @@
         <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="T167" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="U167" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
       </c>
       <c r="W167" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="X167" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Y167" t="n">
         <v>0</v>
@@ -23796,7 +23796,7 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="AB167" t="n">
         <v>5</v>
@@ -23814,39 +23814,39 @@
       </c>
       <c r="AF167" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Transferência entre Órgãos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
         </is>
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -23860,24 +23860,24 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F168" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33913900</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -23891,16 +23891,16 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>448000</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="O168" t="n">
-        <v>0</v>
+        <v>336000</v>
       </c>
       <c r="P168" t="n">
         <v>0</v>
@@ -23909,25 +23909,25 @@
         <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="S168" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="T168" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="U168" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
       </c>
       <c r="W168" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="X168" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y168" t="n">
         <v>0</v>
@@ -23936,7 +23936,7 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="AB168" t="n">
         <v>5</v>
@@ -23944,12 +23944,12 @@
       <c r="AC168" t="inlineStr"/>
       <c r="AD168" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -23959,7 +23959,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Transferência entre Órgãos</t>
         </is>
       </c>
       <c r="AH168" t="inlineStr">
@@ -23969,12 +23969,12 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -24064,10 +24064,10 @@
         <v>0</v>
       </c>
       <c r="W169" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="X169" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="Y169" t="n">
         <v>0</v>
@@ -24076,7 +24076,7 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="AB169" t="n">
         <v>5</v>
@@ -24099,7 +24099,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH169" t="inlineStr">
@@ -24109,12 +24109,12 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
+          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -24140,24 +24140,24 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F170" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>DTIC</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -24204,10 +24204,10 @@
         <v>0</v>
       </c>
       <c r="W170" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="X170" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="Y170" t="n">
         <v>0</v>
@@ -24216,7 +24216,7 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="AB170" t="n">
         <v>5</v>
@@ -24224,12 +24224,12 @@
       <c r="AC170" t="inlineStr"/>
       <c r="AD170" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>DTIC - Desenvolvimento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -24239,7 +24239,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH170" t="inlineStr">
@@ -24249,12 +24249,12 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
+          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -24280,24 +24280,24 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F171" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -24307,7 +24307,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L171" t="n">
@@ -24344,10 +24344,10 @@
         <v>0</v>
       </c>
       <c r="W171" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X171" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y171" t="n">
         <v>0</v>
@@ -24356,7 +24356,7 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB171" t="n">
         <v>5</v>
@@ -24364,12 +24364,12 @@
       <c r="AC171" t="inlineStr"/>
       <c r="AD171" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC - Desenvolvimento</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -24379,22 +24379,22 @@
       </c>
       <c r="AG171" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
         </is>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>16/05/2026 07:31:02</t>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>
@@ -24442,16 +24442,16 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>26512660.49</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
         <v>0</v>
@@ -24460,34 +24460,34 @@
         <v>0</v>
       </c>
       <c r="O172" t="n">
-        <v>26316455.82</v>
+        <v>0</v>
       </c>
       <c r="P172" t="n">
-        <v>3563076.37</v>
+        <v>0</v>
       </c>
       <c r="Q172" t="n">
         <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>41134719.61</v>
+        <v>0</v>
       </c>
       <c r="S172" t="n">
-        <v>33672380.41</v>
+        <v>0</v>
       </c>
       <c r="T172" t="n">
-        <v>35285144.51</v>
+        <v>0</v>
       </c>
       <c r="U172" t="n">
-        <v>37571643.24</v>
+        <v>0</v>
       </c>
       <c r="V172" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="W172" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="X172" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="Y172" t="n">
         <v>0</v>
@@ -24496,7 +24496,7 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="AB172" t="n">
         <v>5</v>
@@ -24514,27 +24514,167 @@
       </c>
       <c r="AF172" t="inlineStr">
         <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>18/05/2026 09:46:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>422</v>
+      </c>
+      <c r="F173" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>26512660.49</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>26512660.49</v>
+      </c>
+      <c r="P173" t="n">
+        <v>3945313.07</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="n">
+        <v>41134719.61</v>
+      </c>
+      <c r="S173" t="n">
+        <v>35250309.69</v>
+      </c>
+      <c r="T173" t="n">
+        <v>36863073.79</v>
+      </c>
+      <c r="U173" t="n">
+        <v>37189406.54</v>
+      </c>
+      <c r="V173" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="W173" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X173" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC173" t="inlineStr"/>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
           <t>08 - Recusos Vinculados</t>
         </is>
       </c>
-      <c r="AG172" t="inlineStr">
+      <c r="AG173" t="inlineStr">
         <is>
           <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
-      <c r="AH172" t="inlineStr">
+      <c r="AH173" t="inlineStr">
         <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AI172" t="inlineStr">
+      <c r="AI173" t="inlineStr">
         <is>
           <t>90.10.14.422.4019.6160.33503900.08.1.759.0958</t>
         </is>
       </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>16/05/2026 07:31:02</t>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>18/05/2026 09:46:52</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44477.62</v>
+        <v>51241.62</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1220,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>43033.12</v>
+        <v>42321.12</v>
       </c>
       <c r="P6" t="n">
-        <v>22914.09</v>
+        <v>23626.09</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1232,16 +1232,16 @@
         <v>77359.71000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>44477.62</v>
+        <v>51241.62</v>
       </c>
       <c r="T6" t="n">
-        <v>60191.71</v>
+        <v>67667.71000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>54445.62</v>
+        <v>53733.62</v>
       </c>
       <c r="V6" t="n">
-        <v>15714.09</v>
+        <v>16426.09</v>
       </c>
       <c r="W6" t="n">
         <v>203353</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>40895.11</v>
+        <v>72985.21000000001</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2275961.54</v>
+        <v>2292564.58</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1783,22 +1783,22 @@
         <v>1973590.98</v>
       </c>
       <c r="P10" t="n">
-        <v>1305626.15</v>
+        <v>1368231.55</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>12905283.63</v>
+        <v>13033559.03</v>
       </c>
       <c r="S10" t="n">
-        <v>8409678.279999999</v>
+        <v>8426281.32</v>
       </c>
       <c r="T10" t="n">
-        <v>8533781.869999999</v>
+        <v>8550384.91</v>
       </c>
       <c r="U10" t="n">
-        <v>11599657.48</v>
+        <v>11665327.48</v>
       </c>
       <c r="V10" t="n">
         <v>124103.59</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -2772,10 +2772,10 @@
         <v>81465.10000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>5459</v>
+        <v>33111.44</v>
       </c>
       <c r="T17" t="n">
-        <v>5459</v>
+        <v>33111.44</v>
       </c>
       <c r="U17" t="n">
         <v>71456.17999999999</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1869188.08</v>
+        <v>1875128.53</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -4583,13 +4583,13 @@
         <v>503279.78</v>
       </c>
       <c r="P30" t="n">
-        <v>316170.82</v>
+        <v>349662.34</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2157842.86</v>
+        <v>2191334.38</v>
       </c>
       <c r="S30" t="n">
         <v>1635347.1</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>42156.29</v>
+        <v>55493.73</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>837355.79</v>
+        <v>1097192.23</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>65193.76</v>
+        <v>71684.91</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>9659.959999999999</v>
+        <v>11125.84</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>66000</v>
+        <v>73500</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>96278.44</v>
+        <v>97378.02</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -17731,7 +17731,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>21384.72</v>
+        <v>21712.72</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>70236.35000000001</v>
+        <v>117560.92</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -19709,7 +19709,7 @@
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>95531.96000000001</v>
+        <v>142934.93</v>
       </c>
       <c r="S138" t="n">
         <v>95531.96000000001</v>
@@ -19718,7 +19718,7 @@
         <v>95531.96000000001</v>
       </c>
       <c r="U138" t="n">
-        <v>95531.96000000001</v>
+        <v>142934.93</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -21791,7 +21791,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>4200</v>
+        <v>5400</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>
@@ -24609,7 +24609,7 @@
         <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>41134719.61</v>
+        <v>41834237.08</v>
       </c>
       <c r="S173" t="n">
         <v>35250309.69</v>
@@ -24618,7 +24618,7 @@
         <v>36863073.79</v>
       </c>
       <c r="U173" t="n">
-        <v>37189406.54</v>
+        <v>37888924.01</v>
       </c>
       <c r="V173" t="n">
         <v>1612764.1</v>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>18/05/2026 09:46:52</t>
+          <t>19/05/2026 09:24:17</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51241.62</v>
+        <v>53733.62</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1232,10 +1232,10 @@
         <v>77359.71000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>51241.62</v>
+        <v>53733.62</v>
       </c>
       <c r="T6" t="n">
-        <v>67667.71000000001</v>
+        <v>70159.71000000001</v>
       </c>
       <c r="U6" t="n">
         <v>53733.62</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1363,13 @@
         <v>11982.8</v>
       </c>
       <c r="P7" t="n">
-        <v>96530.67999999999</v>
+        <v>308127.99</v>
       </c>
       <c r="Q7" t="n">
         <v>63262</v>
       </c>
       <c r="R7" t="n">
-        <v>595544.36</v>
+        <v>857683.76</v>
       </c>
       <c r="S7" t="n">
         <v>153487.35</v>
@@ -1378,7 +1378,7 @@
         <v>153487.35</v>
       </c>
       <c r="U7" t="n">
-        <v>499013.68</v>
+        <v>549555.77</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -1780,16 +1780,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1973590.98</v>
+        <v>2017399.27</v>
       </c>
       <c r="P10" t="n">
-        <v>1368231.55</v>
+        <v>1882231.55</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>13033559.03</v>
+        <v>14082116.63</v>
       </c>
       <c r="S10" t="n">
         <v>8426281.32</v>
@@ -1798,7 +1798,7 @@
         <v>8550384.91</v>
       </c>
       <c r="U10" t="n">
-        <v>11665327.48</v>
+        <v>12199885.08</v>
       </c>
       <c r="V10" t="n">
         <v>124103.59</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -4303,13 +4303,13 @@
         <v>13158.64</v>
       </c>
       <c r="P28" t="n">
-        <v>42067.8</v>
+        <v>137870.4</v>
       </c>
       <c r="Q28" t="n">
         <v>2308</v>
       </c>
       <c r="R28" t="n">
-        <v>610820.98</v>
+        <v>744214.34</v>
       </c>
       <c r="S28" t="n">
         <v>329040.58</v>
@@ -4318,7 +4318,7 @@
         <v>329040.58</v>
       </c>
       <c r="U28" t="n">
-        <v>568753.1800000001</v>
+        <v>606343.9399999999</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -4863,25 +4863,25 @@
         <v>3543371.61</v>
       </c>
       <c r="P32" t="n">
-        <v>800034.36</v>
+        <v>1273689.24</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>18626200.63</v>
+        <v>19159774.07</v>
       </c>
       <c r="S32" t="n">
-        <v>16984300.52</v>
+        <v>16550727.08</v>
       </c>
       <c r="T32" t="n">
         <v>16990873.17</v>
       </c>
       <c r="U32" t="n">
-        <v>17826166.27</v>
+        <v>17886084.83</v>
       </c>
       <c r="V32" t="n">
-        <v>6572.65</v>
+        <v>440146.09</v>
       </c>
       <c r="W32" t="n">
         <v>17954344</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>146687.82</v>
+        <v>166495.2</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>124605.95</v>
+        <v>124940.79</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -6403,13 +6403,13 @@
         <v>4106.28</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="Q43" t="n">
         <v>22671</v>
       </c>
       <c r="R43" t="n">
-        <v>118525.12</v>
+        <v>210635.23</v>
       </c>
       <c r="S43" t="n">
         <v>50187</v>
@@ -6418,7 +6418,7 @@
         <v>54123</v>
       </c>
       <c r="U43" t="n">
-        <v>118525.12</v>
+        <v>143635.23</v>
       </c>
       <c r="V43" t="n">
         <v>3936</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -6680,16 +6680,16 @@
         <v>93886</v>
       </c>
       <c r="O45" t="n">
-        <v>1156730.37</v>
+        <v>1172486.08</v>
       </c>
       <c r="P45" t="n">
-        <v>615163.5600000001</v>
+        <v>983604</v>
       </c>
       <c r="Q45" t="n">
         <v>1186346</v>
       </c>
       <c r="R45" t="n">
-        <v>15333661.41</v>
+        <v>15702101.85</v>
       </c>
       <c r="S45" t="n">
         <v>5295350.24</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>71684.91</v>
+        <v>72406.46000000001</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -13957,7 +13957,7 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2300000</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13984,7 +13984,7 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>2300000</v>
       </c>
       <c r="X97" t="n">
         <v>0</v>
@@ -13996,7 +13996,7 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2300000</v>
       </c>
       <c r="AB97" t="n">
         <v>5</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -14237,7 +14237,7 @@
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -14264,7 +14264,7 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="X99" t="n">
         <v>0</v>
@@ -14276,7 +14276,7 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="AB99" t="n">
         <v>5</v>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -17743,13 +17743,13 @@
         <v>21384.72</v>
       </c>
       <c r="P124" t="n">
-        <v>55391.15</v>
+        <v>152391.15</v>
       </c>
       <c r="Q124" t="n">
         <v>8077</v>
       </c>
       <c r="R124" t="n">
-        <v>307882.16</v>
+        <v>452429.18</v>
       </c>
       <c r="S124" t="n">
         <v>33311.56</v>
@@ -17758,7 +17758,7 @@
         <v>33311.56</v>
       </c>
       <c r="U124" t="n">
-        <v>252491.01</v>
+        <v>300038.03</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -18023,13 +18023,13 @@
         <v>808907.3100000001</v>
       </c>
       <c r="P126" t="n">
-        <v>2102872.47</v>
+        <v>2580572.47</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>5741562.6</v>
+        <v>6319750.68</v>
       </c>
       <c r="S126" t="n">
         <v>2711399.82</v>
@@ -18038,7 +18038,7 @@
         <v>2711719.82</v>
       </c>
       <c r="U126" t="n">
-        <v>3638690.13</v>
+        <v>3739178.21</v>
       </c>
       <c r="V126" t="n">
         <v>320</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -19137,7 +19137,7 @@
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -19164,7 +19164,7 @@
         <v>0</v>
       </c>
       <c r="W134" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="X134" t="n">
         <v>0</v>
@@ -19176,7 +19176,7 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AB134" t="n">
         <v>5</v>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23060,7 @@
         <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>89675298.11</v>
+        <v>90332993.66</v>
       </c>
       <c r="P162" t="n">
         <v>21043600.09</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>19/05/2026 09:24:17</t>
+          <t>20/05/2026 08:59:29</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>42321.12</v>
+        <v>43765.62</v>
       </c>
       <c r="P6" t="n">
         <v>23626.09</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>57410.34</v>
+        <v>86115.50999999999</v>
       </c>
       <c r="P9" t="n">
         <v>106.92</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2017399.27</v>
+        <v>2197197.16</v>
       </c>
       <c r="P10" t="n">
         <v>1882231.55</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1418495.21</v>
+        <v>1422719.21</v>
       </c>
       <c r="P20" t="n">
         <v>3125692.73</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>503279.78</v>
+        <v>652000.73</v>
       </c>
       <c r="P30" t="n">
-        <v>349662.34</v>
+        <v>370669.45</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2191334.38</v>
+        <v>2212341.49</v>
       </c>
       <c r="S30" t="n">
         <v>1635347.1</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>907411.4399999999</v>
+        <v>1346253.6</v>
       </c>
       <c r="P31" t="n">
         <v>2164954.67</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3543371.61</v>
+        <v>3857898.7</v>
       </c>
       <c r="P32" t="n">
         <v>1273689.24</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>166495.2</v>
+        <v>166720.91</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>837355.79</v>
+        <v>1097192.23</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
         <v>131526</v>
       </c>
       <c r="O43" t="n">
-        <v>4106.28</v>
+        <v>4434.28</v>
       </c>
       <c r="P43" t="n">
         <v>67000</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
         <v>650000</v>
       </c>
       <c r="O44" t="n">
-        <v>229579.78</v>
+        <v>344369.67</v>
       </c>
       <c r="P44" t="n">
         <v>406043.22</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1275719.01</v>
+        <v>1291519.01</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6680,7 +6680,7 @@
         <v>93886</v>
       </c>
       <c r="O45" t="n">
-        <v>1172486.08</v>
+        <v>1198264.31</v>
       </c>
       <c r="P45" t="n">
         <v>983604</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>6028997.25</v>
+        <v>6506007.82</v>
       </c>
       <c r="P50" t="n">
         <v>4140329.7</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7520,7 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>44357.8</v>
+        <v>66536.7</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>13052.54</v>
+        <v>19578.81</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -16209,7 +16209,7 @@
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>19646</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -16218,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>19646</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -16352,10 +16352,10 @@
         <v>8863680.02</v>
       </c>
       <c r="S114" t="n">
-        <v>842141.71</v>
+        <v>889621.71</v>
       </c>
       <c r="T114" t="n">
-        <v>842141.71</v>
+        <v>889621.71</v>
       </c>
       <c r="U114" t="n">
         <v>8303680.02</v>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -16620,7 +16620,7 @@
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>13052.54</v>
+        <v>19578.81</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>57410.34</v>
+        <v>86115.50999999999</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -17743,13 +17743,13 @@
         <v>21384.72</v>
       </c>
       <c r="P124" t="n">
-        <v>152391.15</v>
+        <v>266833</v>
       </c>
       <c r="Q124" t="n">
         <v>8077</v>
       </c>
       <c r="R124" t="n">
-        <v>452429.18</v>
+        <v>585048.1800000001</v>
       </c>
       <c r="S124" t="n">
         <v>33311.56</v>
@@ -17758,7 +17758,7 @@
         <v>33311.56</v>
       </c>
       <c r="U124" t="n">
-        <v>300038.03</v>
+        <v>318215.18</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -19700,7 +19700,7 @@
         <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>40338.4</v>
+        <v>51451.2</v>
       </c>
       <c r="P138" t="n">
         <v>0</v>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -19840,7 +19840,7 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>256624.5</v>
+        <v>370073.19</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1011239.26</v>
+        <v>1038010.32</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>132386.98</v>
+        <v>169051.15</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -21800,7 +21800,7 @@
         <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="P153" t="n">
         <v>11400</v>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23060,7 @@
         <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>90332993.66</v>
+        <v>90456591.02</v>
       </c>
       <c r="P162" t="n">
         <v>21043600.09</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -23480,7 +23480,7 @@
         <v>0</v>
       </c>
       <c r="O165" t="n">
-        <v>32341444.51</v>
+        <v>34703144.51</v>
       </c>
       <c r="P165" t="n">
         <v>60670522</v>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>25547681.59</v>
+        <v>26807681.59</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -23900,7 +23900,7 @@
         <v>1406720</v>
       </c>
       <c r="O168" t="n">
-        <v>336000</v>
+        <v>448000</v>
       </c>
       <c r="P168" t="n">
         <v>0</v>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>
@@ -24609,7 +24609,7 @@
         <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>41834237.08</v>
+        <v>42041812.47</v>
       </c>
       <c r="S173" t="n">
         <v>35250309.69</v>
@@ -24618,7 +24618,7 @@
         <v>36863073.79</v>
       </c>
       <c r="U173" t="n">
-        <v>37888924.01</v>
+        <v>38096499.4</v>
       </c>
       <c r="V173" t="n">
         <v>1612764.1</v>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>20/05/2026 08:59:29</t>
+          <t>21/05/2026 09:31:29</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53733.62</v>
+        <v>60940.47</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1229,16 +1229,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>77359.71000000001</v>
+        <v>84566.56</v>
       </c>
       <c r="S6" t="n">
-        <v>53733.62</v>
+        <v>60940.47</v>
       </c>
       <c r="T6" t="n">
-        <v>70159.71000000001</v>
+        <v>77366.56</v>
       </c>
       <c r="U6" t="n">
-        <v>53733.62</v>
+        <v>60940.47</v>
       </c>
       <c r="V6" t="n">
         <v>16426.09</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>10000.06</v>
+        <v>68464.06</v>
       </c>
       <c r="Q24" t="n">
         <v>50000</v>
@@ -3758,7 +3758,7 @@
         <v>6040.6</v>
       </c>
       <c r="U24" t="n">
-        <v>65842.36</v>
+        <v>7378.36</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>652251.36</v>
+        <v>652361.33</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4042025.11</v>
+        <v>4042735.41</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
         <v>93886</v>
       </c>
       <c r="O45" t="n">
-        <v>1198264.31</v>
+        <v>1210264.31</v>
       </c>
       <c r="P45" t="n">
         <v>983604</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9784,7 +9784,7 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="X67" t="n">
         <v>0</v>
@@ -9796,7 +9796,7 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="AB67" t="n">
         <v>5</v>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -10758,7 +10758,7 @@
         <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>45000</v>
+        <v>49500</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>8373</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -14818,7 +14818,7 @@
         <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>8373</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -16340,7 +16340,7 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>386071.33</v>
+        <v>399585.19</v>
       </c>
       <c r="P114" t="n">
         <v>560000</v>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -17743,19 +17743,19 @@
         <v>21384.72</v>
       </c>
       <c r="P124" t="n">
-        <v>266833</v>
+        <v>312620.48</v>
       </c>
       <c r="Q124" t="n">
         <v>8077</v>
       </c>
       <c r="R124" t="n">
-        <v>585048.1800000001</v>
+        <v>630835.66</v>
       </c>
       <c r="S124" t="n">
-        <v>33311.56</v>
+        <v>79099.03999999999</v>
       </c>
       <c r="T124" t="n">
-        <v>33311.56</v>
+        <v>79099.03999999999</v>
       </c>
       <c r="U124" t="n">
         <v>318215.18</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -18857,7 +18857,7 @@
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>428000</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -18884,7 +18884,7 @@
         <v>0</v>
       </c>
       <c r="W132" t="n">
-        <v>0</v>
+        <v>428000</v>
       </c>
       <c r="X132" t="n">
         <v>0</v>
@@ -18896,7 +18896,7 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>428000</v>
       </c>
       <c r="AB132" t="n">
         <v>5</v>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -19137,7 +19137,7 @@
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -19164,7 +19164,7 @@
         <v>0</v>
       </c>
       <c r="W134" t="n">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="X134" t="n">
         <v>0</v>
@@ -19176,7 +19176,7 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="AB134" t="n">
         <v>5</v>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1038010.32</v>
+        <v>1038130.12</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>169051.15</v>
+        <v>169230.85</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -21791,7 +21791,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>5400</v>
+        <v>7200</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -21800,7 +21800,7 @@
         <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="P153" t="n">
         <v>11400</v>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>26807681.59</v>
+        <v>30137681.59</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -23620,7 +23620,7 @@
         <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>25155138.67</v>
+        <v>25306603.06</v>
       </c>
       <c r="P166" t="n">
         <v>49898263.91</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>21/05/2026 09:31:29</t>
+          <t>22/05/2026 08:56:49</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>43765.62</v>
+        <v>53733.62</v>
       </c>
       <c r="P6" t="n">
         <v>23626.09</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>60379.3</v>
+        <v>67683.7</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>72985.21000000001</v>
+        <v>88500.49000000001</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>115966</v>
       </c>
       <c r="O8" t="n">
-        <v>39666.86</v>
+        <v>71756.96000000001</v>
       </c>
       <c r="P8" t="n">
         <v>181083.4</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2292564.58</v>
+        <v>2295230.63</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2197197.16</v>
+        <v>2213800.2</v>
       </c>
       <c r="P10" t="n">
         <v>1882231.55</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49262.3</v>
+        <v>49337.3</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1422719.21</v>
+        <v>1456839.07</v>
       </c>
       <c r="P20" t="n">
         <v>3125692.73</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>652361.33</v>
+        <v>659505.4</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4042735.41</v>
+        <v>4043127.4</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>166720.91</v>
+        <v>171270.71</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>124940.79</v>
+        <v>129705.73</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4434.28</v>
+        <v>4762.28</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1291519.01</v>
+        <v>1291588.11</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6680,7 +6680,7 @@
         <v>93886</v>
       </c>
       <c r="O45" t="n">
-        <v>1210264.31</v>
+        <v>1263773.13</v>
       </c>
       <c r="P45" t="n">
         <v>983604</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -8664,7 +8664,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="X59" t="n">
         <v>200000</v>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>700000</v>
+        <v>1050000</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="X63" t="n">
         <v>350000</v>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>46172.22</v>
+        <v>46241.32</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3589.39</v>
+        <v>3739.39</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -15080,7 +15080,7 @@
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>3416080.98</v>
+        <v>4418871.33</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>97378.02</v>
+        <v>97447.12</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>15685.63</v>
+        <v>16132.17</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -17743,13 +17743,13 @@
         <v>21384.72</v>
       </c>
       <c r="P124" t="n">
-        <v>312620.48</v>
+        <v>411380.02</v>
       </c>
       <c r="Q124" t="n">
         <v>8077</v>
       </c>
       <c r="R124" t="n">
-        <v>630835.66</v>
+        <v>737135.02</v>
       </c>
       <c r="S124" t="n">
         <v>79099.03999999999</v>
@@ -17758,7 +17758,7 @@
         <v>79099.03999999999</v>
       </c>
       <c r="U124" t="n">
-        <v>318215.18</v>
+        <v>325755</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>854277.5699999999</v>
+        <v>854484.87</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -18020,7 +18020,7 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>808907.3100000001</v>
+        <v>852219.98</v>
       </c>
       <c r="P126" t="n">
         <v>2580572.47</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1038130.12</v>
+        <v>1063883.12</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -19980,7 +19980,7 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>982655.9300000001</v>
+        <v>1011239.26</v>
       </c>
       <c r="P140" t="n">
         <v>743505.8100000001</v>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>220000</v>
+        <v>329000</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
@@ -20424,7 +20424,7 @@
         <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>0</v>
+        <v>109000</v>
       </c>
       <c r="X143" t="n">
         <v>110000</v>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>169230.85</v>
+        <v>169265.4</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>90456591.02</v>
+        <v>90570908.59999999</v>
       </c>
       <c r="M162" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -23471,7 +23471,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>38488734.91</v>
+        <v>40147923.71</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>30137681.59</v>
+        <v>30857681.59</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>22/05/2026 08:56:49</t>
+          <t>23/05/2026 07:49:44</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>23/05/2026 07:49:44</t>
+          <t>24/05/2026 07:51:58</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ173"/>
+  <dimension ref="A1:AJ176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -18557,17 +18557,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>44905200</t>
+          <t>33909300</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -18607,16 +18607,16 @@
         <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
         <v>5</v>
@@ -18634,27 +18634,27 @@
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>02 - Transferências Federais</t>
         </is>
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>Aquisição de Material Permanente</t>
+          <t>Indenizações e Restituições</t>
         </is>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC/CONVÊNIO SICONV nº 835820/2016</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.2053.44905200.00.1.500.9001</t>
+          <t>34.10.14.422.4025.2053.33909300.02.1.700.1147</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -18697,17 +18697,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33909300</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -18717,7 +18717,7 @@
         <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -18744,7 +18744,7 @@
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="X131" t="n">
         <v>0</v>
@@ -18756,7 +18756,7 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
         <v>5</v>
@@ -18769,32 +18769,32 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>CPM - Políticas</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>02 - Transferências Federais</t>
         </is>
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Indenizações e Restituições</t>
         </is>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - André Santos</t>
+          <t>PMSP-SMDHC/CONVÊNIO SICONV nº 835820/2016</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7007</t>
+          <t>34.10.14.422.4025.2053.33909300.02.2.700.1147</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -18837,7 +18837,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44905200</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -18847,7 +18847,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -18857,7 +18857,7 @@
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>428000</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -18884,19 +18884,19 @@
         <v>0</v>
       </c>
       <c r="W132" t="n">
-        <v>428000</v>
+        <v>0</v>
       </c>
       <c r="X132" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z132" t="n">
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>428000</v>
+        <v>10000</v>
       </c>
       <c r="AB132" t="n">
         <v>5</v>
@@ -18909,7 +18909,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>CPM - Políticas</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -18919,22 +18919,22 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Aquisição de Material Permanente</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Senival Moura</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7048</t>
+          <t>34.10.14.422.4025.2053.44905200.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -18997,7 +18997,7 @@
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>57000</v>
+        <v>200000</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -19024,7 +19024,7 @@
         <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>57000</v>
+        <v>200000</v>
       </c>
       <c r="X133" t="n">
         <v>0</v>
@@ -19036,7 +19036,7 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>57000</v>
+        <v>200000</v>
       </c>
       <c r="AB133" t="n">
         <v>5</v>
@@ -19064,17 +19064,17 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Kenji Ito</t>
+          <t>Emendas Parlamentares - André Santos</t>
         </is>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7007</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -19127,7 +19127,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -19137,7 +19137,7 @@
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>460000</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -19164,7 +19164,7 @@
         <v>0</v>
       </c>
       <c r="W134" t="n">
-        <v>460000</v>
+        <v>0</v>
       </c>
       <c r="X134" t="n">
         <v>0</v>
@@ -19176,7 +19176,7 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>460000</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
         <v>5</v>
@@ -19204,17 +19204,17 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Lucas Pavanato</t>
+          <t>Emendas Parlamentares - Luna</t>
         </is>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33503900.00.1.500.7077</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7027</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -19267,56 +19267,56 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>3919200</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>428000</v>
       </c>
       <c r="O135" t="n">
-        <v>3919200</v>
+        <v>0</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
-        <v>3984000</v>
+        <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>4763600</v>
+        <v>0</v>
       </c>
       <c r="U135" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="V135" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="W135" t="n">
-        <v>8578400</v>
+        <v>428000</v>
       </c>
       <c r="X135" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>1421600</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>1294560.33</v>
+        <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>8705439.67</v>
+        <v>428000</v>
       </c>
       <c r="AB135" t="n">
         <v>5</v>
@@ -19339,22 +19339,22 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Senival Moura</t>
         </is>
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7048</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -19387,7 +19387,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -19407,47 +19407,47 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>19041664.7</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="O136" t="n">
-        <v>19041664.7</v>
+        <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>1425517.51</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>23851875.51</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>21926109.23</v>
+        <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>22593123.43</v>
+        <v>0</v>
       </c>
       <c r="U136" t="n">
-        <v>22426358</v>
+        <v>0</v>
       </c>
       <c r="V136" t="n">
-        <v>667014.2</v>
+        <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>22426358</v>
+        <v>57000</v>
       </c>
       <c r="X136" t="n">
-        <v>22426358</v>
+        <v>0</v>
       </c>
       <c r="Y136" t="n">
         <v>0</v>
@@ -19456,7 +19456,7 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>22426358</v>
+        <v>57000</v>
       </c>
       <c r="AB136" t="n">
         <v>5</v>
@@ -19469,7 +19469,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -19484,17 +19484,17 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Kenji Ito</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7076</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -19527,7 +19527,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -19537,7 +19537,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -19547,47 +19547,47 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>64653</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>52998</v>
+        <v>460000</v>
       </c>
       <c r="O137" t="n">
-        <v>64653</v>
+        <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>7647.82</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>226677.94</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>143901.12</v>
+        <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>145695.12</v>
+        <v>0</v>
       </c>
       <c r="U137" t="n">
-        <v>219030.12</v>
+        <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>1794</v>
+        <v>0</v>
       </c>
       <c r="W137" t="n">
-        <v>252998</v>
+        <v>460000</v>
       </c>
       <c r="X137" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="Y137" t="n">
         <v>0</v>
@@ -19596,7 +19596,7 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>252998</v>
+        <v>460000</v>
       </c>
       <c r="AB137" t="n">
         <v>5</v>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -19619,22 +19619,22 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Lucas Pavanato</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33503900.00.1.500.7077</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -19691,7 +19691,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>51451.2</v>
+        <v>3919200</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -19700,43 +19700,43 @@
         <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>51451.2</v>
+        <v>3919200</v>
       </c>
       <c r="P138" t="n">
         <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="R138" t="n">
-        <v>142934.93</v>
+        <v>8578400</v>
       </c>
       <c r="S138" t="n">
-        <v>95531.96000000001</v>
+        <v>3984000</v>
       </c>
       <c r="T138" t="n">
-        <v>95531.96000000001</v>
+        <v>4763600</v>
       </c>
       <c r="U138" t="n">
-        <v>142934.93</v>
+        <v>8578400</v>
       </c>
       <c r="V138" t="n">
-        <v>0</v>
+        <v>779600</v>
       </c>
       <c r="W138" t="n">
-        <v>250000</v>
+        <v>8578400</v>
       </c>
       <c r="X138" t="n">
-        <v>250000</v>
+        <v>10000000</v>
       </c>
       <c r="Y138" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Z138" t="n">
-        <v>0</v>
+        <v>1294560.33</v>
       </c>
       <c r="AA138" t="n">
-        <v>250000</v>
+        <v>8705439.67</v>
       </c>
       <c r="AB138" t="n">
         <v>5</v>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AH138" t="inlineStr">
@@ -19769,12 +19769,12 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4025.4329.33904800.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -19831,7 +19831,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>370073.19</v>
+        <v>19041664.7</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -19840,34 +19840,34 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>370073.19</v>
+        <v>19041664.7</v>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1425517.51</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>2537927</v>
+        <v>23851875.51</v>
       </c>
       <c r="S139" t="n">
-        <v>1064838.18</v>
+        <v>21926109.23</v>
       </c>
       <c r="T139" t="n">
-        <v>1131764.02</v>
+        <v>22593123.43</v>
       </c>
       <c r="U139" t="n">
-        <v>2537927</v>
+        <v>22426358</v>
       </c>
       <c r="V139" t="n">
-        <v>66925.84</v>
+        <v>667014.2</v>
       </c>
       <c r="W139" t="n">
-        <v>2537927</v>
+        <v>22426358</v>
       </c>
       <c r="X139" t="n">
-        <v>2537927</v>
+        <v>22426358</v>
       </c>
       <c r="Y139" t="n">
         <v>0</v>
@@ -19876,7 +19876,7 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>2537927</v>
+        <v>22426358</v>
       </c>
       <c r="AB139" t="n">
         <v>5</v>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH139" t="inlineStr">
@@ -19909,12 +19909,12 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -19971,52 +19971,52 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1063883.12</v>
+        <v>64653</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>52998</v>
       </c>
       <c r="O140" t="n">
-        <v>1011239.26</v>
+        <v>64653</v>
       </c>
       <c r="P140" t="n">
-        <v>743505.8100000001</v>
+        <v>7647.82</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>3802648.2</v>
+        <v>226677.94</v>
       </c>
       <c r="S140" t="n">
-        <v>2409038.89</v>
+        <v>143901.12</v>
       </c>
       <c r="T140" t="n">
-        <v>2502957.88</v>
+        <v>145695.12</v>
       </c>
       <c r="U140" t="n">
-        <v>3059142.39</v>
+        <v>219030.12</v>
       </c>
       <c r="V140" t="n">
-        <v>93918.99000000001</v>
+        <v>1794</v>
       </c>
       <c r="W140" t="n">
-        <v>4104655</v>
+        <v>252998</v>
       </c>
       <c r="X140" t="n">
-        <v>4806049</v>
+        <v>200000</v>
       </c>
       <c r="Y140" t="n">
-        <v>63262</v>
+        <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>638132</v>
+        <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>4167917</v>
+        <v>252998</v>
       </c>
       <c r="AB140" t="n">
         <v>5</v>
@@ -20039,7 +20039,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH140" t="inlineStr">
@@ -20049,12 +20049,12 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -20097,7 +20097,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -20107,11 +20107,11 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>368.19</v>
+        <v>51451.2</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -20120,7 +20120,7 @@
         <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>312.26</v>
+        <v>51451.2</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
@@ -20129,25 +20129,25 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>80100</v>
+        <v>142934.93</v>
       </c>
       <c r="S141" t="n">
-        <v>73100</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="T141" t="n">
-        <v>80100</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="U141" t="n">
-        <v>80100</v>
+        <v>142934.93</v>
       </c>
       <c r="V141" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>139282</v>
+        <v>250000</v>
       </c>
       <c r="X141" t="n">
-        <v>139282</v>
+        <v>250000</v>
       </c>
       <c r="Y141" t="n">
         <v>0</v>
@@ -20156,7 +20156,7 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>139282</v>
+        <v>250000</v>
       </c>
       <c r="AB141" t="n">
         <v>5</v>
@@ -20179,22 +20179,22 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4025.6178.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -20251,7 +20251,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>7871.4</v>
+        <v>370073.19</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -20260,7 +20260,7 @@
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>7871.4</v>
+        <v>370073.19</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
@@ -20269,25 +20269,25 @@
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>19678.5</v>
+        <v>2537927</v>
       </c>
       <c r="S142" t="n">
-        <v>19678.5</v>
+        <v>1064838.18</v>
       </c>
       <c r="T142" t="n">
-        <v>19678.5</v>
+        <v>1131764.02</v>
       </c>
       <c r="U142" t="n">
-        <v>19678.5</v>
+        <v>2537927</v>
       </c>
       <c r="V142" t="n">
-        <v>0</v>
+        <v>66925.84</v>
       </c>
       <c r="W142" t="n">
-        <v>49000</v>
+        <v>2537927</v>
       </c>
       <c r="X142" t="n">
-        <v>49000</v>
+        <v>2537927</v>
       </c>
       <c r="Y142" t="n">
         <v>0</v>
@@ -20296,7 +20296,7 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>49000</v>
+        <v>2537927</v>
       </c>
       <c r="AB142" t="n">
         <v>5</v>
@@ -20319,7 +20319,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
@@ -20329,12 +20329,12 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -20367,17 +20367,17 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -20391,7 +20391,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1063883.12</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
@@ -20400,43 +20400,43 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>1011239.26</v>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>743505.8100000001</v>
       </c>
       <c r="Q143" t="n">
-        <v>329000</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>3802648.2</v>
       </c>
       <c r="S143" t="n">
-        <v>0</v>
+        <v>2409038.89</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>2502957.88</v>
       </c>
       <c r="U143" t="n">
-        <v>0</v>
+        <v>3059142.39</v>
       </c>
       <c r="V143" t="n">
-        <v>0</v>
+        <v>93918.99000000001</v>
       </c>
       <c r="W143" t="n">
-        <v>109000</v>
+        <v>4104655</v>
       </c>
       <c r="X143" t="n">
-        <v>110000</v>
+        <v>4806049</v>
       </c>
       <c r="Y143" t="n">
-        <v>330000</v>
+        <v>63262</v>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>638132</v>
       </c>
       <c r="AA143" t="n">
-        <v>110000</v>
+        <v>4167917</v>
       </c>
       <c r="AB143" t="n">
         <v>5</v>
@@ -20444,12 +20444,12 @@
       <c r="AC143" t="inlineStr"/>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -20459,7 +20459,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH143" t="inlineStr">
@@ -20469,12 +20469,12 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -20507,17 +20507,17 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -20527,11 +20527,11 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>368.19</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -20540,43 +20540,43 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>312.26</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>80100</v>
       </c>
       <c r="S144" t="n">
-        <v>0</v>
+        <v>73100</v>
       </c>
       <c r="T144" t="n">
-        <v>0</v>
+        <v>80100</v>
       </c>
       <c r="U144" t="n">
-        <v>0</v>
+        <v>80100</v>
       </c>
       <c r="V144" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="W144" t="n">
-        <v>0</v>
+        <v>139282</v>
       </c>
       <c r="X144" t="n">
-        <v>100000</v>
+        <v>139282</v>
       </c>
       <c r="Y144" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="Z144" t="n">
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>100000</v>
+        <v>139282</v>
       </c>
       <c r="AB144" t="n">
         <v>5</v>
@@ -20584,12 +20584,12 @@
       <c r="AC144" t="inlineStr"/>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -20599,22 +20599,22 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -20647,17 +20647,17 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -20671,7 +20671,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>7871.4</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -20680,43 +20680,43 @@
         <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>7871.4</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S145" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U145" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="X145" t="n">
-        <v>75000</v>
+        <v>49000</v>
       </c>
       <c r="Y145" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="AB145" t="n">
         <v>5</v>
@@ -20724,12 +20724,12 @@
       <c r="AC145" t="inlineStr"/>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AH145" t="inlineStr">
@@ -20749,12 +20749,12 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.6178.33904700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -20783,21 +20783,21 @@
         <v>422</v>
       </c>
       <c r="F146" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -20826,7 +20826,7 @@
         <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>329000</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
@@ -20844,19 +20844,19 @@
         <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>11949</v>
+        <v>109000</v>
       </c>
       <c r="X146" t="n">
-        <v>11949</v>
+        <v>110000</v>
       </c>
       <c r="Y146" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="Z146" t="n">
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>11949</v>
+        <v>110000</v>
       </c>
       <c r="AB146" t="n">
         <v>5</v>
@@ -20864,12 +20864,12 @@
       <c r="AC146" t="inlineStr"/>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>CPIR - Políticas</t>
+          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH146" t="inlineStr">
@@ -20889,12 +20889,12 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9027.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -20923,16 +20923,16 @@
         <v>422</v>
       </c>
       <c r="F147" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -20951,7 +20951,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>3595409.86</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -20960,43 +20960,43 @@
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>3595409.86</v>
+        <v>0</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>127000</v>
+        <v>200000</v>
       </c>
       <c r="R147" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="U147" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>3596273</v>
+        <v>0</v>
       </c>
       <c r="X147" t="n">
-        <v>6455492</v>
+        <v>100000</v>
       </c>
       <c r="Y147" t="n">
-        <v>2986219</v>
+        <v>300000</v>
       </c>
       <c r="Z147" t="n">
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>6455492</v>
+        <v>100000</v>
       </c>
       <c r="AB147" t="n">
         <v>5</v>
@@ -21004,12 +21004,12 @@
       <c r="AC147" t="inlineStr"/>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -21029,12 +21029,12 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9030.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -21063,21 +21063,21 @@
         <v>422</v>
       </c>
       <c r="F148" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -21106,7 +21106,7 @@
         <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
@@ -21124,19 +21124,19 @@
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>5374</v>
+        <v>0</v>
       </c>
       <c r="X148" t="n">
-        <v>10000</v>
+        <v>75000</v>
       </c>
       <c r="Y148" t="n">
-        <v>4626</v>
+        <v>75000</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA148" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
         <v>5</v>
@@ -21144,12 +21144,12 @@
       <c r="AC148" t="inlineStr"/>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
@@ -21169,12 +21169,12 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
+          <t>34.10.14.422.4025.9044.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -21264,19 +21264,19 @@
         <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>80612</v>
+        <v>11949</v>
       </c>
       <c r="X149" t="n">
-        <v>150000</v>
+        <v>11949</v>
       </c>
       <c r="Y149" t="n">
-        <v>69388</v>
+        <v>0</v>
       </c>
       <c r="Z149" t="n">
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>150000</v>
+        <v>11949</v>
       </c>
       <c r="AB149" t="n">
         <v>5</v>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH149" t="inlineStr">
@@ -21309,12 +21309,12 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4327.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>169265.4</v>
+        <v>3595409.86</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -21380,43 +21380,43 @@
         <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>132386.98</v>
+        <v>3595409.86</v>
       </c>
       <c r="P150" t="n">
-        <v>551.08</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="R150" t="n">
-        <v>5040463.02</v>
+        <v>3595409.87</v>
       </c>
       <c r="S150" t="n">
-        <v>570925.76</v>
+        <v>3595409.87</v>
       </c>
       <c r="T150" t="n">
-        <v>570925.76</v>
+        <v>3595409.87</v>
       </c>
       <c r="U150" t="n">
-        <v>5039911.94</v>
+        <v>3595409.87</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>5870981</v>
+        <v>3596273</v>
       </c>
       <c r="X150" t="n">
-        <v>10925362</v>
+        <v>6455492</v>
       </c>
       <c r="Y150" t="n">
-        <v>5054381</v>
+        <v>2986219</v>
       </c>
       <c r="Z150" t="n">
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>10925362</v>
+        <v>6455492</v>
       </c>
       <c r="AB150" t="n">
         <v>5</v>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH150" t="inlineStr">
@@ -21449,12 +21449,12 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -21497,7 +21497,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -21507,11 +21507,11 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>76.61</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -21520,43 +21520,43 @@
         <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>76.61</v>
+        <v>0</v>
       </c>
       <c r="P151" t="n">
-        <v>925</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="U151" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>1000</v>
+        <v>5374</v>
       </c>
       <c r="X151" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="Y151" t="n">
-        <v>0</v>
+        <v>4626</v>
       </c>
       <c r="Z151" t="n">
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AB151" t="n">
         <v>5</v>
@@ -21579,22 +21579,22 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
+          <t>34.10.14.422.4026.4334.33903100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -21627,17 +21627,17 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -21666,7 +21666,7 @@
         <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
@@ -21684,19 +21684,19 @@
         <v>0</v>
       </c>
       <c r="W152" t="n">
-        <v>0</v>
+        <v>80612</v>
       </c>
       <c r="X152" t="n">
-        <v>75000</v>
+        <v>150000</v>
       </c>
       <c r="Y152" t="n">
-        <v>75000</v>
+        <v>69388</v>
       </c>
       <c r="Z152" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AB152" t="n">
         <v>5</v>
@@ -21704,12 +21704,12 @@
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
@@ -21729,12 +21729,12 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903700.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -21760,24 +21760,24 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F153" t="n">
         <v>4026</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -21791,7 +21791,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>7200</v>
+        <v>169265.4</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -21800,43 +21800,43 @@
         <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>3600</v>
+        <v>132386.98</v>
       </c>
       <c r="P153" t="n">
-        <v>11400</v>
+        <v>551.08</v>
       </c>
       <c r="Q153" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>21600</v>
+        <v>5040463.02</v>
       </c>
       <c r="S153" t="n">
-        <v>9600</v>
+        <v>570925.76</v>
       </c>
       <c r="T153" t="n">
-        <v>9600</v>
+        <v>570925.76</v>
       </c>
       <c r="U153" t="n">
-        <v>10200</v>
+        <v>5039911.94</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>22143</v>
+        <v>5870981</v>
       </c>
       <c r="X153" t="n">
-        <v>46881</v>
+        <v>10925362</v>
       </c>
       <c r="Y153" t="n">
-        <v>39738</v>
+        <v>5054381</v>
       </c>
       <c r="Z153" t="n">
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>46881</v>
+        <v>10925362</v>
       </c>
       <c r="AB153" t="n">
         <v>5</v>
@@ -21844,12 +21844,12 @@
       <c r="AC153" t="inlineStr"/>
       <c r="AD153" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>COPIND - Políticas</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -21859,7 +21859,7 @@
       </c>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH153" t="inlineStr">
@@ -21869,12 +21869,12 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -21900,19 +21900,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F154" t="n">
         <v>4026</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -21927,11 +21927,11 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>76.61</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -21940,43 +21940,43 @@
         <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>76.61</v>
       </c>
       <c r="P154" t="n">
-        <v>19140.97</v>
+        <v>925</v>
       </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>52809.97</v>
+        <v>1900</v>
       </c>
       <c r="S154" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="T154" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="U154" t="n">
-        <v>33669</v>
+        <v>975</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>33669</v>
+        <v>1000</v>
       </c>
       <c r="X154" t="n">
-        <v>220966</v>
+        <v>1000</v>
       </c>
       <c r="Y154" t="n">
-        <v>187297</v>
+        <v>0</v>
       </c>
       <c r="Z154" t="n">
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>220966</v>
+        <v>1000</v>
       </c>
       <c r="AB154" t="n">
         <v>5</v>
@@ -21984,12 +21984,12 @@
       <c r="AC154" t="inlineStr"/>
       <c r="AD154" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>COPIND - Políticas</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -22004,17 +22004,17 @@
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.4334.33903900.00.1.500.9006</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -22040,14 +22040,14 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F155" t="n">
         <v>4026</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -22086,7 +22086,7 @@
         <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>127873.65</v>
+        <v>75000</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
@@ -22107,16 +22107,16 @@
         <v>0</v>
       </c>
       <c r="X155" t="n">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="Y155" t="n">
-        <v>155747.3</v>
+        <v>75000</v>
       </c>
       <c r="Z155" t="n">
-        <v>72126.35000000001</v>
+        <v>75000</v>
       </c>
       <c r="AA155" t="n">
-        <v>27873.65</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
         <v>5</v>
@@ -22129,7 +22129,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
+          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -22149,12 +22149,12 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
+          <t>34.10.14.422.4026.9025.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -22166,12 +22166,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -22180,24 +22180,24 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F156" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -22207,56 +22207,56 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>150000</v>
+        <v>7200</v>
       </c>
       <c r="M156" t="n">
         <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
-        <v>150000</v>
+        <v>3600</v>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="R156" t="n">
-        <v>150000</v>
+        <v>21600</v>
       </c>
       <c r="S156" t="n">
-        <v>150000</v>
+        <v>9600</v>
       </c>
       <c r="T156" t="n">
-        <v>150000</v>
+        <v>9600</v>
       </c>
       <c r="U156" t="n">
-        <v>150000</v>
+        <v>10200</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>150000</v>
+        <v>22143</v>
       </c>
       <c r="X156" t="n">
-        <v>0</v>
+        <v>46881</v>
       </c>
       <c r="Y156" t="n">
-        <v>0</v>
+        <v>39738</v>
       </c>
       <c r="Z156" t="n">
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>150000</v>
+        <v>46881</v>
       </c>
       <c r="AB156" t="n">
         <v>5</v>
@@ -22264,12 +22264,12 @@
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -22279,22 +22279,22 @@
       </c>
       <c r="AG156" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
+          <t>34.10.14.423.4026.4322.33903600.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -22306,12 +22306,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -22320,19 +22320,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F157" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -22363,13 +22363,13 @@
         <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>19140.97</v>
       </c>
       <c r="Q157" t="n">
         <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>52809.97</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -22378,25 +22378,25 @@
         <v>0</v>
       </c>
       <c r="U157" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="X157" t="n">
-        <v>589773</v>
+        <v>220966</v>
       </c>
       <c r="Y157" t="n">
-        <v>589773</v>
+        <v>187297</v>
       </c>
       <c r="Z157" t="n">
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>589773</v>
+        <v>220966</v>
       </c>
       <c r="AB157" t="n">
         <v>5</v>
@@ -22404,12 +22404,12 @@
       <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -22429,24 +22429,24 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.4322.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -22456,23 +22456,23 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>244</v>
+        <v>423</v>
       </c>
       <c r="F158" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -22491,52 +22491,52 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>18190190.37</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>5086650.13</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>18190190.37</v>
+        <v>0</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>127873.65</v>
       </c>
       <c r="R158" t="n">
-        <v>45922205.13</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>45922205.12</v>
+        <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>45922205.12</v>
+        <v>0</v>
       </c>
       <c r="U158" t="n">
-        <v>45922205.13</v>
+        <v>0</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>45922205.13</v>
+        <v>0</v>
       </c>
       <c r="X158" t="n">
-        <v>40835555</v>
+        <v>100000</v>
       </c>
       <c r="Y158" t="n">
-        <v>0</v>
+        <v>155747.3</v>
       </c>
       <c r="Z158" t="n">
-        <v>0</v>
+        <v>72126.35000000001</v>
       </c>
       <c r="AA158" t="n">
-        <v>45922205.13</v>
+        <v>27873.65</v>
       </c>
       <c r="AB158" t="n">
         <v>5</v>
@@ -22544,12 +22544,12 @@
       <c r="AC158" t="inlineStr"/>
       <c r="AD158" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -22569,55 +22569,55 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
+          <t>34.10.14.423.4026.9234.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F159" t="n">
         <v>4010</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -22627,20 +22627,20 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O159" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="P159" t="n">
         <v>0</v>
@@ -22649,34 +22649,34 @@
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="S159" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="T159" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U159" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="V159" t="n">
         <v>0</v>
       </c>
       <c r="W159" t="n">
-        <v>600437</v>
+        <v>150000</v>
       </c>
       <c r="X159" t="n">
-        <v>16896102</v>
+        <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="Z159" t="n">
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>16896102</v>
+        <v>150000</v>
       </c>
       <c r="AB159" t="n">
         <v>5</v>
@@ -22689,7 +22689,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -22699,39 +22699,39 @@
       </c>
       <c r="AG159" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
         </is>
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33503900.00.1.500.7069</t>
         </is>
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -22740,14 +22740,14 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F160" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -22804,19 +22804,19 @@
         <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X160" t="n">
-        <v>1000</v>
+        <v>589773</v>
       </c>
       <c r="Y160" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="Z160" t="n">
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1000</v>
+        <v>589773</v>
       </c>
       <c r="AB160" t="n">
         <v>5</v>
@@ -22829,7 +22829,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -22839,7 +22839,7 @@
       </c>
       <c r="AG160" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH160" t="inlineStr">
@@ -22849,12 +22849,12 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
+          <t>34.20.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -22876,28 +22876,28 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F161" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>44906100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -22911,16 +22911,16 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>18190190.37</v>
       </c>
       <c r="M161" t="n">
         <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>361510</v>
+        <v>5086650.13</v>
       </c>
       <c r="O161" t="n">
-        <v>0</v>
+        <v>18190190.37</v>
       </c>
       <c r="P161" t="n">
         <v>0</v>
@@ -22929,25 +22929,25 @@
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>361510</v>
+        <v>45922205.13</v>
       </c>
       <c r="S161" t="n">
-        <v>0</v>
+        <v>45922205.12</v>
       </c>
       <c r="T161" t="n">
-        <v>0</v>
+        <v>45922205.12</v>
       </c>
       <c r="U161" t="n">
-        <v>361510</v>
+        <v>45922205.13</v>
       </c>
       <c r="V161" t="n">
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>361510</v>
+        <v>45922205.13</v>
       </c>
       <c r="X161" t="n">
-        <v>0</v>
+        <v>40835555</v>
       </c>
       <c r="Y161" t="n">
         <v>0</v>
@@ -22956,7 +22956,7 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>361510</v>
+        <v>45922205.13</v>
       </c>
       <c r="AB161" t="n">
         <v>5</v>
@@ -22969,7 +22969,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -22979,7 +22979,7 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>Aquisição de Imóveis</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH161" t="inlineStr">
@@ -22989,12 +22989,12 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -23016,28 +23016,28 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>422</v>
+        <v>244</v>
       </c>
       <c r="F162" t="n">
         <v>4010</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -23051,7 +23051,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>90570908.59999999</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
         <v>0</v>
@@ -23060,43 +23060,43 @@
         <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>90456591.02</v>
+        <v>0</v>
       </c>
       <c r="P162" t="n">
-        <v>21043600.09</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>5086650.13</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>160562812.27</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>135266690.46</v>
+        <v>0</v>
       </c>
       <c r="T162" t="n">
-        <v>140706402.85</v>
+        <v>0</v>
       </c>
       <c r="U162" t="n">
-        <v>139519212.18</v>
+        <v>0</v>
       </c>
       <c r="V162" t="n">
-        <v>5439712.39</v>
+        <v>0</v>
       </c>
       <c r="W162" t="n">
-        <v>165715582</v>
+        <v>600437</v>
       </c>
       <c r="X162" t="n">
-        <v>171813039</v>
+        <v>16896102</v>
       </c>
       <c r="Y162" t="n">
-        <v>5735947</v>
+        <v>16295665</v>
       </c>
       <c r="Z162" t="n">
-        <v>5448160.13</v>
+        <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>166364878.87</v>
+        <v>16896102</v>
       </c>
       <c r="AB162" t="n">
         <v>5</v>
@@ -23109,7 +23109,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AH162" t="inlineStr">
@@ -23129,12 +23129,12 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
+          <t>78.10.08.244.4010.4302.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -23160,14 +23160,14 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F163" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -23177,17 +23177,17 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -23224,10 +23224,10 @@
         <v>0</v>
       </c>
       <c r="W163" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="X163" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="Y163" t="n">
         <v>0</v>
@@ -23236,7 +23236,7 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="AB163" t="n">
         <v>5</v>
@@ -23249,32 +23249,32 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
         <is>
-          <t>05 - Outras Fontes</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
+          <t>78.10.14.122.4001.3002.44905100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -23300,14 +23300,14 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F164" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -23317,17 +23317,17 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>44906100</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L164" t="n">
@@ -23337,7 +23337,7 @@
         <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -23349,7 +23349,7 @@
         <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -23358,16 +23358,16 @@
         <v>0</v>
       </c>
       <c r="U164" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
       </c>
       <c r="W164" t="n">
-        <v>11298</v>
+        <v>361510</v>
       </c>
       <c r="X164" t="n">
-        <v>11298</v>
+        <v>0</v>
       </c>
       <c r="Y164" t="n">
         <v>0</v>
@@ -23376,7 +23376,7 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>11298</v>
+        <v>361510</v>
       </c>
       <c r="AB164" t="n">
         <v>5</v>
@@ -23389,32 +23389,32 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Aquisição de Imóveis</t>
         </is>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
+          <t>78.10.14.122.4001.3002.44906100.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -23471,7 +23471,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>40147923.71</v>
+        <v>90570908.59999999</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
@@ -23480,43 +23480,43 @@
         <v>0</v>
       </c>
       <c r="O165" t="n">
-        <v>34703144.51</v>
+        <v>90456591.02</v>
       </c>
       <c r="P165" t="n">
-        <v>60670522</v>
+        <v>21043600.09</v>
       </c>
       <c r="Q165" t="n">
-        <v>0</v>
+        <v>5086650.13</v>
       </c>
       <c r="R165" t="n">
-        <v>197559544</v>
+        <v>160562812.27</v>
       </c>
       <c r="S165" t="n">
-        <v>107626518.4</v>
+        <v>135266690.46</v>
       </c>
       <c r="T165" t="n">
-        <v>107626518.4</v>
+        <v>140706402.85</v>
       </c>
       <c r="U165" t="n">
-        <v>136889022</v>
+        <v>139519212.18</v>
       </c>
       <c r="V165" t="n">
-        <v>0</v>
+        <v>5439712.39</v>
       </c>
       <c r="W165" t="n">
-        <v>136889022</v>
+        <v>165715582</v>
       </c>
       <c r="X165" t="n">
-        <v>141616875</v>
+        <v>171813039</v>
       </c>
       <c r="Y165" t="n">
-        <v>4727853</v>
+        <v>5735947</v>
       </c>
       <c r="Z165" t="n">
-        <v>0</v>
+        <v>5448160.13</v>
       </c>
       <c r="AA165" t="n">
-        <v>141616875</v>
+        <v>166364878.87</v>
       </c>
       <c r="AB165" t="n">
         <v>5</v>
@@ -23539,7 +23539,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH165" t="inlineStr">
@@ -23549,12 +23549,12 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33503900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -23597,21 +23597,21 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>30857681.59</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -23620,43 +23620,43 @@
         <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>25306603.06</v>
+        <v>0</v>
       </c>
       <c r="P166" t="n">
-        <v>49898263.91</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
         <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>129341289.91</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>79232487.98999999</v>
+        <v>0</v>
       </c>
       <c r="T166" t="n">
-        <v>99116487.98999999</v>
+        <v>0</v>
       </c>
       <c r="U166" t="n">
-        <v>79443026</v>
+        <v>0</v>
       </c>
       <c r="V166" t="n">
-        <v>19884000</v>
+        <v>0</v>
       </c>
       <c r="W166" t="n">
-        <v>79443026</v>
+        <v>2000</v>
       </c>
       <c r="X166" t="n">
-        <v>83642123</v>
+        <v>2000</v>
       </c>
       <c r="Y166" t="n">
-        <v>2792377</v>
+        <v>0</v>
       </c>
       <c r="Z166" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>82235403</v>
+        <v>2000</v>
       </c>
       <c r="AB166" t="n">
         <v>5</v>
@@ -23674,27 +23674,27 @@
       </c>
       <c r="AF166" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>05 - Outras Fontes</t>
         </is>
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903000.05.1.799.1268</t>
         </is>
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -23737,7 +23737,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -23747,7 +23747,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="L167" t="n">
@@ -23784,10 +23784,10 @@
         <v>0</v>
       </c>
       <c r="W167" t="n">
-        <v>2000</v>
+        <v>11298</v>
       </c>
       <c r="X167" t="n">
-        <v>2000</v>
+        <v>11298</v>
       </c>
       <c r="Y167" t="n">
         <v>0</v>
@@ -23796,7 +23796,7 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>2000</v>
+        <v>11298</v>
       </c>
       <c r="AB167" t="n">
         <v>5</v>
@@ -23819,22 +23819,22 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
+          <t>78.10.14.422.4010.4426.33903000.08.1.759.1416</t>
         </is>
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>33913900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -23891,52 +23891,52 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>448000</v>
+        <v>40147923.71</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>448000</v>
+        <v>34703144.51</v>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>60670522</v>
       </c>
       <c r="Q168" t="n">
         <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>1406720</v>
+        <v>197559544</v>
       </c>
       <c r="S168" t="n">
-        <v>1406720</v>
+        <v>107626518.4</v>
       </c>
       <c r="T168" t="n">
-        <v>1406720</v>
+        <v>107626518.4</v>
       </c>
       <c r="U168" t="n">
-        <v>1406720</v>
+        <v>136889022</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
       </c>
       <c r="W168" t="n">
-        <v>1406720</v>
+        <v>136889022</v>
       </c>
       <c r="X168" t="n">
-        <v>0</v>
+        <v>141616875</v>
       </c>
       <c r="Y168" t="n">
-        <v>0</v>
+        <v>4727853</v>
       </c>
       <c r="Z168" t="n">
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>1406720</v>
+        <v>141616875</v>
       </c>
       <c r="AB168" t="n">
         <v>5</v>
@@ -23959,7 +23959,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>Transferência entre Órgãos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AH168" t="inlineStr">
@@ -23969,24 +23969,24 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903200.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -24000,24 +24000,24 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F169" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -24031,7 +24031,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>30857681.59</v>
       </c>
       <c r="M169" t="n">
         <v>0</v>
@@ -24040,43 +24040,43 @@
         <v>0</v>
       </c>
       <c r="O169" t="n">
-        <v>0</v>
+        <v>25306603.06</v>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>49898263.91</v>
       </c>
       <c r="Q169" t="n">
         <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>129341289.91</v>
       </c>
       <c r="S169" t="n">
-        <v>0</v>
+        <v>79232487.98999999</v>
       </c>
       <c r="T169" t="n">
-        <v>0</v>
+        <v>99116487.98999999</v>
       </c>
       <c r="U169" t="n">
-        <v>0</v>
+        <v>79443026</v>
       </c>
       <c r="V169" t="n">
-        <v>0</v>
+        <v>19884000</v>
       </c>
       <c r="W169" t="n">
-        <v>3000</v>
+        <v>79443026</v>
       </c>
       <c r="X169" t="n">
-        <v>3000</v>
+        <v>83642123</v>
       </c>
       <c r="Y169" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Z169" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="AA169" t="n">
-        <v>3000</v>
+        <v>82235403</v>
       </c>
       <c r="AB169" t="n">
         <v>5</v>
@@ -24084,12 +24084,12 @@
       <c r="AC169" t="inlineStr"/>
       <c r="AD169" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH169" t="inlineStr">
@@ -24109,24 +24109,24 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -24140,19 +24140,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F170" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -24162,12 +24162,12 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="L170" t="n">
@@ -24204,10 +24204,10 @@
         <v>0</v>
       </c>
       <c r="W170" t="n">
-        <v>6245</v>
+        <v>2000</v>
       </c>
       <c r="X170" t="n">
-        <v>6245</v>
+        <v>2000</v>
       </c>
       <c r="Y170" t="n">
         <v>0</v>
@@ -24216,7 +24216,7 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>6245</v>
+        <v>2000</v>
       </c>
       <c r="AB170" t="n">
         <v>5</v>
@@ -24224,17 +24224,17 @@
       <c r="AC170" t="inlineStr"/>
       <c r="AD170" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG170" t="inlineStr">
@@ -24244,29 +24244,29 @@
       </c>
       <c r="AH170" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33903900.08.1.759.1796</t>
         </is>
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -24280,24 +24280,24 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>126</v>
+        <v>422</v>
       </c>
       <c r="F171" t="n">
-        <v>4002</v>
+        <v>4010</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>DTIC</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33913900</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -24311,16 +24311,16 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>448000</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="O171" t="n">
-        <v>0</v>
+        <v>448000</v>
       </c>
       <c r="P171" t="n">
         <v>0</v>
@@ -24329,25 +24329,25 @@
         <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="S171" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="T171" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="U171" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
       </c>
       <c r="W171" t="n">
-        <v>1000</v>
+        <v>1406720</v>
       </c>
       <c r="X171" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y171" t="n">
         <v>0</v>
@@ -24356,7 +24356,7 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>1000</v>
+        <v>1406720</v>
       </c>
       <c r="AB171" t="n">
         <v>5</v>
@@ -24364,12 +24364,12 @@
       <c r="AC171" t="inlineStr"/>
       <c r="AD171" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>DTIC - Desenvolvimento</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -24379,7 +24379,7 @@
       </c>
       <c r="AG171" t="inlineStr">
         <is>
-          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+          <t>Transferência entre Órgãos</t>
         </is>
       </c>
       <c r="AH171" t="inlineStr">
@@ -24389,12 +24389,12 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
+          <t>78.10.14.422.4010.4426.33913900.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -24420,24 +24420,24 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F172" t="n">
-        <v>4019</v>
+        <v>4004</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L172" t="n">
@@ -24484,10 +24484,10 @@
         <v>0</v>
       </c>
       <c r="W172" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="X172" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="Y172" t="n">
         <v>0</v>
@@ -24496,7 +24496,7 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AB172" t="n">
         <v>5</v>
@@ -24504,12 +24504,12 @@
       <c r="AC172" t="inlineStr"/>
       <c r="AD172" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -24519,22 +24519,22 @@
       </c>
       <c r="AG172" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+          <t>90.10.14.122.4004.2803.33903000.00.1.500.9001</t>
         </is>
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>24/05/2026 07:51:58</t>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>
@@ -24560,38 +24560,38 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F173" t="n">
-        <v>4019</v>
+        <v>4004</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>26512660.49</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
         <v>0</v>
@@ -24600,34 +24600,34 @@
         <v>0</v>
       </c>
       <c r="O173" t="n">
-        <v>26512660.49</v>
+        <v>0</v>
       </c>
       <c r="P173" t="n">
-        <v>3945313.07</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
         <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>42041812.47</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
-        <v>35250309.69</v>
+        <v>0</v>
       </c>
       <c r="T173" t="n">
-        <v>36863073.79</v>
+        <v>0</v>
       </c>
       <c r="U173" t="n">
-        <v>38096499.4</v>
+        <v>0</v>
       </c>
       <c r="V173" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="W173" t="n">
-        <v>61292510</v>
+        <v>6245</v>
       </c>
       <c r="X173" t="n">
-        <v>61292510</v>
+        <v>6245</v>
       </c>
       <c r="Y173" t="n">
         <v>0</v>
@@ -24636,7 +24636,7 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>61292510</v>
+        <v>6245</v>
       </c>
       <c r="AB173" t="n">
         <v>5</v>
@@ -24644,37 +24644,457 @@
       <c r="AC173" t="inlineStr"/>
       <c r="AD173" t="inlineStr">
         <is>
+          <t>Conselho</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>Conselho</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>90.10.14.122.4004.2803.33903900.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>25/05/2026 09:48:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>126</v>
+      </c>
+      <c r="F174" t="n">
+        <v>4002</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>DTIC</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>44904000</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>9001</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="n">
+        <v>0</v>
+      </c>
+      <c r="T174" t="n">
+        <v>0</v>
+      </c>
+      <c r="U174" t="n">
+        <v>0</v>
+      </c>
+      <c r="V174" t="n">
+        <v>0</v>
+      </c>
+      <c r="W174" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X174" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC174" t="inlineStr"/>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>Tecnologia</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>DTIC - Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>90.10.14.126.4002.1220.44904000.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>25/05/2026 09:48:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>422</v>
+      </c>
+      <c r="F175" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>0004</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>0</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" t="n">
+        <v>0</v>
+      </c>
+      <c r="V175" t="n">
+        <v>0</v>
+      </c>
+      <c r="W175" t="n">
+        <v>0</v>
+      </c>
+      <c r="X175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC175" t="inlineStr"/>
+      <c r="AD175" t="inlineStr">
+        <is>
           <t>Criança e Adolescente</t>
         </is>
       </c>
-      <c r="AE173" t="inlineStr">
+      <c r="AE175" t="inlineStr">
         <is>
           <t>FUMCAD</t>
         </is>
       </c>
-      <c r="AF173" t="inlineStr">
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>90.10.14.422.4019.6160.33503900.00.1.501.0004</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>25/05/2026 09:48:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>422</v>
+      </c>
+      <c r="F176" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>26512660.49</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>26512660.49</v>
+      </c>
+      <c r="P176" t="n">
+        <v>3945313.07</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" t="n">
+        <v>42041812.47</v>
+      </c>
+      <c r="S176" t="n">
+        <v>35250309.69</v>
+      </c>
+      <c r="T176" t="n">
+        <v>36863073.79</v>
+      </c>
+      <c r="U176" t="n">
+        <v>38096499.4</v>
+      </c>
+      <c r="V176" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="W176" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X176" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC176" t="inlineStr"/>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
         <is>
           <t>08 - Recusos Vinculados</t>
         </is>
       </c>
-      <c r="AG173" t="inlineStr">
+      <c r="AG176" t="inlineStr">
         <is>
           <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
-      <c r="AH173" t="inlineStr">
+      <c r="AH176" t="inlineStr">
         <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AI173" t="inlineStr">
+      <c r="AI176" t="inlineStr">
         <is>
           <t>90.10.14.422.4019.6160.33503900.08.1.759.0958</t>
         </is>
       </c>
-      <c r="AJ173" t="inlineStr">
-        <is>
-          <t>24/05/2026 07:51:58</t>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>25/05/2026 09:48:01</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>334134</v>
       </c>
       <c r="O7" t="n">
-        <v>11982.8</v>
+        <v>14217.8</v>
       </c>
       <c r="P7" t="n">
         <v>308127.99</v>
@@ -1369,7 +1369,7 @@
         <v>63262</v>
       </c>
       <c r="R7" t="n">
-        <v>857683.76</v>
+        <v>858923.46</v>
       </c>
       <c r="S7" t="n">
         <v>258487.35</v>
@@ -1378,7 +1378,7 @@
         <v>258487.35</v>
       </c>
       <c r="U7" t="n">
-        <v>549555.77</v>
+        <v>550795.47</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -1503,13 +1503,13 @@
         <v>71756.96000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>181083.4</v>
+        <v>186055.9</v>
       </c>
       <c r="Q8" t="n">
         <v>57913</v>
       </c>
       <c r="R8" t="n">
-        <v>597048.9</v>
+        <v>602021.4</v>
       </c>
       <c r="S8" t="n">
         <v>348834.72</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2213923.2</v>
+        <v>2242880.09</v>
       </c>
       <c r="P10" t="n">
         <v>1916363.61</v>
@@ -1792,10 +1792,10 @@
         <v>14150380.75</v>
       </c>
       <c r="S10" t="n">
-        <v>8426281.32</v>
+        <v>8431131.32</v>
       </c>
       <c r="T10" t="n">
-        <v>8550384.91</v>
+        <v>8555234.91</v>
       </c>
       <c r="U10" t="n">
         <v>12234017.14</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v>116000</v>
       </c>
       <c r="O11" t="n">
-        <v>21682.98</v>
+        <v>21907.98</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -3183,25 +3183,25 @@
         <v>1456839.07</v>
       </c>
       <c r="P20" t="n">
-        <v>3125692.73</v>
+        <v>3188599.85</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>8815226.73</v>
+        <v>8879223.73</v>
       </c>
       <c r="S20" t="n">
-        <v>4831031.07</v>
+        <v>4824031.07</v>
       </c>
       <c r="T20" t="n">
         <v>4831031.1</v>
       </c>
       <c r="U20" t="n">
-        <v>5689534</v>
+        <v>5690623.88</v>
       </c>
       <c r="V20" t="n">
-        <v>0.03</v>
+        <v>7000.03</v>
       </c>
       <c r="W20" t="n">
         <v>5690644</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3857898.7</v>
+        <v>3951136.37</v>
       </c>
       <c r="P32" t="n">
         <v>1273689.24</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>129705.73</v>
+        <v>130137.67</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -17880,7 +17880,7 @@
         <v>166923</v>
       </c>
       <c r="O125" t="n">
-        <v>21384.72</v>
+        <v>21712.72</v>
       </c>
       <c r="P125" t="n">
         <v>411380.02</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -19149,7 +19149,7 @@
         <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -19158,7 +19158,7 @@
         <v>0</v>
       </c>
       <c r="U134" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -19569,7 +19569,7 @@
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -19578,7 +19578,7 @@
         <v>0</v>
       </c>
       <c r="U137" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -22369,7 +22369,7 @@
         <v>15000</v>
       </c>
       <c r="R157" t="n">
-        <v>21600</v>
+        <v>22200</v>
       </c>
       <c r="S157" t="n">
         <v>9600</v>
@@ -22378,7 +22378,7 @@
         <v>9600</v>
       </c>
       <c r="U157" t="n">
-        <v>10200</v>
+        <v>10800</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -24031,7 +24031,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>40147923.71</v>
+        <v>40361270.91</v>
       </c>
       <c r="M169" t="n">
         <v>0</v>
@@ -24040,7 +24040,7 @@
         <v>0</v>
       </c>
       <c r="O169" t="n">
-        <v>34703144.51</v>
+        <v>36595939.71</v>
       </c>
       <c r="P169" t="n">
         <v>60670522</v>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>31217681.59</v>
+        <v>31307681.59</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24180,7 +24180,7 @@
         <v>0</v>
       </c>
       <c r="O170" t="n">
-        <v>25306603.06</v>
+        <v>25427969.69</v>
       </c>
       <c r="P170" t="n">
         <v>49898263.91</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>
@@ -25163,22 +25163,22 @@
         <v>26512660.49</v>
       </c>
       <c r="P177" t="n">
-        <v>3945313.07</v>
+        <v>3974852.19</v>
       </c>
       <c r="Q177" t="n">
         <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>42041812.47</v>
+        <v>42504185.13</v>
       </c>
       <c r="S177" t="n">
-        <v>35250309.69</v>
+        <v>35281048.81</v>
       </c>
       <c r="T177" t="n">
-        <v>36863073.79</v>
+        <v>36893812.91</v>
       </c>
       <c r="U177" t="n">
-        <v>38096499.4</v>
+        <v>38529332.94</v>
       </c>
       <c r="V177" t="n">
         <v>1612764.1</v>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>27/05/2026 09:36:17</t>
+          <t>28/05/2026 09:43:47</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>53733.62</v>
+        <v>60940.47</v>
       </c>
       <c r="P6" t="n">
         <v>23626.09</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -1372,16 +1372,16 @@
         <v>858923.46</v>
       </c>
       <c r="S7" t="n">
-        <v>258487.35</v>
+        <v>267600.35</v>
       </c>
       <c r="T7" t="n">
-        <v>258487.35</v>
+        <v>372600.35</v>
       </c>
       <c r="U7" t="n">
         <v>550795.47</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>105000</v>
       </c>
       <c r="W7" t="n">
         <v>661845</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2299634.46</v>
+        <v>2295341.92</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2242880.09</v>
+        <v>2231571.95</v>
       </c>
       <c r="P10" t="n">
-        <v>1916363.61</v>
+        <v>1929544.08</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1792,16 +1792,16 @@
         <v>14150380.75</v>
       </c>
       <c r="S10" t="n">
-        <v>8431131.32</v>
+        <v>8419823.18</v>
       </c>
       <c r="T10" t="n">
         <v>8555234.91</v>
       </c>
       <c r="U10" t="n">
-        <v>12234017.14</v>
+        <v>12220836.67</v>
       </c>
       <c r="V10" t="n">
-        <v>124103.59</v>
+        <v>135411.73</v>
       </c>
       <c r="W10" t="n">
         <v>12250650</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v>116000</v>
       </c>
       <c r="O11" t="n">
-        <v>21907.98</v>
+        <v>46963.68</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>659505.4</v>
+        <v>659602.22</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>652000.73</v>
+        <v>657391.13</v>
       </c>
       <c r="P30" t="n">
         <v>370669.45</v>
@@ -4592,10 +4592,10 @@
         <v>2212341.49</v>
       </c>
       <c r="S30" t="n">
-        <v>1635347.1</v>
+        <v>1656354.21</v>
       </c>
       <c r="T30" t="n">
-        <v>1749242.93</v>
+        <v>1770250.04</v>
       </c>
       <c r="U30" t="n">
         <v>1841672.04</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>19159774.07</v>
+        <v>19160355.68</v>
       </c>
       <c r="S32" t="n">
         <v>16550727.08</v>
@@ -4878,7 +4878,7 @@
         <v>16990873.17</v>
       </c>
       <c r="U32" t="n">
-        <v>17886084.83</v>
+        <v>17886666.44</v>
       </c>
       <c r="V32" t="n">
         <v>440146.09</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>130137.67</v>
+        <v>164259.81</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -6689,16 +6689,16 @@
         <v>1186346</v>
       </c>
       <c r="R45" t="n">
-        <v>15702101.85</v>
+        <v>15734235.17</v>
       </c>
       <c r="S45" t="n">
-        <v>5295350.24</v>
+        <v>5296550.24</v>
       </c>
       <c r="T45" t="n">
-        <v>5717985.82</v>
+        <v>5719185.82</v>
       </c>
       <c r="U45" t="n">
-        <v>14718497.85</v>
+        <v>14750631.17</v>
       </c>
       <c r="V45" t="n">
         <v>422635.58</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
         <v>219000</v>
       </c>
       <c r="O46" t="n">
-        <v>41714.54</v>
+        <v>70905.44</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7800,7 @@
         <v>50000</v>
       </c>
       <c r="O53" t="n">
-        <v>6005.24</v>
+        <v>10768.14</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>122884.29</v>
+        <v>153936.68</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11589,7 @@
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>260366.25</v>
+        <v>410366.25</v>
       </c>
       <c r="S80" t="n">
         <v>133147</v>
@@ -11598,7 +11598,7 @@
         <v>134497</v>
       </c>
       <c r="U80" t="n">
-        <v>256794.66</v>
+        <v>406794.66</v>
       </c>
       <c r="V80" t="n">
         <v>1350</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11720,7 @@
         <v>40000</v>
       </c>
       <c r="O81" t="n">
-        <v>2770.6</v>
+        <v>3520.67</v>
       </c>
       <c r="P81" t="n">
         <v>450</v>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -17320,7 +17320,7 @@
         <v>50000</v>
       </c>
       <c r="O121" t="n">
-        <v>11250.59</v>
+        <v>15595.99</v>
       </c>
       <c r="P121" t="n">
         <v>2250</v>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -17871,25 +17871,25 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>21712.72</v>
+        <v>22040.72</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>166923</v>
+        <v>259262</v>
       </c>
       <c r="O125" t="n">
         <v>21712.72</v>
       </c>
       <c r="P125" t="n">
-        <v>411380.02</v>
+        <v>525416.98</v>
       </c>
       <c r="Q125" t="n">
         <v>8077</v>
       </c>
       <c r="R125" t="n">
-        <v>737135.02</v>
+        <v>889609.24</v>
       </c>
       <c r="S125" t="n">
         <v>79099.03999999999</v>
@@ -17898,13 +17898,13 @@
         <v>79099.03999999999</v>
       </c>
       <c r="U125" t="n">
-        <v>325755</v>
+        <v>364192.26</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>325755</v>
+        <v>418094</v>
       </c>
       <c r="X125" t="n">
         <v>158832</v>
@@ -17916,7 +17916,7 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>325755</v>
+        <v>418094</v>
       </c>
       <c r="AB125" t="n">
         <v>5</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>242961.36</v>
+        <v>323948.48</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -18151,40 +18151,40 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>854484.87</v>
+        <v>875899.35</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>211572</v>
       </c>
       <c r="O127" t="n">
         <v>852219.98</v>
       </c>
       <c r="P127" t="n">
-        <v>2580572.47</v>
+        <v>2661868</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>6319750.68</v>
+        <v>6612696.72</v>
       </c>
       <c r="S127" t="n">
-        <v>2711399.82</v>
+        <v>2712899.82</v>
       </c>
       <c r="T127" t="n">
-        <v>2711719.82</v>
+        <v>2713219.82</v>
       </c>
       <c r="U127" t="n">
-        <v>3739178.21</v>
+        <v>3950828.72</v>
       </c>
       <c r="V127" t="n">
         <v>320</v>
       </c>
       <c r="W127" t="n">
-        <v>3739256.72</v>
+        <v>3950828.72</v>
       </c>
       <c r="X127" t="n">
         <v>4953156</v>
@@ -18196,7 +18196,7 @@
         <v>888923</v>
       </c>
       <c r="AA127" t="n">
-        <v>4064233</v>
+        <v>4275805</v>
       </c>
       <c r="AB127" t="n">
         <v>5</v>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -18300,7 +18300,7 @@
         <v>158000</v>
       </c>
       <c r="O128" t="n">
-        <v>54411.04</v>
+        <v>86013.25</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -19709,7 +19709,7 @@
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -19718,7 +19718,7 @@
         <v>0</v>
       </c>
       <c r="U138" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>19041664.7</v>
+        <v>20222134.92</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -20564,7 +20564,7 @@
         <v>93918.99000000001</v>
       </c>
       <c r="W144" t="n">
-        <v>4104655</v>
+        <v>3800744</v>
       </c>
       <c r="X144" t="n">
         <v>4806049</v>
@@ -20573,10 +20573,10 @@
         <v>63262</v>
       </c>
       <c r="Z144" t="n">
-        <v>638132</v>
+        <v>942043</v>
       </c>
       <c r="AA144" t="n">
-        <v>4167917</v>
+        <v>3864006</v>
       </c>
       <c r="AB144" t="n">
         <v>5</v>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -22351,7 +22351,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>7200</v>
+        <v>7800</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -23611,16 +23611,16 @@
         </is>
       </c>
       <c r="L166" t="n">
+        <v>91096031.91</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
         <v>90570908.59999999</v>
-      </c>
-      <c r="M166" t="n">
-        <v>0</v>
-      </c>
-      <c r="N166" t="n">
-        <v>0</v>
-      </c>
-      <c r="O166" t="n">
-        <v>90456591.02</v>
       </c>
       <c r="P166" t="n">
         <v>21043600.09</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>31307681.59</v>
+        <v>31757681.59</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24180,7 +24180,7 @@
         <v>0</v>
       </c>
       <c r="O170" t="n">
-        <v>25427969.69</v>
+        <v>26687969.69</v>
       </c>
       <c r="P170" t="n">
         <v>49898263.91</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>
@@ -25151,7 +25151,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>26512660.49</v>
+        <v>27224747.91</v>
       </c>
       <c r="M177" t="n">
         <v>0</v>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>28/05/2026 09:43:47</t>
+          <t>29/05/2026 09:31:28</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>10652419.08</v>
+        <v>13385006.64</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>10652419.08</v>
+        <v>13385006.64</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1089,16 +1089,16 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>10652419.08</v>
+        <v>13385006.64</v>
       </c>
       <c r="S5" t="n">
-        <v>10652419.08</v>
+        <v>13385006.64</v>
       </c>
       <c r="T5" t="n">
-        <v>10652419.08</v>
+        <v>13385006.64</v>
       </c>
       <c r="U5" t="n">
-        <v>10652419.08</v>
+        <v>13385006.64</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>61510.47</v>
+        <v>62855.61</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1229,16 +1229,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>85136.56</v>
+        <v>86481.7</v>
       </c>
       <c r="S6" t="n">
-        <v>61510.47</v>
+        <v>62855.61</v>
       </c>
       <c r="T6" t="n">
-        <v>77936.56</v>
+        <v>79281.7</v>
       </c>
       <c r="U6" t="n">
-        <v>61510.47</v>
+        <v>62855.61</v>
       </c>
       <c r="V6" t="n">
         <v>16426.09</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         <v>115966</v>
       </c>
       <c r="O8" t="n">
-        <v>71756.96000000001</v>
+        <v>87272.24000000001</v>
       </c>
       <c r="P8" t="n">
         <v>186055.9</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2295341.92</v>
+        <v>2545319.67</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,16 +1780,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2231571.95</v>
+        <v>2233079.15</v>
       </c>
       <c r="P10" t="n">
-        <v>1929544.08</v>
+        <v>2025944.04</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>14150380.75</v>
+        <v>14260335.85</v>
       </c>
       <c r="S10" t="n">
         <v>8419823.18</v>
@@ -1798,7 +1798,7 @@
         <v>8555234.91</v>
       </c>
       <c r="U10" t="n">
-        <v>12220836.67</v>
+        <v>12234391.81</v>
       </c>
       <c r="V10" t="n">
         <v>135411.73</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v>116000</v>
       </c>
       <c r="O11" t="n">
-        <v>46963.68</v>
+        <v>48056.44</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1899983.68</v>
+        <v>2394157.97</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1899983.68</v>
+        <v>2394157.97</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -2069,16 +2069,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1899983.68</v>
+        <v>2394157.97</v>
       </c>
       <c r="S12" t="n">
-        <v>1899983.68</v>
+        <v>2394157.97</v>
       </c>
       <c r="T12" t="n">
-        <v>1899983.68</v>
+        <v>2394157.97</v>
       </c>
       <c r="U12" t="n">
-        <v>1899983.68</v>
+        <v>2394157.97</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>99051.78999999999</v>
+        <v>117953.94</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>99051.78999999999</v>
+        <v>117953.94</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -2349,16 +2349,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>99051.78999999999</v>
+        <v>117953.94</v>
       </c>
       <c r="S14" t="n">
-        <v>99051.78999999999</v>
+        <v>117953.94</v>
       </c>
       <c r="T14" t="n">
-        <v>99051.78999999999</v>
+        <v>117953.94</v>
       </c>
       <c r="U14" t="n">
-        <v>99051.78999999999</v>
+        <v>117953.94</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
         <v>50000</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>7035.32</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1875128.53</v>
+        <v>1884045.71</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>657391.13</v>
+        <v>657501.1</v>
       </c>
       <c r="P30" t="n">
         <v>370669.45</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4043127.4</v>
+        <v>4813416.35</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3951136.37</v>
+        <v>3952238.66</v>
       </c>
       <c r="P32" t="n">
         <v>1273689.24</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>164259.81</v>
+        <v>165425.92</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1291588.11</v>
+        <v>1334964.4</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
         <v>219000</v>
       </c>
       <c r="O46" t="n">
-        <v>70905.44</v>
+        <v>71494.37</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7800,7 @@
         <v>50000</v>
       </c>
       <c r="O53" t="n">
-        <v>10768.14</v>
+        <v>10942.96</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11720,7 @@
         <v>40000</v>
       </c>
       <c r="O81" t="n">
-        <v>3520.67</v>
+        <v>3528.45</v>
       </c>
       <c r="P81" t="n">
         <v>450</v>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -14943,13 +14943,13 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>8373</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>2225</v>
       </c>
       <c r="R104" t="n">
-        <v>8373</v>
+        <v>18971</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -14958,13 +14958,13 @@
         <v>0</v>
       </c>
       <c r="U104" t="n">
-        <v>8373</v>
+        <v>10598</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>8373</v>
+        <v>10598</v>
       </c>
       <c r="X104" t="n">
         <v>10598</v>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -16492,10 +16492,10 @@
         <v>8863680.02</v>
       </c>
       <c r="S115" t="n">
-        <v>889621.71</v>
+        <v>925621.71</v>
       </c>
       <c r="T115" t="n">
-        <v>889621.71</v>
+        <v>925621.71</v>
       </c>
       <c r="U115" t="n">
         <v>8303680.02</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -17320,7 +17320,7 @@
         <v>50000</v>
       </c>
       <c r="O121" t="n">
-        <v>15595.99</v>
+        <v>15638.58</v>
       </c>
       <c r="P121" t="n">
         <v>2250</v>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>875899.35</v>
+        <v>904591.3</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -20564,13 +20564,13 @@
         <v>93918.99000000001</v>
       </c>
       <c r="W144" t="n">
-        <v>3800744</v>
+        <v>3798519</v>
       </c>
       <c r="X144" t="n">
         <v>4806049</v>
       </c>
       <c r="Y144" t="n">
-        <v>63262</v>
+        <v>65487</v>
       </c>
       <c r="Z144" t="n">
         <v>942043</v>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -20680,7 +20680,7 @@
         <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>312.26</v>
+        <v>327.92</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -22360,7 +22360,7 @@
         <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>4200</v>
+        <v>5400</v>
       </c>
       <c r="P157" t="n">
         <v>11400</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>91096031.91</v>
+        <v>91251027.70999999</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>31757681.59</v>
+        <v>31847681.59</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24180,7 +24180,7 @@
         <v>0</v>
       </c>
       <c r="O170" t="n">
-        <v>26687969.69</v>
+        <v>30737969.69</v>
       </c>
       <c r="P170" t="n">
         <v>49898263.91</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>
@@ -25163,7 +25163,7 @@
         <v>26512660.49</v>
       </c>
       <c r="P177" t="n">
-        <v>3974852.19</v>
+        <v>4120579.53</v>
       </c>
       <c r="Q177" t="n">
         <v>0</v>
@@ -25172,13 +25172,13 @@
         <v>42504185.13</v>
       </c>
       <c r="S177" t="n">
-        <v>35281048.81</v>
+        <v>35701639.67</v>
       </c>
       <c r="T177" t="n">
-        <v>36893812.91</v>
+        <v>37314403.77</v>
       </c>
       <c r="U177" t="n">
-        <v>38529332.94</v>
+        <v>38383605.6</v>
       </c>
       <c r="V177" t="n">
         <v>1612764.1</v>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>29/05/2026 09:31:28</t>
+          <t>30/05/2026 07:57:23</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202605.xlsx
+++ b/base_despesas/2026/despesas_202605.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -24043,19 +24043,19 @@
         <v>36595939.71</v>
       </c>
       <c r="P169" t="n">
-        <v>60670522</v>
+        <v>62818272</v>
       </c>
       <c r="Q169" t="n">
         <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>197559544</v>
+        <v>199707294</v>
       </c>
       <c r="S169" t="n">
-        <v>107626518.4</v>
+        <v>113049655.2</v>
       </c>
       <c r="T169" t="n">
-        <v>107626518.4</v>
+        <v>113049655.2</v>
       </c>
       <c r="U169" t="n">
         <v>136889022</v>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57:23</t>
+          <t>31/05/2026 08:13:41</t>
         </is>
       </c>
     </row>
